--- a/raw/Timetable_2026Autumn_2025LE.xlsx
+++ b/raw/Timetable_2026Autumn_2025LE.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30425"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACCF92B2-579D-4E72-A46A-E1825EFA7F01}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14970802-2FB1-4743-8917-A2D6AC0E7B98}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="178">
   <si>
     <t>week</t>
   </si>
@@ -237,9 +237,6 @@
     <t>23       Sep.</t>
   </si>
   <si>
-    <t>B110</t>
-  </si>
-  <si>
     <t>24       Sep.</t>
   </si>
   <si>
@@ -580,9 +577,6 @@
   </si>
   <si>
     <t>10       Jan.</t>
-  </si>
-  <si>
-    <t>B109</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1029,46 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1045,9 +1078,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1068,42 +1098,6 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1112,7 +1106,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -1457,81 +1451,81 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="62" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="75"/>
-      <c r="D2" s="69" t="s">
+      <c r="D2" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69" t="s">
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69" t="s">
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69" t="s">
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69" t="s">
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69" t="s">
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="69"/>
-      <c r="U2" s="69"/>
+      <c r="T2" s="52"/>
+      <c r="U2" s="52"/>
     </row>
     <row r="3" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="69"/>
-      <c r="B3" s="73"/>
+      <c r="A3" s="52"/>
+      <c r="B3" s="64"/>
       <c r="C3" s="76"/>
-      <c r="D3" s="70" t="s">
+      <c r="D3" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="69" t="s">
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="69" t="s">
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="69"/>
-      <c r="L3" s="69"/>
-      <c r="M3" s="69" t="s">
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="69"/>
-      <c r="O3" s="69"/>
-      <c r="P3" s="69" t="s">
+      <c r="N3" s="52"/>
+      <c r="O3" s="52"/>
+      <c r="P3" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="69"/>
-      <c r="R3" s="69"/>
-      <c r="S3" s="69" t="s">
+      <c r="Q3" s="52"/>
+      <c r="R3" s="52"/>
+      <c r="S3" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="69"/>
-      <c r="U3" s="69"/>
+      <c r="T3" s="52"/>
+      <c r="U3" s="52"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="56">
+      <c r="A4" s="53">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1589,7 +1583,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="56"/>
+      <c r="A5" s="53"/>
       <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
@@ -1647,7 +1641,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="56"/>
+      <c r="A6" s="53"/>
       <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
@@ -1703,7 +1697,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="56"/>
+      <c r="A7" s="53"/>
       <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
@@ -1761,7 +1755,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="56"/>
+      <c r="A8" s="53"/>
       <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
@@ -1823,7 +1817,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="56"/>
+      <c r="A9" s="53"/>
       <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
@@ -1867,7 +1861,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="56"/>
+      <c r="A10" s="53"/>
       <c r="B10" s="2" t="s">
         <v>40</v>
       </c>
@@ -1909,7 +1903,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="52">
+      <c r="A11" s="60">
         <v>2</v>
       </c>
       <c r="B11" s="13" t="s">
@@ -1957,7 +1951,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="52"/>
+      <c r="A12" s="60"/>
       <c r="B12" s="13" t="s">
         <v>46</v>
       </c>
@@ -2001,7 +1995,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="52"/>
+      <c r="A13" s="60"/>
       <c r="B13" s="13" t="s">
         <v>48</v>
       </c>
@@ -2045,7 +2039,7 @@
       </c>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="52"/>
+      <c r="A14" s="60"/>
       <c r="B14" s="13" t="s">
         <v>49</v>
       </c>
@@ -2091,7 +2085,7 @@
       <c r="AA14" s="3"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="52"/>
+      <c r="A15" s="60"/>
       <c r="B15" s="13" t="s">
         <v>53</v>
       </c>
@@ -2125,7 +2119,7 @@
       <c r="AA15" s="3"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="52"/>
+      <c r="A16" s="60"/>
       <c r="B16" s="13" t="s">
         <v>54</v>
       </c>
@@ -2157,7 +2151,7 @@
       <c r="AA16" s="3"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="52"/>
+      <c r="A17" s="60"/>
       <c r="B17" s="13" t="s">
         <v>55</v>
       </c>
@@ -2184,7 +2178,7 @@
       <c r="U17" s="16"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="56">
+      <c r="A18" s="53">
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -2221,7 +2215,7 @@
       <c r="U18" s="5"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="56"/>
+      <c r="A19" s="53"/>
       <c r="B19" s="2" t="s">
         <v>57</v>
       </c>
@@ -2268,7 +2262,7 @@
       <c r="U19" s="5"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="56"/>
+      <c r="A20" s="53"/>
       <c r="B20" s="2" t="s">
         <v>58</v>
       </c>
@@ -2315,7 +2309,7 @@
       <c r="U20" s="5"/>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="56"/>
+      <c r="A21" s="53"/>
       <c r="B21" s="2" t="s">
         <v>59</v>
       </c>
@@ -2374,7 +2368,7 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="56"/>
+      <c r="A22" s="53"/>
       <c r="B22" s="2" t="s">
         <v>60</v>
       </c>
@@ -2415,7 +2409,7 @@
       <c r="U22" s="5"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="56"/>
+      <c r="A23" s="53"/>
       <c r="B23" s="2" t="s">
         <v>61</v>
       </c>
@@ -2442,7 +2436,7 @@
       <c r="U23" s="5"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="56"/>
+      <c r="A24" s="53"/>
       <c r="B24" s="21" t="s">
         <v>62</v>
       </c>
@@ -2487,7 +2481,7 @@
       <c r="U24" s="24"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="52">
+      <c r="A25" s="60">
         <v>4</v>
       </c>
       <c r="B25" s="13" t="s">
@@ -2536,7 +2530,7 @@
       <c r="U25" s="16"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="52"/>
+      <c r="A26" s="60"/>
       <c r="B26" s="13" t="s">
         <v>64</v>
       </c>
@@ -2583,7 +2577,7 @@
       <c r="U26" s="16"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="52"/>
+      <c r="A27" s="60"/>
       <c r="B27" s="13" t="s">
         <v>65</v>
       </c>
@@ -2606,7 +2600,7 @@
         <v>39</v>
       </c>
       <c r="I27" s="16" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="J27" s="13"/>
       <c r="K27" s="15"/>
@@ -2624,9 +2618,9 @@
       <c r="U27" s="16"/>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="52"/>
+      <c r="A28" s="60"/>
       <c r="B28" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C28" s="14" t="s">
         <v>30</v>
@@ -2671,94 +2665,94 @@
       <c r="U28" s="16"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="52"/>
+      <c r="A29" s="60"/>
       <c r="B29" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C29" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="63" t="s">
+      <c r="D29" s="54" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="54"/>
+      <c r="K29" s="54"/>
+      <c r="L29" s="54"/>
+      <c r="M29" s="54"/>
+      <c r="N29" s="54"/>
+      <c r="O29" s="54"/>
+      <c r="P29" s="54"/>
+      <c r="Q29" s="54"/>
+      <c r="R29" s="54"/>
+      <c r="S29" s="54"/>
+      <c r="T29" s="54"/>
+      <c r="U29" s="55"/>
+    </row>
+    <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
+      <c r="A30" s="60"/>
+      <c r="B30" s="26" t="s">
         <v>69</v>
-      </c>
-      <c r="E29" s="63"/>
-      <c r="F29" s="63"/>
-      <c r="G29" s="63"/>
-      <c r="H29" s="63"/>
-      <c r="I29" s="63"/>
-      <c r="J29" s="63"/>
-      <c r="K29" s="63"/>
-      <c r="L29" s="63"/>
-      <c r="M29" s="63"/>
-      <c r="N29" s="63"/>
-      <c r="O29" s="63"/>
-      <c r="P29" s="63"/>
-      <c r="Q29" s="63"/>
-      <c r="R29" s="63"/>
-      <c r="S29" s="63"/>
-      <c r="T29" s="63"/>
-      <c r="U29" s="64"/>
-    </row>
-    <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="52"/>
-      <c r="B30" s="26" t="s">
-        <v>70</v>
       </c>
       <c r="C30" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D30" s="65"/>
-      <c r="E30" s="65"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="65"/>
-      <c r="H30" s="65"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="65"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="65"/>
-      <c r="M30" s="65"/>
-      <c r="N30" s="65"/>
-      <c r="O30" s="65"/>
-      <c r="P30" s="65"/>
-      <c r="Q30" s="65"/>
-      <c r="R30" s="65"/>
-      <c r="S30" s="65"/>
-      <c r="T30" s="65"/>
-      <c r="U30" s="66"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="56"/>
+      <c r="J30" s="56"/>
+      <c r="K30" s="56"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="56"/>
+      <c r="N30" s="56"/>
+      <c r="O30" s="56"/>
+      <c r="P30" s="56"/>
+      <c r="Q30" s="56"/>
+      <c r="R30" s="56"/>
+      <c r="S30" s="56"/>
+      <c r="T30" s="56"/>
+      <c r="U30" s="57"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="52"/>
+      <c r="A31" s="60"/>
       <c r="B31" s="26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C31" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="67"/>
-      <c r="E31" s="67"/>
-      <c r="F31" s="67"/>
-      <c r="G31" s="67"/>
-      <c r="H31" s="67"/>
-      <c r="I31" s="67"/>
-      <c r="J31" s="67"/>
-      <c r="K31" s="67"/>
-      <c r="L31" s="67"/>
-      <c r="M31" s="67"/>
-      <c r="N31" s="67"/>
-      <c r="O31" s="67"/>
-      <c r="P31" s="67"/>
-      <c r="Q31" s="67"/>
-      <c r="R31" s="67"/>
-      <c r="S31" s="67"/>
-      <c r="T31" s="67"/>
-      <c r="U31" s="68"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="58"/>
+      <c r="L31" s="58"/>
+      <c r="M31" s="58"/>
+      <c r="N31" s="58"/>
+      <c r="O31" s="58"/>
+      <c r="P31" s="58"/>
+      <c r="Q31" s="58"/>
+      <c r="R31" s="58"/>
+      <c r="S31" s="58"/>
+      <c r="T31" s="58"/>
+      <c r="U31" s="59"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="56">
+      <c r="A32" s="53">
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>15</v>
@@ -2779,7 +2773,7 @@
         <v>39</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="4"/>
@@ -2797,9 +2791,9 @@
       <c r="U32" s="5"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="56"/>
+      <c r="A33" s="53"/>
       <c r="B33" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>24</v>
@@ -2844,9 +2838,9 @@
       <c r="U33" s="5"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="56"/>
+      <c r="A34" s="53"/>
       <c r="B34" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>27</v>
@@ -2891,202 +2885,202 @@
       <c r="U34" s="5"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="56"/>
+      <c r="A35" s="53"/>
       <c r="B35" s="28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C35" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="63" t="s">
-        <v>69</v>
-      </c>
-      <c r="E35" s="63"/>
-      <c r="F35" s="63"/>
-      <c r="G35" s="63"/>
-      <c r="H35" s="63"/>
-      <c r="I35" s="63"/>
-      <c r="J35" s="63"/>
-      <c r="K35" s="63"/>
-      <c r="L35" s="63"/>
-      <c r="M35" s="63"/>
-      <c r="N35" s="63"/>
-      <c r="O35" s="63"/>
-      <c r="P35" s="63"/>
-      <c r="Q35" s="63"/>
-      <c r="R35" s="63"/>
-      <c r="S35" s="63"/>
-      <c r="T35" s="63"/>
-      <c r="U35" s="64"/>
+      <c r="D35" s="54" t="s">
+        <v>68</v>
+      </c>
+      <c r="E35" s="54"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="54"/>
+      <c r="K35" s="54"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="54"/>
+      <c r="N35" s="54"/>
+      <c r="O35" s="54"/>
+      <c r="P35" s="54"/>
+      <c r="Q35" s="54"/>
+      <c r="R35" s="54"/>
+      <c r="S35" s="54"/>
+      <c r="T35" s="54"/>
+      <c r="U35" s="55"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="56"/>
+      <c r="A36" s="53"/>
       <c r="B36" s="28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C36" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="65"/>
-      <c r="E36" s="65"/>
-      <c r="F36" s="65"/>
-      <c r="G36" s="65"/>
-      <c r="H36" s="65"/>
-      <c r="I36" s="65"/>
-      <c r="J36" s="65"/>
-      <c r="K36" s="65"/>
-      <c r="L36" s="65"/>
-      <c r="M36" s="65"/>
-      <c r="N36" s="65"/>
-      <c r="O36" s="65"/>
-      <c r="P36" s="65"/>
-      <c r="Q36" s="65"/>
-      <c r="R36" s="65"/>
-      <c r="S36" s="65"/>
-      <c r="T36" s="65"/>
-      <c r="U36" s="66"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="56"/>
+      <c r="F36" s="56"/>
+      <c r="G36" s="56"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="56"/>
+      <c r="J36" s="56"/>
+      <c r="K36" s="56"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="56"/>
+      <c r="N36" s="56"/>
+      <c r="O36" s="56"/>
+      <c r="P36" s="56"/>
+      <c r="Q36" s="56"/>
+      <c r="R36" s="56"/>
+      <c r="S36" s="56"/>
+      <c r="T36" s="56"/>
+      <c r="U36" s="57"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="56"/>
+      <c r="A37" s="53"/>
       <c r="B37" s="28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C37" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D37" s="65"/>
-      <c r="E37" s="65"/>
-      <c r="F37" s="65"/>
-      <c r="G37" s="65"/>
-      <c r="H37" s="65"/>
-      <c r="I37" s="65"/>
-      <c r="J37" s="65"/>
-      <c r="K37" s="65"/>
-      <c r="L37" s="65"/>
-      <c r="M37" s="65"/>
-      <c r="N37" s="65"/>
-      <c r="O37" s="65"/>
-      <c r="P37" s="65"/>
-      <c r="Q37" s="65"/>
-      <c r="R37" s="65"/>
-      <c r="S37" s="65"/>
-      <c r="T37" s="65"/>
-      <c r="U37" s="66"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="56"/>
+      <c r="F37" s="56"/>
+      <c r="G37" s="56"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="56"/>
+      <c r="J37" s="56"/>
+      <c r="K37" s="56"/>
+      <c r="L37" s="56"/>
+      <c r="M37" s="56"/>
+      <c r="N37" s="56"/>
+      <c r="O37" s="56"/>
+      <c r="P37" s="56"/>
+      <c r="Q37" s="56"/>
+      <c r="R37" s="56"/>
+      <c r="S37" s="56"/>
+      <c r="T37" s="56"/>
+      <c r="U37" s="57"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="56"/>
+      <c r="A38" s="53"/>
       <c r="B38" s="28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C38" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D38" s="65"/>
-      <c r="E38" s="65"/>
-      <c r="F38" s="65"/>
-      <c r="G38" s="65"/>
-      <c r="H38" s="65"/>
-      <c r="I38" s="65"/>
-      <c r="J38" s="65"/>
-      <c r="K38" s="65"/>
-      <c r="L38" s="65"/>
-      <c r="M38" s="65"/>
-      <c r="N38" s="65"/>
-      <c r="O38" s="65"/>
-      <c r="P38" s="65"/>
-      <c r="Q38" s="65"/>
-      <c r="R38" s="65"/>
-      <c r="S38" s="65"/>
-      <c r="T38" s="65"/>
-      <c r="U38" s="66"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="56"/>
+      <c r="H38" s="56"/>
+      <c r="I38" s="56"/>
+      <c r="J38" s="56"/>
+      <c r="K38" s="56"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="56"/>
+      <c r="N38" s="56"/>
+      <c r="O38" s="56"/>
+      <c r="P38" s="56"/>
+      <c r="Q38" s="56"/>
+      <c r="R38" s="56"/>
+      <c r="S38" s="56"/>
+      <c r="T38" s="56"/>
+      <c r="U38" s="57"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="52">
+      <c r="A39" s="60">
         <v>6</v>
       </c>
       <c r="B39" s="28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C39" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="65"/>
-      <c r="E39" s="65"/>
-      <c r="F39" s="65"/>
-      <c r="G39" s="65"/>
-      <c r="H39" s="65"/>
-      <c r="I39" s="65"/>
-      <c r="J39" s="65"/>
-      <c r="K39" s="65"/>
-      <c r="L39" s="65"/>
-      <c r="M39" s="65"/>
-      <c r="N39" s="65"/>
-      <c r="O39" s="65"/>
-      <c r="P39" s="65"/>
-      <c r="Q39" s="65"/>
-      <c r="R39" s="65"/>
-      <c r="S39" s="65"/>
-      <c r="T39" s="65"/>
-      <c r="U39" s="66"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="56"/>
+      <c r="F39" s="56"/>
+      <c r="G39" s="56"/>
+      <c r="H39" s="56"/>
+      <c r="I39" s="56"/>
+      <c r="J39" s="56"/>
+      <c r="K39" s="56"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="56"/>
+      <c r="N39" s="56"/>
+      <c r="O39" s="56"/>
+      <c r="P39" s="56"/>
+      <c r="Q39" s="56"/>
+      <c r="R39" s="56"/>
+      <c r="S39" s="56"/>
+      <c r="T39" s="56"/>
+      <c r="U39" s="57"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="52"/>
+      <c r="A40" s="60"/>
       <c r="B40" s="28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C40" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="D40" s="65"/>
-      <c r="E40" s="65"/>
-      <c r="F40" s="65"/>
-      <c r="G40" s="65"/>
-      <c r="H40" s="65"/>
-      <c r="I40" s="65"/>
-      <c r="J40" s="65"/>
-      <c r="K40" s="65"/>
-      <c r="L40" s="65"/>
-      <c r="M40" s="65"/>
-      <c r="N40" s="65"/>
-      <c r="O40" s="65"/>
-      <c r="P40" s="65"/>
-      <c r="Q40" s="65"/>
-      <c r="R40" s="65"/>
-      <c r="S40" s="65"/>
-      <c r="T40" s="65"/>
-      <c r="U40" s="66"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="56"/>
+      <c r="K40" s="56"/>
+      <c r="L40" s="56"/>
+      <c r="M40" s="56"/>
+      <c r="N40" s="56"/>
+      <c r="O40" s="56"/>
+      <c r="P40" s="56"/>
+      <c r="Q40" s="56"/>
+      <c r="R40" s="56"/>
+      <c r="S40" s="56"/>
+      <c r="T40" s="56"/>
+      <c r="U40" s="57"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="52"/>
+      <c r="A41" s="60"/>
       <c r="B41" s="28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C41" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="67"/>
-      <c r="H41" s="67"/>
-      <c r="I41" s="67"/>
-      <c r="J41" s="67"/>
-      <c r="K41" s="67"/>
-      <c r="L41" s="67"/>
-      <c r="M41" s="67"/>
-      <c r="N41" s="67"/>
-      <c r="O41" s="67"/>
-      <c r="P41" s="67"/>
-      <c r="Q41" s="67"/>
-      <c r="R41" s="67"/>
-      <c r="S41" s="67"/>
-      <c r="T41" s="67"/>
-      <c r="U41" s="68"/>
+      <c r="D41" s="58"/>
+      <c r="E41" s="58"/>
+      <c r="F41" s="58"/>
+      <c r="G41" s="58"/>
+      <c r="H41" s="58"/>
+      <c r="I41" s="58"/>
+      <c r="J41" s="58"/>
+      <c r="K41" s="58"/>
+      <c r="L41" s="58"/>
+      <c r="M41" s="58"/>
+      <c r="N41" s="58"/>
+      <c r="O41" s="58"/>
+      <c r="P41" s="58"/>
+      <c r="Q41" s="58"/>
+      <c r="R41" s="58"/>
+      <c r="S41" s="58"/>
+      <c r="T41" s="58"/>
+      <c r="U41" s="59"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="52"/>
+      <c r="A42" s="60"/>
       <c r="B42" s="29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C42" s="14" t="s">
         <v>30</v>
@@ -3125,9 +3119,9 @@
       </c>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="52"/>
+      <c r="A43" s="60"/>
       <c r="B43" s="29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C43" s="14" t="s">
         <v>34</v>
@@ -3154,9 +3148,9 @@
       <c r="U43" s="16"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="52"/>
+      <c r="A44" s="60"/>
       <c r="B44" s="30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C44" s="22" t="s">
         <v>37</v>
@@ -3181,9 +3175,9 @@
       <c r="U44" s="24"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="52"/>
+      <c r="A45" s="60"/>
       <c r="B45" s="29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C45" s="14" t="s">
         <v>41</v>
@@ -3208,11 +3202,11 @@
       <c r="U45" s="16"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="56">
+      <c r="A46" s="53">
         <v>7</v>
       </c>
       <c r="B46" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>15</v>
@@ -3257,9 +3251,9 @@
       <c r="U46" s="5"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="56"/>
+      <c r="A47" s="53"/>
       <c r="B47" s="31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>24</v>
@@ -3280,7 +3274,7 @@
         <v>39</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>38</v>
@@ -3289,7 +3283,7 @@
         <v>39</v>
       </c>
       <c r="L47" s="5" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="M47" s="2" t="s">
         <v>19</v>
@@ -3304,9 +3298,9 @@
       <c r="U47" s="5"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="56"/>
+      <c r="A48" s="53"/>
       <c r="B48" s="31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>27</v>
@@ -3351,9 +3345,9 @@
       <c r="U48" s="5"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="56"/>
+      <c r="A49" s="53"/>
       <c r="B49" s="31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>30</v>
@@ -3374,7 +3368,7 @@
         <v>39</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>38</v>
@@ -3383,7 +3377,7 @@
         <v>39</v>
       </c>
       <c r="L49" s="5" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="M49" s="11" t="s">
         <v>19</v>
@@ -3398,9 +3392,9 @@
       <c r="U49" s="5"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="56"/>
+      <c r="A50" s="53"/>
       <c r="B50" s="31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>34</v>
@@ -3445,9 +3439,9 @@
       <c r="U50" s="5"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="56"/>
+      <c r="A51" s="53"/>
       <c r="B51" s="31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>37</v>
@@ -3472,9 +3466,9 @@
       <c r="U51" s="5"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="56"/>
+      <c r="A52" s="53"/>
       <c r="B52" s="31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>41</v>
@@ -3499,11 +3493,11 @@
       <c r="U52" s="5"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="52">
+      <c r="A53" s="60">
         <v>8</v>
       </c>
       <c r="B53" s="29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C53" s="14" t="s">
         <v>15</v>
@@ -3548,9 +3542,9 @@
       <c r="U53" s="16"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="52"/>
+      <c r="A54" s="60"/>
       <c r="B54" s="29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C54" s="14" t="s">
         <v>24</v>
@@ -3589,9 +3583,9 @@
       <c r="U54" s="16"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="52"/>
+      <c r="A55" s="60"/>
       <c r="B55" s="29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C55" s="14" t="s">
         <v>27</v>
@@ -3636,9 +3630,9 @@
       <c r="U55" s="16"/>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="52"/>
+      <c r="A56" s="60"/>
       <c r="B56" s="29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C56" s="14" t="s">
         <v>30</v>
@@ -3689,9 +3683,9 @@
       </c>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="52"/>
+      <c r="A57" s="60"/>
       <c r="B57" s="29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C57" s="14" t="s">
         <v>34</v>
@@ -3736,9 +3730,9 @@
       <c r="U57" s="16"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="52"/>
+      <c r="A58" s="60"/>
       <c r="B58" s="29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C58" s="14" t="s">
         <v>37</v>
@@ -3763,9 +3757,9 @@
       <c r="U58" s="16"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="52"/>
+      <c r="A59" s="60"/>
       <c r="B59" s="29" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C59" s="14" t="s">
         <v>41</v>
@@ -3790,11 +3784,11 @@
       <c r="U59" s="16"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="56">
+      <c r="A60" s="53">
         <v>9</v>
       </c>
       <c r="B60" s="31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>15</v>
@@ -3839,9 +3833,9 @@
       <c r="U60" s="5"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="56"/>
+      <c r="A61" s="53"/>
       <c r="B61" s="31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>24</v>
@@ -3886,9 +3880,9 @@
       <c r="U61" s="5"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="56"/>
+      <c r="A62" s="53"/>
       <c r="B62" s="31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>27</v>
@@ -3918,7 +3912,7 @@
         <v>39</v>
       </c>
       <c r="L62" s="5" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="M62" s="10" t="s">
         <v>19</v>
@@ -3933,9 +3927,9 @@
       <c r="U62" s="5"/>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="56"/>
+      <c r="A63" s="53"/>
       <c r="B63" s="31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>30</v>
@@ -3986,9 +3980,9 @@
       </c>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="56"/>
+      <c r="A64" s="53"/>
       <c r="B64" s="31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>34</v>
@@ -4027,9 +4021,9 @@
       <c r="U64" s="6"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="56"/>
+      <c r="A65" s="53"/>
       <c r="B65" s="31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>37</v>
@@ -4072,9 +4066,9 @@
       <c r="U65" s="6"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="56"/>
+      <c r="A66" s="53"/>
       <c r="B66" s="31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>41</v>
@@ -4099,11 +4093,11 @@
       <c r="U66" s="6"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="52">
+      <c r="A67" s="60">
         <v>10</v>
       </c>
       <c r="B67" s="29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C67" s="14" t="s">
         <v>15</v>
@@ -4148,9 +4142,9 @@
       <c r="U67" s="17"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="52"/>
+      <c r="A68" s="60"/>
       <c r="B68" s="29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C68" s="14" t="s">
         <v>24</v>
@@ -4189,9 +4183,9 @@
       <c r="U68" s="17"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="52"/>
+      <c r="A69" s="60"/>
       <c r="B69" s="29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C69" s="14" t="s">
         <v>27</v>
@@ -4236,9 +4230,9 @@
       <c r="U69" s="17"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="52"/>
+      <c r="A70" s="60"/>
       <c r="B70" s="29" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C70" s="14" t="s">
         <v>30</v>
@@ -4289,9 +4283,9 @@
       </c>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="52"/>
+      <c r="A71" s="60"/>
       <c r="B71" s="29" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C71" s="14" t="s">
         <v>34</v>
@@ -4336,9 +4330,9 @@
       <c r="U71" s="17"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="52"/>
+      <c r="A72" s="60"/>
       <c r="B72" s="29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C72" s="14" t="s">
         <v>37</v>
@@ -4381,9 +4375,9 @@
       <c r="U72" s="17"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="52"/>
+      <c r="A73" s="60"/>
       <c r="B73" s="29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C73" s="14" t="s">
         <v>41</v>
@@ -4408,11 +4402,11 @@
       <c r="U73" s="17"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="56">
+      <c r="A74" s="53">
         <v>11</v>
       </c>
       <c r="B74" s="31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>15</v>
@@ -4451,9 +4445,9 @@
       <c r="U74" s="6"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="56"/>
+      <c r="A75" s="53"/>
       <c r="B75" s="31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>24</v>
@@ -4492,9 +4486,9 @@
       <c r="U75" s="6"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="56"/>
+      <c r="A76" s="53"/>
       <c r="B76" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>27</v>
@@ -4533,9 +4527,9 @@
       <c r="U76" s="6"/>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="56"/>
+      <c r="A77" s="53"/>
       <c r="B77" s="31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>30</v>
@@ -4574,9 +4568,9 @@
       <c r="U77" s="5"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="56"/>
+      <c r="A78" s="53"/>
       <c r="B78" s="31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>34</v>
@@ -4621,9 +4615,9 @@
       <c r="U78" s="5"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="56"/>
+      <c r="A79" s="53"/>
       <c r="B79" s="31" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>37</v>
@@ -4666,9 +4660,9 @@
       <c r="U79" s="5"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="56"/>
+      <c r="A80" s="53"/>
       <c r="B80" s="31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>41</v>
@@ -4693,395 +4687,395 @@
       <c r="U80" s="5"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="52">
+      <c r="A81" s="60">
         <v>12</v>
       </c>
       <c r="B81" s="29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C81" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D81" s="57" t="s">
+      <c r="D81" s="69" t="s">
+        <v>121</v>
+      </c>
+      <c r="E81" s="69"/>
+      <c r="F81" s="69"/>
+      <c r="G81" s="69"/>
+      <c r="H81" s="69"/>
+      <c r="I81" s="69"/>
+      <c r="J81" s="69"/>
+      <c r="K81" s="69"/>
+      <c r="L81" s="69"/>
+      <c r="M81" s="69"/>
+      <c r="N81" s="69"/>
+      <c r="O81" s="69"/>
+      <c r="P81" s="69"/>
+      <c r="Q81" s="69"/>
+      <c r="R81" s="69"/>
+      <c r="S81" s="69"/>
+      <c r="T81" s="69"/>
+      <c r="U81" s="70"/>
+    </row>
+    <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
+      <c r="A82" s="60"/>
+      <c r="B82" s="29" t="s">
         <v>122</v>
-      </c>
-      <c r="E81" s="57"/>
-      <c r="F81" s="57"/>
-      <c r="G81" s="57"/>
-      <c r="H81" s="57"/>
-      <c r="I81" s="57"/>
-      <c r="J81" s="57"/>
-      <c r="K81" s="57"/>
-      <c r="L81" s="57"/>
-      <c r="M81" s="57"/>
-      <c r="N81" s="57"/>
-      <c r="O81" s="57"/>
-      <c r="P81" s="57"/>
-      <c r="Q81" s="57"/>
-      <c r="R81" s="57"/>
-      <c r="S81" s="57"/>
-      <c r="T81" s="57"/>
-      <c r="U81" s="58"/>
-    </row>
-    <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="52"/>
-      <c r="B82" s="29" t="s">
-        <v>123</v>
       </c>
       <c r="C82" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D82" s="59"/>
-      <c r="E82" s="59"/>
-      <c r="F82" s="59"/>
-      <c r="G82" s="59"/>
-      <c r="H82" s="59"/>
-      <c r="I82" s="59"/>
-      <c r="J82" s="59"/>
-      <c r="K82" s="59"/>
-      <c r="L82" s="59"/>
-      <c r="M82" s="59"/>
-      <c r="N82" s="59"/>
-      <c r="O82" s="59"/>
-      <c r="P82" s="59"/>
-      <c r="Q82" s="59"/>
-      <c r="R82" s="59"/>
-      <c r="S82" s="59"/>
-      <c r="T82" s="59"/>
-      <c r="U82" s="60"/>
+      <c r="D82" s="71"/>
+      <c r="E82" s="71"/>
+      <c r="F82" s="71"/>
+      <c r="G82" s="71"/>
+      <c r="H82" s="71"/>
+      <c r="I82" s="71"/>
+      <c r="J82" s="71"/>
+      <c r="K82" s="71"/>
+      <c r="L82" s="71"/>
+      <c r="M82" s="71"/>
+      <c r="N82" s="71"/>
+      <c r="O82" s="71"/>
+      <c r="P82" s="71"/>
+      <c r="Q82" s="71"/>
+      <c r="R82" s="71"/>
+      <c r="S82" s="71"/>
+      <c r="T82" s="71"/>
+      <c r="U82" s="72"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="52"/>
+      <c r="A83" s="60"/>
       <c r="B83" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C83" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D83" s="59"/>
-      <c r="E83" s="59"/>
-      <c r="F83" s="59"/>
-      <c r="G83" s="59"/>
-      <c r="H83" s="59"/>
-      <c r="I83" s="59"/>
-      <c r="J83" s="59"/>
-      <c r="K83" s="59"/>
-      <c r="L83" s="59"/>
-      <c r="M83" s="59"/>
-      <c r="N83" s="59"/>
-      <c r="O83" s="59"/>
-      <c r="P83" s="59"/>
-      <c r="Q83" s="59"/>
-      <c r="R83" s="59"/>
-      <c r="S83" s="59"/>
-      <c r="T83" s="59"/>
-      <c r="U83" s="60"/>
+      <c r="D83" s="71"/>
+      <c r="E83" s="71"/>
+      <c r="F83" s="71"/>
+      <c r="G83" s="71"/>
+      <c r="H83" s="71"/>
+      <c r="I83" s="71"/>
+      <c r="J83" s="71"/>
+      <c r="K83" s="71"/>
+      <c r="L83" s="71"/>
+      <c r="M83" s="71"/>
+      <c r="N83" s="71"/>
+      <c r="O83" s="71"/>
+      <c r="P83" s="71"/>
+      <c r="Q83" s="71"/>
+      <c r="R83" s="71"/>
+      <c r="S83" s="71"/>
+      <c r="T83" s="71"/>
+      <c r="U83" s="72"/>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="52"/>
+      <c r="A84" s="60"/>
       <c r="B84" s="29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C84" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D84" s="59"/>
-      <c r="E84" s="59"/>
-      <c r="F84" s="59"/>
-      <c r="G84" s="59"/>
-      <c r="H84" s="59"/>
-      <c r="I84" s="59"/>
-      <c r="J84" s="59"/>
-      <c r="K84" s="59"/>
-      <c r="L84" s="59"/>
-      <c r="M84" s="59"/>
-      <c r="N84" s="59"/>
-      <c r="O84" s="59"/>
-      <c r="P84" s="59"/>
-      <c r="Q84" s="59"/>
-      <c r="R84" s="59"/>
-      <c r="S84" s="59"/>
-      <c r="T84" s="59"/>
-      <c r="U84" s="60"/>
+      <c r="D84" s="71"/>
+      <c r="E84" s="71"/>
+      <c r="F84" s="71"/>
+      <c r="G84" s="71"/>
+      <c r="H84" s="71"/>
+      <c r="I84" s="71"/>
+      <c r="J84" s="71"/>
+      <c r="K84" s="71"/>
+      <c r="L84" s="71"/>
+      <c r="M84" s="71"/>
+      <c r="N84" s="71"/>
+      <c r="O84" s="71"/>
+      <c r="P84" s="71"/>
+      <c r="Q84" s="71"/>
+      <c r="R84" s="71"/>
+      <c r="S84" s="71"/>
+      <c r="T84" s="71"/>
+      <c r="U84" s="72"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="52"/>
+      <c r="A85" s="60"/>
       <c r="B85" s="29" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C85" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D85" s="59"/>
-      <c r="E85" s="59"/>
-      <c r="F85" s="59"/>
-      <c r="G85" s="59"/>
-      <c r="H85" s="59"/>
-      <c r="I85" s="59"/>
-      <c r="J85" s="59"/>
-      <c r="K85" s="59"/>
-      <c r="L85" s="59"/>
-      <c r="M85" s="59"/>
-      <c r="N85" s="59"/>
-      <c r="O85" s="59"/>
-      <c r="P85" s="59"/>
-      <c r="Q85" s="59"/>
-      <c r="R85" s="59"/>
-      <c r="S85" s="59"/>
-      <c r="T85" s="59"/>
-      <c r="U85" s="60"/>
+      <c r="D85" s="71"/>
+      <c r="E85" s="71"/>
+      <c r="F85" s="71"/>
+      <c r="G85" s="71"/>
+      <c r="H85" s="71"/>
+      <c r="I85" s="71"/>
+      <c r="J85" s="71"/>
+      <c r="K85" s="71"/>
+      <c r="L85" s="71"/>
+      <c r="M85" s="71"/>
+      <c r="N85" s="71"/>
+      <c r="O85" s="71"/>
+      <c r="P85" s="71"/>
+      <c r="Q85" s="71"/>
+      <c r="R85" s="71"/>
+      <c r="S85" s="71"/>
+      <c r="T85" s="71"/>
+      <c r="U85" s="72"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="52"/>
+      <c r="A86" s="60"/>
       <c r="B86" s="29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C86" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D86" s="59"/>
-      <c r="E86" s="59"/>
-      <c r="F86" s="59"/>
-      <c r="G86" s="59"/>
-      <c r="H86" s="59"/>
-      <c r="I86" s="59"/>
-      <c r="J86" s="59"/>
-      <c r="K86" s="59"/>
-      <c r="L86" s="59"/>
-      <c r="M86" s="59"/>
-      <c r="N86" s="59"/>
-      <c r="O86" s="59"/>
-      <c r="P86" s="59"/>
-      <c r="Q86" s="59"/>
-      <c r="R86" s="59"/>
-      <c r="S86" s="59"/>
-      <c r="T86" s="59"/>
-      <c r="U86" s="60"/>
+      <c r="D86" s="71"/>
+      <c r="E86" s="71"/>
+      <c r="F86" s="71"/>
+      <c r="G86" s="71"/>
+      <c r="H86" s="71"/>
+      <c r="I86" s="71"/>
+      <c r="J86" s="71"/>
+      <c r="K86" s="71"/>
+      <c r="L86" s="71"/>
+      <c r="M86" s="71"/>
+      <c r="N86" s="71"/>
+      <c r="O86" s="71"/>
+      <c r="P86" s="71"/>
+      <c r="Q86" s="71"/>
+      <c r="R86" s="71"/>
+      <c r="S86" s="71"/>
+      <c r="T86" s="71"/>
+      <c r="U86" s="72"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="52"/>
+      <c r="A87" s="60"/>
       <c r="B87" s="29" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C87" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D87" s="59"/>
-      <c r="E87" s="59"/>
-      <c r="F87" s="59"/>
-      <c r="G87" s="59"/>
-      <c r="H87" s="59"/>
-      <c r="I87" s="59"/>
-      <c r="J87" s="59"/>
-      <c r="K87" s="59"/>
-      <c r="L87" s="59"/>
-      <c r="M87" s="59"/>
-      <c r="N87" s="59"/>
-      <c r="O87" s="59"/>
-      <c r="P87" s="59"/>
-      <c r="Q87" s="59"/>
-      <c r="R87" s="59"/>
-      <c r="S87" s="59"/>
-      <c r="T87" s="59"/>
-      <c r="U87" s="60"/>
+      <c r="D87" s="71"/>
+      <c r="E87" s="71"/>
+      <c r="F87" s="71"/>
+      <c r="G87" s="71"/>
+      <c r="H87" s="71"/>
+      <c r="I87" s="71"/>
+      <c r="J87" s="71"/>
+      <c r="K87" s="71"/>
+      <c r="L87" s="71"/>
+      <c r="M87" s="71"/>
+      <c r="N87" s="71"/>
+      <c r="O87" s="71"/>
+      <c r="P87" s="71"/>
+      <c r="Q87" s="71"/>
+      <c r="R87" s="71"/>
+      <c r="S87" s="71"/>
+      <c r="T87" s="71"/>
+      <c r="U87" s="72"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="56">
+      <c r="A88" s="53">
         <v>13</v>
       </c>
       <c r="B88" s="31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D88" s="59"/>
-      <c r="E88" s="59"/>
-      <c r="F88" s="59"/>
-      <c r="G88" s="59"/>
-      <c r="H88" s="59"/>
-      <c r="I88" s="59"/>
-      <c r="J88" s="59"/>
-      <c r="K88" s="59"/>
-      <c r="L88" s="59"/>
-      <c r="M88" s="59"/>
-      <c r="N88" s="59"/>
-      <c r="O88" s="59"/>
-      <c r="P88" s="59"/>
-      <c r="Q88" s="59"/>
-      <c r="R88" s="59"/>
-      <c r="S88" s="59"/>
-      <c r="T88" s="59"/>
-      <c r="U88" s="60"/>
+      <c r="D88" s="71"/>
+      <c r="E88" s="71"/>
+      <c r="F88" s="71"/>
+      <c r="G88" s="71"/>
+      <c r="H88" s="71"/>
+      <c r="I88" s="71"/>
+      <c r="J88" s="71"/>
+      <c r="K88" s="71"/>
+      <c r="L88" s="71"/>
+      <c r="M88" s="71"/>
+      <c r="N88" s="71"/>
+      <c r="O88" s="71"/>
+      <c r="P88" s="71"/>
+      <c r="Q88" s="71"/>
+      <c r="R88" s="71"/>
+      <c r="S88" s="71"/>
+      <c r="T88" s="71"/>
+      <c r="U88" s="72"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="56"/>
+      <c r="A89" s="53"/>
       <c r="B89" s="31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D89" s="59"/>
-      <c r="E89" s="59"/>
-      <c r="F89" s="59"/>
-      <c r="G89" s="59"/>
-      <c r="H89" s="59"/>
-      <c r="I89" s="59"/>
-      <c r="J89" s="59"/>
-      <c r="K89" s="59"/>
-      <c r="L89" s="59"/>
-      <c r="M89" s="59"/>
-      <c r="N89" s="59"/>
-      <c r="O89" s="59"/>
-      <c r="P89" s="59"/>
-      <c r="Q89" s="59"/>
-      <c r="R89" s="59"/>
-      <c r="S89" s="59"/>
-      <c r="T89" s="59"/>
-      <c r="U89" s="60"/>
+      <c r="D89" s="71"/>
+      <c r="E89" s="71"/>
+      <c r="F89" s="71"/>
+      <c r="G89" s="71"/>
+      <c r="H89" s="71"/>
+      <c r="I89" s="71"/>
+      <c r="J89" s="71"/>
+      <c r="K89" s="71"/>
+      <c r="L89" s="71"/>
+      <c r="M89" s="71"/>
+      <c r="N89" s="71"/>
+      <c r="O89" s="71"/>
+      <c r="P89" s="71"/>
+      <c r="Q89" s="71"/>
+      <c r="R89" s="71"/>
+      <c r="S89" s="71"/>
+      <c r="T89" s="71"/>
+      <c r="U89" s="72"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="56"/>
+      <c r="A90" s="53"/>
       <c r="B90" s="31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D90" s="59"/>
-      <c r="E90" s="59"/>
-      <c r="F90" s="59"/>
-      <c r="G90" s="59"/>
-      <c r="H90" s="59"/>
-      <c r="I90" s="59"/>
-      <c r="J90" s="59"/>
-      <c r="K90" s="59"/>
-      <c r="L90" s="59"/>
-      <c r="M90" s="59"/>
-      <c r="N90" s="59"/>
-      <c r="O90" s="59"/>
-      <c r="P90" s="59"/>
-      <c r="Q90" s="59"/>
-      <c r="R90" s="59"/>
-      <c r="S90" s="59"/>
-      <c r="T90" s="59"/>
-      <c r="U90" s="60"/>
+      <c r="D90" s="71"/>
+      <c r="E90" s="71"/>
+      <c r="F90" s="71"/>
+      <c r="G90" s="71"/>
+      <c r="H90" s="71"/>
+      <c r="I90" s="71"/>
+      <c r="J90" s="71"/>
+      <c r="K90" s="71"/>
+      <c r="L90" s="71"/>
+      <c r="M90" s="71"/>
+      <c r="N90" s="71"/>
+      <c r="O90" s="71"/>
+      <c r="P90" s="71"/>
+      <c r="Q90" s="71"/>
+      <c r="R90" s="71"/>
+      <c r="S90" s="71"/>
+      <c r="T90" s="71"/>
+      <c r="U90" s="72"/>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="56"/>
+      <c r="A91" s="53"/>
       <c r="B91" s="31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D91" s="59"/>
-      <c r="E91" s="59"/>
-      <c r="F91" s="59"/>
-      <c r="G91" s="59"/>
-      <c r="H91" s="59"/>
-      <c r="I91" s="59"/>
-      <c r="J91" s="59"/>
-      <c r="K91" s="59"/>
-      <c r="L91" s="59"/>
-      <c r="M91" s="59"/>
-      <c r="N91" s="59"/>
-      <c r="O91" s="59"/>
-      <c r="P91" s="59"/>
-      <c r="Q91" s="59"/>
-      <c r="R91" s="59"/>
-      <c r="S91" s="59"/>
-      <c r="T91" s="59"/>
-      <c r="U91" s="60"/>
+      <c r="D91" s="71"/>
+      <c r="E91" s="71"/>
+      <c r="F91" s="71"/>
+      <c r="G91" s="71"/>
+      <c r="H91" s="71"/>
+      <c r="I91" s="71"/>
+      <c r="J91" s="71"/>
+      <c r="K91" s="71"/>
+      <c r="L91" s="71"/>
+      <c r="M91" s="71"/>
+      <c r="N91" s="71"/>
+      <c r="O91" s="71"/>
+      <c r="P91" s="71"/>
+      <c r="Q91" s="71"/>
+      <c r="R91" s="71"/>
+      <c r="S91" s="71"/>
+      <c r="T91" s="71"/>
+      <c r="U91" s="72"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="56"/>
+      <c r="A92" s="53"/>
       <c r="B92" s="31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D92" s="59"/>
-      <c r="E92" s="59"/>
-      <c r="F92" s="59"/>
-      <c r="G92" s="59"/>
-      <c r="H92" s="59"/>
-      <c r="I92" s="59"/>
-      <c r="J92" s="59"/>
-      <c r="K92" s="59"/>
-      <c r="L92" s="59"/>
-      <c r="M92" s="59"/>
-      <c r="N92" s="59"/>
-      <c r="O92" s="59"/>
-      <c r="P92" s="59"/>
-      <c r="Q92" s="59"/>
-      <c r="R92" s="59"/>
-      <c r="S92" s="59"/>
-      <c r="T92" s="59"/>
-      <c r="U92" s="60"/>
+      <c r="D92" s="71"/>
+      <c r="E92" s="71"/>
+      <c r="F92" s="71"/>
+      <c r="G92" s="71"/>
+      <c r="H92" s="71"/>
+      <c r="I92" s="71"/>
+      <c r="J92" s="71"/>
+      <c r="K92" s="71"/>
+      <c r="L92" s="71"/>
+      <c r="M92" s="71"/>
+      <c r="N92" s="71"/>
+      <c r="O92" s="71"/>
+      <c r="P92" s="71"/>
+      <c r="Q92" s="71"/>
+      <c r="R92" s="71"/>
+      <c r="S92" s="71"/>
+      <c r="T92" s="71"/>
+      <c r="U92" s="72"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="56"/>
+      <c r="A93" s="53"/>
       <c r="B93" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D93" s="59"/>
-      <c r="E93" s="59"/>
-      <c r="F93" s="59"/>
-      <c r="G93" s="59"/>
-      <c r="H93" s="59"/>
-      <c r="I93" s="59"/>
-      <c r="J93" s="59"/>
-      <c r="K93" s="59"/>
-      <c r="L93" s="59"/>
-      <c r="M93" s="59"/>
-      <c r="N93" s="59"/>
-      <c r="O93" s="59"/>
-      <c r="P93" s="59"/>
-      <c r="Q93" s="59"/>
-      <c r="R93" s="59"/>
-      <c r="S93" s="59"/>
-      <c r="T93" s="59"/>
-      <c r="U93" s="60"/>
+      <c r="D93" s="71"/>
+      <c r="E93" s="71"/>
+      <c r="F93" s="71"/>
+      <c r="G93" s="71"/>
+      <c r="H93" s="71"/>
+      <c r="I93" s="71"/>
+      <c r="J93" s="71"/>
+      <c r="K93" s="71"/>
+      <c r="L93" s="71"/>
+      <c r="M93" s="71"/>
+      <c r="N93" s="71"/>
+      <c r="O93" s="71"/>
+      <c r="P93" s="71"/>
+      <c r="Q93" s="71"/>
+      <c r="R93" s="71"/>
+      <c r="S93" s="71"/>
+      <c r="T93" s="71"/>
+      <c r="U93" s="72"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="56"/>
+      <c r="A94" s="53"/>
       <c r="B94" s="31" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D94" s="61"/>
-      <c r="E94" s="61"/>
-      <c r="F94" s="61"/>
-      <c r="G94" s="61"/>
-      <c r="H94" s="61"/>
-      <c r="I94" s="61"/>
-      <c r="J94" s="61"/>
-      <c r="K94" s="61"/>
-      <c r="L94" s="61"/>
-      <c r="M94" s="61"/>
-      <c r="N94" s="61"/>
-      <c r="O94" s="61"/>
-      <c r="P94" s="61"/>
-      <c r="Q94" s="61"/>
-      <c r="R94" s="61"/>
-      <c r="S94" s="61"/>
-      <c r="T94" s="61"/>
-      <c r="U94" s="62"/>
+      <c r="D94" s="73"/>
+      <c r="E94" s="73"/>
+      <c r="F94" s="73"/>
+      <c r="G94" s="73"/>
+      <c r="H94" s="73"/>
+      <c r="I94" s="73"/>
+      <c r="J94" s="73"/>
+      <c r="K94" s="73"/>
+      <c r="L94" s="73"/>
+      <c r="M94" s="73"/>
+      <c r="N94" s="73"/>
+      <c r="O94" s="73"/>
+      <c r="P94" s="73"/>
+      <c r="Q94" s="73"/>
+      <c r="R94" s="73"/>
+      <c r="S94" s="73"/>
+      <c r="T94" s="73"/>
+      <c r="U94" s="74"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="52">
+      <c r="A95" s="60">
         <v>14</v>
       </c>
       <c r="B95" s="29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C95" s="14" t="s">
         <v>15</v>
@@ -5103,16 +5097,16 @@
       </c>
       <c r="Q95" s="32"/>
       <c r="R95" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S95" s="13"/>
       <c r="T95" s="15"/>
       <c r="U95" s="16"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="52"/>
+      <c r="A96" s="60"/>
       <c r="B96" s="29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C96" s="14" t="s">
         <v>24</v>
@@ -5134,16 +5128,16 @@
       </c>
       <c r="Q96" s="32"/>
       <c r="R96" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S96" s="13"/>
       <c r="T96" s="15"/>
       <c r="U96" s="16"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="52"/>
+      <c r="A97" s="60"/>
       <c r="B97" s="29" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C97" s="14" t="s">
         <v>27</v>
@@ -5165,16 +5159,16 @@
       </c>
       <c r="Q97" s="32"/>
       <c r="R97" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S97" s="13"/>
       <c r="T97" s="15"/>
       <c r="U97" s="16"/>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="52"/>
+      <c r="A98" s="60"/>
       <c r="B98" s="29" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C98" s="14" t="s">
         <v>30</v>
@@ -5196,16 +5190,16 @@
       </c>
       <c r="Q98" s="32"/>
       <c r="R98" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S98" s="13"/>
       <c r="T98" s="15"/>
       <c r="U98" s="16"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="52"/>
+      <c r="A99" s="60"/>
       <c r="B99" s="29" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C99" s="14" t="s">
         <v>34</v>
@@ -5227,16 +5221,16 @@
       </c>
       <c r="Q99" s="32"/>
       <c r="R99" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S99" s="13"/>
       <c r="T99" s="15"/>
       <c r="U99" s="16"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="52"/>
+      <c r="A100" s="60"/>
       <c r="B100" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C100" s="14" t="s">
         <v>37</v>
@@ -5258,16 +5252,16 @@
       </c>
       <c r="Q100" s="32"/>
       <c r="R100" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S100" s="13"/>
       <c r="T100" s="15"/>
       <c r="U100" s="16"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="52"/>
+      <c r="A101" s="60"/>
       <c r="B101" s="29" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C101" s="14" t="s">
         <v>41</v>
@@ -5289,18 +5283,18 @@
       </c>
       <c r="Q101" s="32"/>
       <c r="R101" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S101" s="13"/>
       <c r="T101" s="15"/>
       <c r="U101" s="16"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="56">
+      <c r="A102" s="53">
         <v>15</v>
       </c>
       <c r="B102" s="31" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>15</v>
@@ -5322,16 +5316,16 @@
       </c>
       <c r="Q102" s="35"/>
       <c r="R102" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S102" s="2"/>
       <c r="T102" s="4"/>
       <c r="U102" s="5"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="56"/>
+      <c r="A103" s="53"/>
       <c r="B103" s="31" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>24</v>
@@ -5353,16 +5347,16 @@
       </c>
       <c r="Q103" s="35"/>
       <c r="R103" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S103" s="2"/>
       <c r="T103" s="4"/>
       <c r="U103" s="5"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="56"/>
+      <c r="A104" s="53"/>
       <c r="B104" s="31" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>27</v>
@@ -5384,16 +5378,16 @@
       </c>
       <c r="Q104" s="35"/>
       <c r="R104" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S104" s="2"/>
       <c r="T104" s="4"/>
       <c r="U104" s="5"/>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="56"/>
+      <c r="A105" s="53"/>
       <c r="B105" s="31" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>30</v>
@@ -5415,16 +5409,16 @@
       </c>
       <c r="Q105" s="35"/>
       <c r="R105" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S105" s="2"/>
       <c r="T105" s="4"/>
       <c r="U105" s="5"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="56"/>
+      <c r="A106" s="53"/>
       <c r="B106" s="31" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>34</v>
@@ -5446,16 +5440,16 @@
       </c>
       <c r="Q106" s="35"/>
       <c r="R106" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S106" s="2"/>
       <c r="T106" s="4"/>
       <c r="U106" s="5"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="56"/>
+      <c r="A107" s="53"/>
       <c r="B107" s="31" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>37</v>
@@ -5477,16 +5471,16 @@
       </c>
       <c r="Q107" s="35"/>
       <c r="R107" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S107" s="2"/>
       <c r="T107" s="4"/>
       <c r="U107" s="5"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="56"/>
+      <c r="A108" s="53"/>
       <c r="B108" s="31" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>41</v>
@@ -5508,18 +5502,18 @@
       </c>
       <c r="Q108" s="35"/>
       <c r="R108" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S108" s="2"/>
       <c r="T108" s="4"/>
       <c r="U108" s="5"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="52">
+      <c r="A109" s="60">
         <v>16</v>
       </c>
       <c r="B109" s="29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C109" s="14" t="s">
         <v>15</v>
@@ -5541,16 +5535,16 @@
       </c>
       <c r="Q109" s="32"/>
       <c r="R109" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S109" s="13"/>
       <c r="T109" s="15"/>
       <c r="U109" s="17"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="52"/>
+      <c r="A110" s="60"/>
       <c r="B110" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C110" s="14" t="s">
         <v>24</v>
@@ -5572,16 +5566,16 @@
       </c>
       <c r="Q110" s="32"/>
       <c r="R110" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S110" s="13"/>
       <c r="T110" s="15"/>
       <c r="U110" s="17"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="52"/>
+      <c r="A111" s="60"/>
       <c r="B111" s="29" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C111" s="14" t="s">
         <v>27</v>
@@ -5603,16 +5597,16 @@
       </c>
       <c r="Q111" s="32"/>
       <c r="R111" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S111" s="13"/>
       <c r="T111" s="15"/>
       <c r="U111" s="17"/>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="52"/>
+      <c r="A112" s="60"/>
       <c r="B112" s="29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C112" s="14" t="s">
         <v>30</v>
@@ -5634,16 +5628,16 @@
       </c>
       <c r="Q112" s="32"/>
       <c r="R112" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S112" s="13"/>
       <c r="T112" s="15"/>
       <c r="U112" s="17"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="52"/>
+      <c r="A113" s="60"/>
       <c r="B113" s="29" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C113" s="14" t="s">
         <v>34</v>
@@ -5665,16 +5659,16 @@
       </c>
       <c r="Q113" s="32"/>
       <c r="R113" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S113" s="13"/>
       <c r="T113" s="15"/>
       <c r="U113" s="17"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="52"/>
+      <c r="A114" s="60"/>
       <c r="B114" s="29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C114" s="14" t="s">
         <v>37</v>
@@ -5696,16 +5690,16 @@
       </c>
       <c r="Q114" s="32"/>
       <c r="R114" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S114" s="13"/>
       <c r="T114" s="15"/>
       <c r="U114" s="17"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="52"/>
+      <c r="A115" s="60"/>
       <c r="B115" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C115" s="14" t="s">
         <v>41</v>
@@ -5727,18 +5721,18 @@
       </c>
       <c r="Q115" s="32"/>
       <c r="R115" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S115" s="13"/>
       <c r="T115" s="15"/>
       <c r="U115" s="17"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="56">
+      <c r="A116" s="53">
         <v>17</v>
       </c>
       <c r="B116" s="31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>15</v>
@@ -5760,16 +5754,16 @@
       </c>
       <c r="Q116" s="35"/>
       <c r="R116" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S116" s="2"/>
       <c r="T116" s="4"/>
       <c r="U116" s="5"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="56"/>
+      <c r="A117" s="53"/>
       <c r="B117" s="31" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>24</v>
@@ -5791,16 +5785,16 @@
       </c>
       <c r="Q117" s="35"/>
       <c r="R117" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S117" s="2"/>
       <c r="T117" s="4"/>
       <c r="U117" s="5"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="56"/>
+      <c r="A118" s="53"/>
       <c r="B118" s="31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>27</v>
@@ -5822,16 +5816,16 @@
       </c>
       <c r="Q118" s="35"/>
       <c r="R118" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S118" s="2"/>
       <c r="T118" s="4"/>
       <c r="U118" s="5"/>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="56"/>
+      <c r="A119" s="53"/>
       <c r="B119" s="31" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>30</v>
@@ -5853,16 +5847,16 @@
       </c>
       <c r="Q119" s="35"/>
       <c r="R119" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S119" s="2"/>
       <c r="T119" s="4"/>
       <c r="U119" s="5"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="56"/>
+      <c r="A120" s="53"/>
       <c r="B120" s="31" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>34</v>
@@ -5884,16 +5878,16 @@
       </c>
       <c r="Q120" s="35"/>
       <c r="R120" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S120" s="2"/>
       <c r="T120" s="4"/>
       <c r="U120" s="5"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="56"/>
+      <c r="A121" s="53"/>
       <c r="B121" s="31" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>37</v>
@@ -5915,16 +5909,16 @@
       </c>
       <c r="Q121" s="35"/>
       <c r="R121" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S121" s="2"/>
       <c r="T121" s="4"/>
       <c r="U121" s="5"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="56"/>
+      <c r="A122" s="53"/>
       <c r="B122" s="31" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>41</v>
@@ -5946,18 +5940,18 @@
       </c>
       <c r="Q122" s="35"/>
       <c r="R122" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S122" s="2"/>
       <c r="T122" s="4"/>
       <c r="U122" s="5"/>
     </row>
     <row r="123" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="52">
+      <c r="A123" s="60">
         <v>18</v>
       </c>
       <c r="B123" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C123" s="14" t="s">
         <v>15</v>
@@ -5979,16 +5973,16 @@
       </c>
       <c r="Q123" s="32"/>
       <c r="R123" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S123" s="13"/>
       <c r="T123" s="15"/>
       <c r="U123" s="17"/>
     </row>
     <row r="124" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="52"/>
+      <c r="A124" s="60"/>
       <c r="B124" s="29" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C124" s="14" t="s">
         <v>24</v>
@@ -6010,16 +6004,16 @@
       </c>
       <c r="Q124" s="32"/>
       <c r="R124" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S124" s="13"/>
       <c r="T124" s="15"/>
       <c r="U124" s="17"/>
     </row>
     <row r="125" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="52"/>
+      <c r="A125" s="60"/>
       <c r="B125" s="29" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C125" s="14" t="s">
         <v>27</v>
@@ -6041,16 +6035,16 @@
       </c>
       <c r="Q125" s="32"/>
       <c r="R125" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S125" s="13"/>
       <c r="T125" s="15"/>
       <c r="U125" s="17"/>
     </row>
     <row r="126" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="52"/>
+      <c r="A126" s="60"/>
       <c r="B126" s="29" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C126" s="14" t="s">
         <v>30</v>
@@ -6072,45 +6066,45 @@
       </c>
       <c r="Q126" s="32"/>
       <c r="R126" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S126" s="13"/>
       <c r="T126" s="15"/>
       <c r="U126" s="17"/>
     </row>
     <row r="127" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="52"/>
+      <c r="A127" s="60"/>
       <c r="B127" s="28" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C127" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D127" s="54" t="s">
-        <v>69</v>
-      </c>
-      <c r="E127" s="54"/>
-      <c r="F127" s="54"/>
-      <c r="G127" s="54"/>
-      <c r="H127" s="54"/>
-      <c r="I127" s="54"/>
-      <c r="J127" s="54"/>
-      <c r="K127" s="54"/>
-      <c r="L127" s="54"/>
-      <c r="M127" s="54"/>
-      <c r="N127" s="54"/>
-      <c r="O127" s="54"/>
-      <c r="P127" s="54"/>
-      <c r="Q127" s="54"/>
-      <c r="R127" s="54"/>
-      <c r="S127" s="54"/>
-      <c r="T127" s="54"/>
-      <c r="U127" s="55"/>
+      <c r="D127" s="67" t="s">
+        <v>68</v>
+      </c>
+      <c r="E127" s="67"/>
+      <c r="F127" s="67"/>
+      <c r="G127" s="67"/>
+      <c r="H127" s="67"/>
+      <c r="I127" s="67"/>
+      <c r="J127" s="67"/>
+      <c r="K127" s="67"/>
+      <c r="L127" s="67"/>
+      <c r="M127" s="67"/>
+      <c r="N127" s="67"/>
+      <c r="O127" s="67"/>
+      <c r="P127" s="67"/>
+      <c r="Q127" s="67"/>
+      <c r="R127" s="67"/>
+      <c r="S127" s="67"/>
+      <c r="T127" s="67"/>
+      <c r="U127" s="68"/>
     </row>
     <row r="128" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="52"/>
+      <c r="A128" s="60"/>
       <c r="B128" s="29" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C128" s="14" t="s">
         <v>37</v>
@@ -6132,16 +6126,16 @@
       </c>
       <c r="Q128" s="32"/>
       <c r="R128" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S128" s="13"/>
       <c r="T128" s="15"/>
       <c r="U128" s="17"/>
     </row>
     <row r="129" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="52"/>
+      <c r="A129" s="60"/>
       <c r="B129" s="29" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C129" s="14" t="s">
         <v>41</v>
@@ -6163,18 +6157,18 @@
       </c>
       <c r="Q129" s="32"/>
       <c r="R129" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S129" s="13"/>
       <c r="T129" s="15"/>
       <c r="U129" s="17"/>
     </row>
     <row r="130" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="56">
+      <c r="A130" s="53">
         <v>19</v>
       </c>
       <c r="B130" s="31" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C130" s="3" t="s">
         <v>15</v>
@@ -6196,16 +6190,16 @@
       </c>
       <c r="Q130" s="35"/>
       <c r="R130" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S130" s="2"/>
       <c r="T130" s="4"/>
       <c r="U130" s="5"/>
     </row>
     <row r="131" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="56"/>
+      <c r="A131" s="53"/>
       <c r="B131" s="31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>24</v>
@@ -6227,16 +6221,16 @@
       </c>
       <c r="Q131" s="35"/>
       <c r="R131" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S131" s="2"/>
       <c r="T131" s="4"/>
       <c r="U131" s="5"/>
     </row>
     <row r="132" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="56"/>
+      <c r="A132" s="53"/>
       <c r="B132" s="31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>27</v>
@@ -6258,16 +6252,16 @@
       </c>
       <c r="Q132" s="35"/>
       <c r="R132" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S132" s="2"/>
       <c r="T132" s="4"/>
       <c r="U132" s="5"/>
     </row>
     <row r="133" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="56"/>
+      <c r="A133" s="53"/>
       <c r="B133" s="31" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>30</v>
@@ -6289,16 +6283,16 @@
       </c>
       <c r="Q133" s="35"/>
       <c r="R133" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S133" s="2"/>
       <c r="T133" s="4"/>
       <c r="U133" s="5"/>
     </row>
     <row r="134" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="56"/>
+      <c r="A134" s="53"/>
       <c r="B134" s="31" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>34</v>
@@ -6320,16 +6314,16 @@
       </c>
       <c r="Q134" s="35"/>
       <c r="R134" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S134" s="2"/>
       <c r="T134" s="4"/>
       <c r="U134" s="5"/>
     </row>
     <row r="135" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="56"/>
+      <c r="A135" s="53"/>
       <c r="B135" s="31" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>37</v>
@@ -6351,16 +6345,16 @@
       </c>
       <c r="Q135" s="35"/>
       <c r="R135" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S135" s="2"/>
       <c r="T135" s="4"/>
       <c r="U135" s="5"/>
     </row>
     <row r="136" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="56"/>
+      <c r="A136" s="53"/>
       <c r="B136" s="31" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>41</v>
@@ -6382,7 +6376,7 @@
       </c>
       <c r="Q136" s="35"/>
       <c r="R136" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S136" s="2"/>
       <c r="T136" s="4"/>
@@ -6404,6 +6398,27 @@
     <row r="150" ht="20.25"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A123:A129"/>
+    <mergeCell ref="D127:U127"/>
+    <mergeCell ref="A130:A136"/>
+    <mergeCell ref="D81:U94"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A101"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="A116:A122"/>
+    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="A74:A80"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="D29:U31"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="A32:A38"/>
     <mergeCell ref="D35:U41"/>
@@ -6420,27 +6435,6 @@
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="D29:U31"/>
-    <mergeCell ref="A46:A52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
-    <mergeCell ref="A123:A129"/>
-    <mergeCell ref="D127:U127"/>
-    <mergeCell ref="A130:A136"/>
-    <mergeCell ref="D81:U94"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="A116:A122"/>
-    <mergeCell ref="A81:A87"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6483,81 +6477,81 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="69" t="s">
+      <c r="C2" s="63"/>
+      <c r="D2" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69" t="s">
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69" t="s">
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69" t="s">
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69" t="s">
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69" t="s">
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="69"/>
-      <c r="U2" s="69"/>
+      <c r="T2" s="52"/>
+      <c r="U2" s="52"/>
     </row>
     <row r="3" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="69"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="70" t="s">
+      <c r="A3" s="52"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="69" t="s">
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="69" t="s">
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="69"/>
-      <c r="L3" s="69"/>
-      <c r="M3" s="69" t="s">
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="69"/>
-      <c r="O3" s="69"/>
-      <c r="P3" s="69" t="s">
+      <c r="N3" s="52"/>
+      <c r="O3" s="52"/>
+      <c r="P3" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="69"/>
-      <c r="R3" s="69"/>
-      <c r="S3" s="69" t="s">
+      <c r="Q3" s="52"/>
+      <c r="R3" s="52"/>
+      <c r="S3" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="69"/>
-      <c r="U3" s="69"/>
+      <c r="T3" s="52"/>
+      <c r="U3" s="52"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="56">
+      <c r="A4" s="53">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -6615,7 +6609,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="56"/>
+      <c r="A5" s="53"/>
       <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
@@ -6673,7 +6667,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="56"/>
+      <c r="A6" s="53"/>
       <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
@@ -6729,7 +6723,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="56"/>
+      <c r="A7" s="53"/>
       <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
@@ -6787,7 +6781,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="56"/>
+      <c r="A8" s="53"/>
       <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
@@ -6849,7 +6843,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="56"/>
+      <c r="A9" s="53"/>
       <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
@@ -6893,7 +6887,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="56"/>
+      <c r="A10" s="53"/>
       <c r="B10" s="2" t="s">
         <v>40</v>
       </c>
@@ -6935,7 +6929,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="52">
+      <c r="A11" s="60">
         <v>2</v>
       </c>
       <c r="B11" s="13" t="s">
@@ -6983,7 +6977,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="52"/>
+      <c r="A12" s="60"/>
       <c r="B12" s="13" t="s">
         <v>46</v>
       </c>
@@ -7027,7 +7021,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="52"/>
+      <c r="A13" s="60"/>
       <c r="B13" s="13" t="s">
         <v>48</v>
       </c>
@@ -7071,7 +7065,7 @@
       </c>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="52"/>
+      <c r="A14" s="60"/>
       <c r="B14" s="13" t="s">
         <v>49</v>
       </c>
@@ -7117,7 +7111,7 @@
       <c r="AA14" s="3"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="52"/>
+      <c r="A15" s="60"/>
       <c r="B15" s="13" t="s">
         <v>53</v>
       </c>
@@ -7151,7 +7145,7 @@
       <c r="AA15" s="3"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="52"/>
+      <c r="A16" s="60"/>
       <c r="B16" s="13" t="s">
         <v>54</v>
       </c>
@@ -7183,7 +7177,7 @@
       <c r="AA16" s="3"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="52"/>
+      <c r="A17" s="60"/>
       <c r="B17" s="13" t="s">
         <v>55</v>
       </c>
@@ -7210,7 +7204,7 @@
       <c r="U17" s="16"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="56">
+      <c r="A18" s="53">
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -7259,7 +7253,7 @@
       <c r="U18" s="5"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="56"/>
+      <c r="A19" s="53"/>
       <c r="B19" s="2" t="s">
         <v>57</v>
       </c>
@@ -7294,7 +7288,7 @@
       <c r="U19" s="5"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="56"/>
+      <c r="A20" s="53"/>
       <c r="B20" s="2" t="s">
         <v>58</v>
       </c>
@@ -7341,7 +7335,7 @@
       <c r="U20" s="5"/>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="56"/>
+      <c r="A21" s="53"/>
       <c r="B21" s="2" t="s">
         <v>59</v>
       </c>
@@ -7394,7 +7388,7 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="56"/>
+      <c r="A22" s="53"/>
       <c r="B22" s="2" t="s">
         <v>60</v>
       </c>
@@ -7441,7 +7435,7 @@
       <c r="U22" s="5"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="56"/>
+      <c r="A23" s="53"/>
       <c r="B23" s="2" t="s">
         <v>61</v>
       </c>
@@ -7468,7 +7462,7 @@
       <c r="U23" s="5"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="56"/>
+      <c r="A24" s="53"/>
       <c r="B24" s="21" t="s">
         <v>62</v>
       </c>
@@ -7513,7 +7507,7 @@
       <c r="U24" s="24"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="52">
+      <c r="A25" s="60">
         <v>4</v>
       </c>
       <c r="B25" s="13" t="s">
@@ -7562,7 +7556,7 @@
       <c r="U25" s="16"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="52"/>
+      <c r="A26" s="60"/>
       <c r="B26" s="13" t="s">
         <v>64</v>
       </c>
@@ -7609,7 +7603,7 @@
       <c r="U26" s="16"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="52"/>
+      <c r="A27" s="60"/>
       <c r="B27" s="13" t="s">
         <v>65</v>
       </c>
@@ -7635,7 +7629,7 @@
         <v>39</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>179</v>
+        <v>18</v>
       </c>
       <c r="M27" s="18" t="s">
         <v>19</v>
@@ -7650,9 +7644,9 @@
       <c r="U27" s="16"/>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="52"/>
+      <c r="A28" s="60"/>
       <c r="B28" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C28" s="14" t="s">
         <v>30</v>
@@ -7697,94 +7691,94 @@
       <c r="U28" s="16"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="52"/>
+      <c r="A29" s="60"/>
       <c r="B29" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C29" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="63" t="s">
+      <c r="D29" s="54" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="54"/>
+      <c r="K29" s="54"/>
+      <c r="L29" s="54"/>
+      <c r="M29" s="54"/>
+      <c r="N29" s="54"/>
+      <c r="O29" s="54"/>
+      <c r="P29" s="54"/>
+      <c r="Q29" s="54"/>
+      <c r="R29" s="54"/>
+      <c r="S29" s="54"/>
+      <c r="T29" s="54"/>
+      <c r="U29" s="55"/>
+    </row>
+    <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
+      <c r="A30" s="60"/>
+      <c r="B30" s="26" t="s">
         <v>69</v>
-      </c>
-      <c r="E29" s="63"/>
-      <c r="F29" s="63"/>
-      <c r="G29" s="63"/>
-      <c r="H29" s="63"/>
-      <c r="I29" s="63"/>
-      <c r="J29" s="63"/>
-      <c r="K29" s="63"/>
-      <c r="L29" s="63"/>
-      <c r="M29" s="63"/>
-      <c r="N29" s="63"/>
-      <c r="O29" s="63"/>
-      <c r="P29" s="63"/>
-      <c r="Q29" s="63"/>
-      <c r="R29" s="63"/>
-      <c r="S29" s="63"/>
-      <c r="T29" s="63"/>
-      <c r="U29" s="64"/>
-    </row>
-    <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="52"/>
-      <c r="B30" s="26" t="s">
-        <v>70</v>
       </c>
       <c r="C30" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D30" s="65"/>
-      <c r="E30" s="65"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="65"/>
-      <c r="H30" s="65"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="65"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="65"/>
-      <c r="M30" s="65"/>
-      <c r="N30" s="65"/>
-      <c r="O30" s="65"/>
-      <c r="P30" s="65"/>
-      <c r="Q30" s="65"/>
-      <c r="R30" s="65"/>
-      <c r="S30" s="65"/>
-      <c r="T30" s="65"/>
-      <c r="U30" s="66"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="56"/>
+      <c r="J30" s="56"/>
+      <c r="K30" s="56"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="56"/>
+      <c r="N30" s="56"/>
+      <c r="O30" s="56"/>
+      <c r="P30" s="56"/>
+      <c r="Q30" s="56"/>
+      <c r="R30" s="56"/>
+      <c r="S30" s="56"/>
+      <c r="T30" s="56"/>
+      <c r="U30" s="57"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="52"/>
+      <c r="A31" s="60"/>
       <c r="B31" s="26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C31" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="67"/>
-      <c r="E31" s="67"/>
-      <c r="F31" s="67"/>
-      <c r="G31" s="67"/>
-      <c r="H31" s="67"/>
-      <c r="I31" s="67"/>
-      <c r="J31" s="67"/>
-      <c r="K31" s="67"/>
-      <c r="L31" s="67"/>
-      <c r="M31" s="67"/>
-      <c r="N31" s="67"/>
-      <c r="O31" s="67"/>
-      <c r="P31" s="67"/>
-      <c r="Q31" s="67"/>
-      <c r="R31" s="67"/>
-      <c r="S31" s="67"/>
-      <c r="T31" s="67"/>
-      <c r="U31" s="68"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="58"/>
+      <c r="L31" s="58"/>
+      <c r="M31" s="58"/>
+      <c r="N31" s="58"/>
+      <c r="O31" s="58"/>
+      <c r="P31" s="58"/>
+      <c r="Q31" s="58"/>
+      <c r="R31" s="58"/>
+      <c r="S31" s="58"/>
+      <c r="T31" s="58"/>
+      <c r="U31" s="59"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="56">
+      <c r="A32" s="53">
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>15</v>
@@ -7808,7 +7802,7 @@
         <v>39</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>179</v>
+        <v>18</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>19</v>
@@ -7823,9 +7817,9 @@
       <c r="U32" s="5"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="56"/>
+      <c r="A33" s="53"/>
       <c r="B33" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>24</v>
@@ -7870,9 +7864,9 @@
       <c r="U33" s="5"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="56"/>
+      <c r="A34" s="53"/>
       <c r="B34" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>27</v>
@@ -7917,202 +7911,202 @@
       <c r="U34" s="5"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="56"/>
+      <c r="A35" s="53"/>
       <c r="B35" s="28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C35" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="63" t="s">
-        <v>69</v>
-      </c>
-      <c r="E35" s="63"/>
-      <c r="F35" s="63"/>
-      <c r="G35" s="63"/>
-      <c r="H35" s="63"/>
-      <c r="I35" s="63"/>
-      <c r="J35" s="63"/>
-      <c r="K35" s="63"/>
-      <c r="L35" s="63"/>
-      <c r="M35" s="63"/>
-      <c r="N35" s="63"/>
-      <c r="O35" s="63"/>
-      <c r="P35" s="63"/>
-      <c r="Q35" s="63"/>
-      <c r="R35" s="63"/>
-      <c r="S35" s="63"/>
-      <c r="T35" s="63"/>
-      <c r="U35" s="64"/>
+      <c r="D35" s="54" t="s">
+        <v>68</v>
+      </c>
+      <c r="E35" s="54"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="54"/>
+      <c r="K35" s="54"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="54"/>
+      <c r="N35" s="54"/>
+      <c r="O35" s="54"/>
+      <c r="P35" s="54"/>
+      <c r="Q35" s="54"/>
+      <c r="R35" s="54"/>
+      <c r="S35" s="54"/>
+      <c r="T35" s="54"/>
+      <c r="U35" s="55"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="56"/>
+      <c r="A36" s="53"/>
       <c r="B36" s="28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C36" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="65"/>
-      <c r="E36" s="65"/>
-      <c r="F36" s="65"/>
-      <c r="G36" s="65"/>
-      <c r="H36" s="65"/>
-      <c r="I36" s="65"/>
-      <c r="J36" s="65"/>
-      <c r="K36" s="65"/>
-      <c r="L36" s="65"/>
-      <c r="M36" s="65"/>
-      <c r="N36" s="65"/>
-      <c r="O36" s="65"/>
-      <c r="P36" s="65"/>
-      <c r="Q36" s="65"/>
-      <c r="R36" s="65"/>
-      <c r="S36" s="65"/>
-      <c r="T36" s="65"/>
-      <c r="U36" s="66"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="56"/>
+      <c r="F36" s="56"/>
+      <c r="G36" s="56"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="56"/>
+      <c r="J36" s="56"/>
+      <c r="K36" s="56"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="56"/>
+      <c r="N36" s="56"/>
+      <c r="O36" s="56"/>
+      <c r="P36" s="56"/>
+      <c r="Q36" s="56"/>
+      <c r="R36" s="56"/>
+      <c r="S36" s="56"/>
+      <c r="T36" s="56"/>
+      <c r="U36" s="57"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="56"/>
+      <c r="A37" s="53"/>
       <c r="B37" s="28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C37" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D37" s="65"/>
-      <c r="E37" s="65"/>
-      <c r="F37" s="65"/>
-      <c r="G37" s="65"/>
-      <c r="H37" s="65"/>
-      <c r="I37" s="65"/>
-      <c r="J37" s="65"/>
-      <c r="K37" s="65"/>
-      <c r="L37" s="65"/>
-      <c r="M37" s="65"/>
-      <c r="N37" s="65"/>
-      <c r="O37" s="65"/>
-      <c r="P37" s="65"/>
-      <c r="Q37" s="65"/>
-      <c r="R37" s="65"/>
-      <c r="S37" s="65"/>
-      <c r="T37" s="65"/>
-      <c r="U37" s="66"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="56"/>
+      <c r="F37" s="56"/>
+      <c r="G37" s="56"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="56"/>
+      <c r="J37" s="56"/>
+      <c r="K37" s="56"/>
+      <c r="L37" s="56"/>
+      <c r="M37" s="56"/>
+      <c r="N37" s="56"/>
+      <c r="O37" s="56"/>
+      <c r="P37" s="56"/>
+      <c r="Q37" s="56"/>
+      <c r="R37" s="56"/>
+      <c r="S37" s="56"/>
+      <c r="T37" s="56"/>
+      <c r="U37" s="57"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="56"/>
+      <c r="A38" s="53"/>
       <c r="B38" s="28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C38" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D38" s="65"/>
-      <c r="E38" s="65"/>
-      <c r="F38" s="65"/>
-      <c r="G38" s="65"/>
-      <c r="H38" s="65"/>
-      <c r="I38" s="65"/>
-      <c r="J38" s="65"/>
-      <c r="K38" s="65"/>
-      <c r="L38" s="65"/>
-      <c r="M38" s="65"/>
-      <c r="N38" s="65"/>
-      <c r="O38" s="65"/>
-      <c r="P38" s="65"/>
-      <c r="Q38" s="65"/>
-      <c r="R38" s="65"/>
-      <c r="S38" s="65"/>
-      <c r="T38" s="65"/>
-      <c r="U38" s="66"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="56"/>
+      <c r="H38" s="56"/>
+      <c r="I38" s="56"/>
+      <c r="J38" s="56"/>
+      <c r="K38" s="56"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="56"/>
+      <c r="N38" s="56"/>
+      <c r="O38" s="56"/>
+      <c r="P38" s="56"/>
+      <c r="Q38" s="56"/>
+      <c r="R38" s="56"/>
+      <c r="S38" s="56"/>
+      <c r="T38" s="56"/>
+      <c r="U38" s="57"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="52">
+      <c r="A39" s="60">
         <v>6</v>
       </c>
       <c r="B39" s="28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C39" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="65"/>
-      <c r="E39" s="65"/>
-      <c r="F39" s="65"/>
-      <c r="G39" s="65"/>
-      <c r="H39" s="65"/>
-      <c r="I39" s="65"/>
-      <c r="J39" s="65"/>
-      <c r="K39" s="65"/>
-      <c r="L39" s="65"/>
-      <c r="M39" s="65"/>
-      <c r="N39" s="65"/>
-      <c r="O39" s="65"/>
-      <c r="P39" s="65"/>
-      <c r="Q39" s="65"/>
-      <c r="R39" s="65"/>
-      <c r="S39" s="65"/>
-      <c r="T39" s="65"/>
-      <c r="U39" s="66"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="56"/>
+      <c r="F39" s="56"/>
+      <c r="G39" s="56"/>
+      <c r="H39" s="56"/>
+      <c r="I39" s="56"/>
+      <c r="J39" s="56"/>
+      <c r="K39" s="56"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="56"/>
+      <c r="N39" s="56"/>
+      <c r="O39" s="56"/>
+      <c r="P39" s="56"/>
+      <c r="Q39" s="56"/>
+      <c r="R39" s="56"/>
+      <c r="S39" s="56"/>
+      <c r="T39" s="56"/>
+      <c r="U39" s="57"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="52"/>
+      <c r="A40" s="60"/>
       <c r="B40" s="28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C40" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="D40" s="65"/>
-      <c r="E40" s="65"/>
-      <c r="F40" s="65"/>
-      <c r="G40" s="65"/>
-      <c r="H40" s="65"/>
-      <c r="I40" s="65"/>
-      <c r="J40" s="65"/>
-      <c r="K40" s="65"/>
-      <c r="L40" s="65"/>
-      <c r="M40" s="65"/>
-      <c r="N40" s="65"/>
-      <c r="O40" s="65"/>
-      <c r="P40" s="65"/>
-      <c r="Q40" s="65"/>
-      <c r="R40" s="65"/>
-      <c r="S40" s="65"/>
-      <c r="T40" s="65"/>
-      <c r="U40" s="66"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="56"/>
+      <c r="K40" s="56"/>
+      <c r="L40" s="56"/>
+      <c r="M40" s="56"/>
+      <c r="N40" s="56"/>
+      <c r="O40" s="56"/>
+      <c r="P40" s="56"/>
+      <c r="Q40" s="56"/>
+      <c r="R40" s="56"/>
+      <c r="S40" s="56"/>
+      <c r="T40" s="56"/>
+      <c r="U40" s="57"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="52"/>
+      <c r="A41" s="60"/>
       <c r="B41" s="28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C41" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="67"/>
-      <c r="H41" s="67"/>
-      <c r="I41" s="67"/>
-      <c r="J41" s="67"/>
-      <c r="K41" s="67"/>
-      <c r="L41" s="67"/>
-      <c r="M41" s="67"/>
-      <c r="N41" s="67"/>
-      <c r="O41" s="67"/>
-      <c r="P41" s="67"/>
-      <c r="Q41" s="67"/>
-      <c r="R41" s="67"/>
-      <c r="S41" s="67"/>
-      <c r="T41" s="67"/>
-      <c r="U41" s="68"/>
+      <c r="D41" s="58"/>
+      <c r="E41" s="58"/>
+      <c r="F41" s="58"/>
+      <c r="G41" s="58"/>
+      <c r="H41" s="58"/>
+      <c r="I41" s="58"/>
+      <c r="J41" s="58"/>
+      <c r="K41" s="58"/>
+      <c r="L41" s="58"/>
+      <c r="M41" s="58"/>
+      <c r="N41" s="58"/>
+      <c r="O41" s="58"/>
+      <c r="P41" s="58"/>
+      <c r="Q41" s="58"/>
+      <c r="R41" s="58"/>
+      <c r="S41" s="58"/>
+      <c r="T41" s="58"/>
+      <c r="U41" s="59"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="52"/>
+      <c r="A42" s="60"/>
       <c r="B42" s="29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C42" s="14" t="s">
         <v>30</v>
@@ -8151,9 +8145,9 @@
       </c>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="52"/>
+      <c r="A43" s="60"/>
       <c r="B43" s="29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C43" s="14" t="s">
         <v>34</v>
@@ -8180,9 +8174,9 @@
       <c r="U43" s="16"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="52"/>
+      <c r="A44" s="60"/>
       <c r="B44" s="30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C44" s="22" t="s">
         <v>37</v>
@@ -8207,9 +8201,9 @@
       <c r="U44" s="24"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="52"/>
+      <c r="A45" s="60"/>
       <c r="B45" s="29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C45" s="14" t="s">
         <v>41</v>
@@ -8234,11 +8228,11 @@
       <c r="U45" s="16"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="56">
+      <c r="A46" s="53">
         <v>7</v>
       </c>
       <c r="B46" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>15</v>
@@ -8259,7 +8253,7 @@
         <v>39</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>179</v>
+        <v>18</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>38</v>
@@ -8268,7 +8262,7 @@
         <v>39</v>
       </c>
       <c r="L46" s="5" t="s">
-        <v>179</v>
+        <v>18</v>
       </c>
       <c r="M46" s="2" t="s">
         <v>19</v>
@@ -8283,9 +8277,9 @@
       <c r="U46" s="5"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="56"/>
+      <c r="A47" s="53"/>
       <c r="B47" s="31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>24</v>
@@ -8330,9 +8324,9 @@
       <c r="U47" s="5"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="56"/>
+      <c r="A48" s="53"/>
       <c r="B48" s="31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>27</v>
@@ -8353,7 +8347,7 @@
         <v>39</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>179</v>
+        <v>18</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>38</v>
@@ -8362,7 +8356,7 @@
         <v>39</v>
       </c>
       <c r="L48" s="5" t="s">
-        <v>179</v>
+        <v>18</v>
       </c>
       <c r="M48" s="10" t="s">
         <v>19</v>
@@ -8377,9 +8371,9 @@
       <c r="U48" s="5"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="56"/>
+      <c r="A49" s="53"/>
       <c r="B49" s="46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C49" s="47" t="s">
         <v>30</v>
@@ -8424,9 +8418,9 @@
       <c r="U49" s="5"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="56"/>
+      <c r="A50" s="53"/>
       <c r="B50" s="46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C50" s="31" t="s">
         <v>34</v>
@@ -8471,9 +8465,9 @@
       <c r="U50" s="5"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="56"/>
+      <c r="A51" s="53"/>
       <c r="B51" s="46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C51" s="31" t="s">
         <v>37</v>
@@ -8498,9 +8492,9 @@
       <c r="U51" s="5"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="56"/>
+      <c r="A52" s="53"/>
       <c r="B52" s="46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C52" s="31" t="s">
         <v>41</v>
@@ -8525,11 +8519,11 @@
       <c r="U52" s="5"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="52">
+      <c r="A53" s="60">
         <v>8</v>
       </c>
       <c r="B53" s="48" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C53" s="29" t="s">
         <v>15</v>
@@ -8568,9 +8562,9 @@
       <c r="U53" s="16"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="52"/>
+      <c r="A54" s="60"/>
       <c r="B54" s="48" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C54" s="29" t="s">
         <v>24</v>
@@ -8615,9 +8609,9 @@
       <c r="U54" s="16"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="52"/>
+      <c r="A55" s="60"/>
       <c r="B55" s="48" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C55" s="29" t="s">
         <v>27</v>
@@ -8656,9 +8650,9 @@
       <c r="U55" s="16"/>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="52"/>
+      <c r="A56" s="60"/>
       <c r="B56" s="48" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C56" s="29" t="s">
         <v>30</v>
@@ -8715,9 +8709,9 @@
       </c>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="52"/>
+      <c r="A57" s="60"/>
       <c r="B57" s="48" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C57" s="29" t="s">
         <v>34</v>
@@ -8762,9 +8756,9 @@
       <c r="U57" s="16"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="52"/>
+      <c r="A58" s="60"/>
       <c r="B58" s="48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C58" s="29" t="s">
         <v>37</v>
@@ -8789,9 +8783,9 @@
       <c r="U58" s="16"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="52"/>
+      <c r="A59" s="60"/>
       <c r="B59" s="48" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C59" s="29" t="s">
         <v>41</v>
@@ -8816,11 +8810,11 @@
       <c r="U59" s="16"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="56">
+      <c r="A60" s="53">
         <v>9</v>
       </c>
       <c r="B60" s="46" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C60" s="31" t="s">
         <v>15</v>
@@ -8865,9 +8859,9 @@
       <c r="U60" s="5"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="56"/>
+      <c r="A61" s="53"/>
       <c r="B61" s="46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C61" s="31" t="s">
         <v>24</v>
@@ -8912,9 +8906,9 @@
       <c r="U61" s="5"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="56"/>
+      <c r="A62" s="53"/>
       <c r="B62" s="46" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C62" s="31" t="s">
         <v>27</v>
@@ -8935,7 +8929,7 @@
         <v>39</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>179</v>
+        <v>18</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>31</v>
@@ -8959,9 +8953,9 @@
       <c r="U62" s="5"/>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="56"/>
+      <c r="A63" s="53"/>
       <c r="B63" s="46" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C63" s="31" t="s">
         <v>30</v>
@@ -9012,9 +9006,9 @@
       </c>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="56"/>
+      <c r="A64" s="53"/>
       <c r="B64" s="46" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C64" s="31" t="s">
         <v>34</v>
@@ -9053,9 +9047,9 @@
       <c r="U64" s="6"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="56"/>
+      <c r="A65" s="53"/>
       <c r="B65" s="46" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C65" s="31" t="s">
         <v>37</v>
@@ -9098,9 +9092,9 @@
       <c r="U65" s="6"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="56"/>
+      <c r="A66" s="53"/>
       <c r="B66" s="46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C66" s="31" t="s">
         <v>41</v>
@@ -9125,11 +9119,11 @@
       <c r="U66" s="6"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="52">
+      <c r="A67" s="60">
         <v>10</v>
       </c>
       <c r="B67" s="48" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C67" s="29" t="s">
         <v>15</v>
@@ -9168,9 +9162,9 @@
       <c r="U67" s="17"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="52"/>
+      <c r="A68" s="60"/>
       <c r="B68" s="48" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C68" s="29" t="s">
         <v>24</v>
@@ -9215,9 +9209,9 @@
       <c r="U68" s="17"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="52"/>
+      <c r="A69" s="60"/>
       <c r="B69" s="48" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C69" s="29" t="s">
         <v>27</v>
@@ -9256,9 +9250,9 @@
       <c r="U69" s="17"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="52"/>
+      <c r="A70" s="60"/>
       <c r="B70" s="48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C70" s="29" t="s">
         <v>30</v>
@@ -9315,9 +9309,9 @@
       </c>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="52"/>
+      <c r="A71" s="60"/>
       <c r="B71" s="48" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C71" s="29" t="s">
         <v>34</v>
@@ -9356,9 +9350,9 @@
       <c r="U71" s="17"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="52"/>
+      <c r="A72" s="60"/>
       <c r="B72" s="48" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C72" s="29" t="s">
         <v>37</v>
@@ -9401,9 +9395,9 @@
       <c r="U72" s="17"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="52"/>
+      <c r="A73" s="60"/>
       <c r="B73" s="48" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C73" s="29" t="s">
         <v>41</v>
@@ -9428,11 +9422,11 @@
       <c r="U73" s="17"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="56">
+      <c r="A74" s="53">
         <v>11</v>
       </c>
       <c r="B74" s="46" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C74" s="49" t="s">
         <v>15</v>
@@ -9477,9 +9471,9 @@
       <c r="U74" s="6"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="56"/>
+      <c r="A75" s="53"/>
       <c r="B75" s="31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>24</v>
@@ -9518,9 +9512,9 @@
       <c r="U75" s="6"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="56"/>
+      <c r="A76" s="53"/>
       <c r="B76" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>27</v>
@@ -9559,9 +9553,9 @@
       <c r="U76" s="6"/>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="56"/>
+      <c r="A77" s="53"/>
       <c r="B77" s="31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>30</v>
@@ -9600,9 +9594,9 @@
       <c r="U77" s="5"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="56"/>
+      <c r="A78" s="53"/>
       <c r="B78" s="31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>34</v>
@@ -9647,9 +9641,9 @@
       <c r="U78" s="5"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="56"/>
+      <c r="A79" s="53"/>
       <c r="B79" s="31" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>37</v>
@@ -9692,9 +9686,9 @@
       <c r="U79" s="5"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="56"/>
+      <c r="A80" s="53"/>
       <c r="B80" s="31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>41</v>
@@ -9719,395 +9713,395 @@
       <c r="U80" s="5"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="52">
+      <c r="A81" s="60">
         <v>12</v>
       </c>
       <c r="B81" s="29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C81" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D81" s="57" t="s">
+      <c r="D81" s="69" t="s">
+        <v>121</v>
+      </c>
+      <c r="E81" s="69"/>
+      <c r="F81" s="69"/>
+      <c r="G81" s="69"/>
+      <c r="H81" s="69"/>
+      <c r="I81" s="69"/>
+      <c r="J81" s="69"/>
+      <c r="K81" s="69"/>
+      <c r="L81" s="69"/>
+      <c r="M81" s="69"/>
+      <c r="N81" s="69"/>
+      <c r="O81" s="69"/>
+      <c r="P81" s="69"/>
+      <c r="Q81" s="69"/>
+      <c r="R81" s="69"/>
+      <c r="S81" s="69"/>
+      <c r="T81" s="69"/>
+      <c r="U81" s="70"/>
+    </row>
+    <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
+      <c r="A82" s="60"/>
+      <c r="B82" s="29" t="s">
         <v>122</v>
-      </c>
-      <c r="E81" s="57"/>
-      <c r="F81" s="57"/>
-      <c r="G81" s="57"/>
-      <c r="H81" s="57"/>
-      <c r="I81" s="57"/>
-      <c r="J81" s="57"/>
-      <c r="K81" s="57"/>
-      <c r="L81" s="57"/>
-      <c r="M81" s="57"/>
-      <c r="N81" s="57"/>
-      <c r="O81" s="57"/>
-      <c r="P81" s="57"/>
-      <c r="Q81" s="57"/>
-      <c r="R81" s="57"/>
-      <c r="S81" s="57"/>
-      <c r="T81" s="57"/>
-      <c r="U81" s="58"/>
-    </row>
-    <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="52"/>
-      <c r="B82" s="29" t="s">
-        <v>123</v>
       </c>
       <c r="C82" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D82" s="59"/>
-      <c r="E82" s="59"/>
-      <c r="F82" s="59"/>
-      <c r="G82" s="59"/>
-      <c r="H82" s="59"/>
-      <c r="I82" s="59"/>
-      <c r="J82" s="59"/>
-      <c r="K82" s="59"/>
-      <c r="L82" s="59"/>
-      <c r="M82" s="59"/>
-      <c r="N82" s="59"/>
-      <c r="O82" s="59"/>
-      <c r="P82" s="59"/>
-      <c r="Q82" s="59"/>
-      <c r="R82" s="59"/>
-      <c r="S82" s="59"/>
-      <c r="T82" s="59"/>
-      <c r="U82" s="60"/>
+      <c r="D82" s="71"/>
+      <c r="E82" s="71"/>
+      <c r="F82" s="71"/>
+      <c r="G82" s="71"/>
+      <c r="H82" s="71"/>
+      <c r="I82" s="71"/>
+      <c r="J82" s="71"/>
+      <c r="K82" s="71"/>
+      <c r="L82" s="71"/>
+      <c r="M82" s="71"/>
+      <c r="N82" s="71"/>
+      <c r="O82" s="71"/>
+      <c r="P82" s="71"/>
+      <c r="Q82" s="71"/>
+      <c r="R82" s="71"/>
+      <c r="S82" s="71"/>
+      <c r="T82" s="71"/>
+      <c r="U82" s="72"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="52"/>
+      <c r="A83" s="60"/>
       <c r="B83" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C83" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D83" s="59"/>
-      <c r="E83" s="59"/>
-      <c r="F83" s="59"/>
-      <c r="G83" s="59"/>
-      <c r="H83" s="59"/>
-      <c r="I83" s="59"/>
-      <c r="J83" s="59"/>
-      <c r="K83" s="59"/>
-      <c r="L83" s="59"/>
-      <c r="M83" s="59"/>
-      <c r="N83" s="59"/>
-      <c r="O83" s="59"/>
-      <c r="P83" s="59"/>
-      <c r="Q83" s="59"/>
-      <c r="R83" s="59"/>
-      <c r="S83" s="59"/>
-      <c r="T83" s="59"/>
-      <c r="U83" s="60"/>
+      <c r="D83" s="71"/>
+      <c r="E83" s="71"/>
+      <c r="F83" s="71"/>
+      <c r="G83" s="71"/>
+      <c r="H83" s="71"/>
+      <c r="I83" s="71"/>
+      <c r="J83" s="71"/>
+      <c r="K83" s="71"/>
+      <c r="L83" s="71"/>
+      <c r="M83" s="71"/>
+      <c r="N83" s="71"/>
+      <c r="O83" s="71"/>
+      <c r="P83" s="71"/>
+      <c r="Q83" s="71"/>
+      <c r="R83" s="71"/>
+      <c r="S83" s="71"/>
+      <c r="T83" s="71"/>
+      <c r="U83" s="72"/>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="52"/>
+      <c r="A84" s="60"/>
       <c r="B84" s="29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C84" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D84" s="59"/>
-      <c r="E84" s="59"/>
-      <c r="F84" s="59"/>
-      <c r="G84" s="59"/>
-      <c r="H84" s="59"/>
-      <c r="I84" s="59"/>
-      <c r="J84" s="59"/>
-      <c r="K84" s="59"/>
-      <c r="L84" s="59"/>
-      <c r="M84" s="59"/>
-      <c r="N84" s="59"/>
-      <c r="O84" s="59"/>
-      <c r="P84" s="59"/>
-      <c r="Q84" s="59"/>
-      <c r="R84" s="59"/>
-      <c r="S84" s="59"/>
-      <c r="T84" s="59"/>
-      <c r="U84" s="60"/>
+      <c r="D84" s="71"/>
+      <c r="E84" s="71"/>
+      <c r="F84" s="71"/>
+      <c r="G84" s="71"/>
+      <c r="H84" s="71"/>
+      <c r="I84" s="71"/>
+      <c r="J84" s="71"/>
+      <c r="K84" s="71"/>
+      <c r="L84" s="71"/>
+      <c r="M84" s="71"/>
+      <c r="N84" s="71"/>
+      <c r="O84" s="71"/>
+      <c r="P84" s="71"/>
+      <c r="Q84" s="71"/>
+      <c r="R84" s="71"/>
+      <c r="S84" s="71"/>
+      <c r="T84" s="71"/>
+      <c r="U84" s="72"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="52"/>
+      <c r="A85" s="60"/>
       <c r="B85" s="29" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C85" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D85" s="59"/>
-      <c r="E85" s="59"/>
-      <c r="F85" s="59"/>
-      <c r="G85" s="59"/>
-      <c r="H85" s="59"/>
-      <c r="I85" s="59"/>
-      <c r="J85" s="59"/>
-      <c r="K85" s="59"/>
-      <c r="L85" s="59"/>
-      <c r="M85" s="59"/>
-      <c r="N85" s="59"/>
-      <c r="O85" s="59"/>
-      <c r="P85" s="59"/>
-      <c r="Q85" s="59"/>
-      <c r="R85" s="59"/>
-      <c r="S85" s="59"/>
-      <c r="T85" s="59"/>
-      <c r="U85" s="60"/>
+      <c r="D85" s="71"/>
+      <c r="E85" s="71"/>
+      <c r="F85" s="71"/>
+      <c r="G85" s="71"/>
+      <c r="H85" s="71"/>
+      <c r="I85" s="71"/>
+      <c r="J85" s="71"/>
+      <c r="K85" s="71"/>
+      <c r="L85" s="71"/>
+      <c r="M85" s="71"/>
+      <c r="N85" s="71"/>
+      <c r="O85" s="71"/>
+      <c r="P85" s="71"/>
+      <c r="Q85" s="71"/>
+      <c r="R85" s="71"/>
+      <c r="S85" s="71"/>
+      <c r="T85" s="71"/>
+      <c r="U85" s="72"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="52"/>
+      <c r="A86" s="60"/>
       <c r="B86" s="29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C86" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D86" s="59"/>
-      <c r="E86" s="59"/>
-      <c r="F86" s="59"/>
-      <c r="G86" s="59"/>
-      <c r="H86" s="59"/>
-      <c r="I86" s="59"/>
-      <c r="J86" s="59"/>
-      <c r="K86" s="59"/>
-      <c r="L86" s="59"/>
-      <c r="M86" s="59"/>
-      <c r="N86" s="59"/>
-      <c r="O86" s="59"/>
-      <c r="P86" s="59"/>
-      <c r="Q86" s="59"/>
-      <c r="R86" s="59"/>
-      <c r="S86" s="59"/>
-      <c r="T86" s="59"/>
-      <c r="U86" s="60"/>
+      <c r="D86" s="71"/>
+      <c r="E86" s="71"/>
+      <c r="F86" s="71"/>
+      <c r="G86" s="71"/>
+      <c r="H86" s="71"/>
+      <c r="I86" s="71"/>
+      <c r="J86" s="71"/>
+      <c r="K86" s="71"/>
+      <c r="L86" s="71"/>
+      <c r="M86" s="71"/>
+      <c r="N86" s="71"/>
+      <c r="O86" s="71"/>
+      <c r="P86" s="71"/>
+      <c r="Q86" s="71"/>
+      <c r="R86" s="71"/>
+      <c r="S86" s="71"/>
+      <c r="T86" s="71"/>
+      <c r="U86" s="72"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="52"/>
+      <c r="A87" s="60"/>
       <c r="B87" s="29" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C87" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D87" s="59"/>
-      <c r="E87" s="59"/>
-      <c r="F87" s="59"/>
-      <c r="G87" s="59"/>
-      <c r="H87" s="59"/>
-      <c r="I87" s="59"/>
-      <c r="J87" s="59"/>
-      <c r="K87" s="59"/>
-      <c r="L87" s="59"/>
-      <c r="M87" s="59"/>
-      <c r="N87" s="59"/>
-      <c r="O87" s="59"/>
-      <c r="P87" s="59"/>
-      <c r="Q87" s="59"/>
-      <c r="R87" s="59"/>
-      <c r="S87" s="59"/>
-      <c r="T87" s="59"/>
-      <c r="U87" s="60"/>
+      <c r="D87" s="71"/>
+      <c r="E87" s="71"/>
+      <c r="F87" s="71"/>
+      <c r="G87" s="71"/>
+      <c r="H87" s="71"/>
+      <c r="I87" s="71"/>
+      <c r="J87" s="71"/>
+      <c r="K87" s="71"/>
+      <c r="L87" s="71"/>
+      <c r="M87" s="71"/>
+      <c r="N87" s="71"/>
+      <c r="O87" s="71"/>
+      <c r="P87" s="71"/>
+      <c r="Q87" s="71"/>
+      <c r="R87" s="71"/>
+      <c r="S87" s="71"/>
+      <c r="T87" s="71"/>
+      <c r="U87" s="72"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="56">
+      <c r="A88" s="53">
         <v>13</v>
       </c>
       <c r="B88" s="31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D88" s="59"/>
-      <c r="E88" s="59"/>
-      <c r="F88" s="59"/>
-      <c r="G88" s="59"/>
-      <c r="H88" s="59"/>
-      <c r="I88" s="59"/>
-      <c r="J88" s="59"/>
-      <c r="K88" s="59"/>
-      <c r="L88" s="59"/>
-      <c r="M88" s="59"/>
-      <c r="N88" s="59"/>
-      <c r="O88" s="59"/>
-      <c r="P88" s="59"/>
-      <c r="Q88" s="59"/>
-      <c r="R88" s="59"/>
-      <c r="S88" s="59"/>
-      <c r="T88" s="59"/>
-      <c r="U88" s="60"/>
+      <c r="D88" s="71"/>
+      <c r="E88" s="71"/>
+      <c r="F88" s="71"/>
+      <c r="G88" s="71"/>
+      <c r="H88" s="71"/>
+      <c r="I88" s="71"/>
+      <c r="J88" s="71"/>
+      <c r="K88" s="71"/>
+      <c r="L88" s="71"/>
+      <c r="M88" s="71"/>
+      <c r="N88" s="71"/>
+      <c r="O88" s="71"/>
+      <c r="P88" s="71"/>
+      <c r="Q88" s="71"/>
+      <c r="R88" s="71"/>
+      <c r="S88" s="71"/>
+      <c r="T88" s="71"/>
+      <c r="U88" s="72"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="56"/>
+      <c r="A89" s="53"/>
       <c r="B89" s="31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D89" s="59"/>
-      <c r="E89" s="59"/>
-      <c r="F89" s="59"/>
-      <c r="G89" s="59"/>
-      <c r="H89" s="59"/>
-      <c r="I89" s="59"/>
-      <c r="J89" s="59"/>
-      <c r="K89" s="59"/>
-      <c r="L89" s="59"/>
-      <c r="M89" s="59"/>
-      <c r="N89" s="59"/>
-      <c r="O89" s="59"/>
-      <c r="P89" s="59"/>
-      <c r="Q89" s="59"/>
-      <c r="R89" s="59"/>
-      <c r="S89" s="59"/>
-      <c r="T89" s="59"/>
-      <c r="U89" s="60"/>
+      <c r="D89" s="71"/>
+      <c r="E89" s="71"/>
+      <c r="F89" s="71"/>
+      <c r="G89" s="71"/>
+      <c r="H89" s="71"/>
+      <c r="I89" s="71"/>
+      <c r="J89" s="71"/>
+      <c r="K89" s="71"/>
+      <c r="L89" s="71"/>
+      <c r="M89" s="71"/>
+      <c r="N89" s="71"/>
+      <c r="O89" s="71"/>
+      <c r="P89" s="71"/>
+      <c r="Q89" s="71"/>
+      <c r="R89" s="71"/>
+      <c r="S89" s="71"/>
+      <c r="T89" s="71"/>
+      <c r="U89" s="72"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="56"/>
+      <c r="A90" s="53"/>
       <c r="B90" s="31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D90" s="59"/>
-      <c r="E90" s="59"/>
-      <c r="F90" s="59"/>
-      <c r="G90" s="59"/>
-      <c r="H90" s="59"/>
-      <c r="I90" s="59"/>
-      <c r="J90" s="59"/>
-      <c r="K90" s="59"/>
-      <c r="L90" s="59"/>
-      <c r="M90" s="59"/>
-      <c r="N90" s="59"/>
-      <c r="O90" s="59"/>
-      <c r="P90" s="59"/>
-      <c r="Q90" s="59"/>
-      <c r="R90" s="59"/>
-      <c r="S90" s="59"/>
-      <c r="T90" s="59"/>
-      <c r="U90" s="60"/>
+      <c r="D90" s="71"/>
+      <c r="E90" s="71"/>
+      <c r="F90" s="71"/>
+      <c r="G90" s="71"/>
+      <c r="H90" s="71"/>
+      <c r="I90" s="71"/>
+      <c r="J90" s="71"/>
+      <c r="K90" s="71"/>
+      <c r="L90" s="71"/>
+      <c r="M90" s="71"/>
+      <c r="N90" s="71"/>
+      <c r="O90" s="71"/>
+      <c r="P90" s="71"/>
+      <c r="Q90" s="71"/>
+      <c r="R90" s="71"/>
+      <c r="S90" s="71"/>
+      <c r="T90" s="71"/>
+      <c r="U90" s="72"/>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="56"/>
+      <c r="A91" s="53"/>
       <c r="B91" s="31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D91" s="59"/>
-      <c r="E91" s="59"/>
-      <c r="F91" s="59"/>
-      <c r="G91" s="59"/>
-      <c r="H91" s="59"/>
-      <c r="I91" s="59"/>
-      <c r="J91" s="59"/>
-      <c r="K91" s="59"/>
-      <c r="L91" s="59"/>
-      <c r="M91" s="59"/>
-      <c r="N91" s="59"/>
-      <c r="O91" s="59"/>
-      <c r="P91" s="59"/>
-      <c r="Q91" s="59"/>
-      <c r="R91" s="59"/>
-      <c r="S91" s="59"/>
-      <c r="T91" s="59"/>
-      <c r="U91" s="60"/>
+      <c r="D91" s="71"/>
+      <c r="E91" s="71"/>
+      <c r="F91" s="71"/>
+      <c r="G91" s="71"/>
+      <c r="H91" s="71"/>
+      <c r="I91" s="71"/>
+      <c r="J91" s="71"/>
+      <c r="K91" s="71"/>
+      <c r="L91" s="71"/>
+      <c r="M91" s="71"/>
+      <c r="N91" s="71"/>
+      <c r="O91" s="71"/>
+      <c r="P91" s="71"/>
+      <c r="Q91" s="71"/>
+      <c r="R91" s="71"/>
+      <c r="S91" s="71"/>
+      <c r="T91" s="71"/>
+      <c r="U91" s="72"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="56"/>
+      <c r="A92" s="53"/>
       <c r="B92" s="31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D92" s="59"/>
-      <c r="E92" s="59"/>
-      <c r="F92" s="59"/>
-      <c r="G92" s="59"/>
-      <c r="H92" s="59"/>
-      <c r="I92" s="59"/>
-      <c r="J92" s="59"/>
-      <c r="K92" s="59"/>
-      <c r="L92" s="59"/>
-      <c r="M92" s="59"/>
-      <c r="N92" s="59"/>
-      <c r="O92" s="59"/>
-      <c r="P92" s="59"/>
-      <c r="Q92" s="59"/>
-      <c r="R92" s="59"/>
-      <c r="S92" s="59"/>
-      <c r="T92" s="59"/>
-      <c r="U92" s="60"/>
+      <c r="D92" s="71"/>
+      <c r="E92" s="71"/>
+      <c r="F92" s="71"/>
+      <c r="G92" s="71"/>
+      <c r="H92" s="71"/>
+      <c r="I92" s="71"/>
+      <c r="J92" s="71"/>
+      <c r="K92" s="71"/>
+      <c r="L92" s="71"/>
+      <c r="M92" s="71"/>
+      <c r="N92" s="71"/>
+      <c r="O92" s="71"/>
+      <c r="P92" s="71"/>
+      <c r="Q92" s="71"/>
+      <c r="R92" s="71"/>
+      <c r="S92" s="71"/>
+      <c r="T92" s="71"/>
+      <c r="U92" s="72"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="56"/>
+      <c r="A93" s="53"/>
       <c r="B93" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D93" s="59"/>
-      <c r="E93" s="59"/>
-      <c r="F93" s="59"/>
-      <c r="G93" s="59"/>
-      <c r="H93" s="59"/>
-      <c r="I93" s="59"/>
-      <c r="J93" s="59"/>
-      <c r="K93" s="59"/>
-      <c r="L93" s="59"/>
-      <c r="M93" s="59"/>
-      <c r="N93" s="59"/>
-      <c r="O93" s="59"/>
-      <c r="P93" s="59"/>
-      <c r="Q93" s="59"/>
-      <c r="R93" s="59"/>
-      <c r="S93" s="59"/>
-      <c r="T93" s="59"/>
-      <c r="U93" s="60"/>
+      <c r="D93" s="71"/>
+      <c r="E93" s="71"/>
+      <c r="F93" s="71"/>
+      <c r="G93" s="71"/>
+      <c r="H93" s="71"/>
+      <c r="I93" s="71"/>
+      <c r="J93" s="71"/>
+      <c r="K93" s="71"/>
+      <c r="L93" s="71"/>
+      <c r="M93" s="71"/>
+      <c r="N93" s="71"/>
+      <c r="O93" s="71"/>
+      <c r="P93" s="71"/>
+      <c r="Q93" s="71"/>
+      <c r="R93" s="71"/>
+      <c r="S93" s="71"/>
+      <c r="T93" s="71"/>
+      <c r="U93" s="72"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="56"/>
+      <c r="A94" s="53"/>
       <c r="B94" s="31" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D94" s="61"/>
-      <c r="E94" s="61"/>
-      <c r="F94" s="61"/>
-      <c r="G94" s="61"/>
-      <c r="H94" s="61"/>
-      <c r="I94" s="61"/>
-      <c r="J94" s="61"/>
-      <c r="K94" s="61"/>
-      <c r="L94" s="61"/>
-      <c r="M94" s="61"/>
-      <c r="N94" s="61"/>
-      <c r="O94" s="61"/>
-      <c r="P94" s="61"/>
-      <c r="Q94" s="61"/>
-      <c r="R94" s="61"/>
-      <c r="S94" s="61"/>
-      <c r="T94" s="61"/>
-      <c r="U94" s="62"/>
+      <c r="D94" s="73"/>
+      <c r="E94" s="73"/>
+      <c r="F94" s="73"/>
+      <c r="G94" s="73"/>
+      <c r="H94" s="73"/>
+      <c r="I94" s="73"/>
+      <c r="J94" s="73"/>
+      <c r="K94" s="73"/>
+      <c r="L94" s="73"/>
+      <c r="M94" s="73"/>
+      <c r="N94" s="73"/>
+      <c r="O94" s="73"/>
+      <c r="P94" s="73"/>
+      <c r="Q94" s="73"/>
+      <c r="R94" s="73"/>
+      <c r="S94" s="73"/>
+      <c r="T94" s="73"/>
+      <c r="U94" s="74"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="52">
+      <c r="A95" s="60">
         <v>14</v>
       </c>
       <c r="B95" s="29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C95" s="14" t="s">
         <v>15</v>
@@ -10129,16 +10123,16 @@
       </c>
       <c r="Q95" s="32"/>
       <c r="R95" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S95" s="13"/>
       <c r="T95" s="15"/>
       <c r="U95" s="16"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="52"/>
+      <c r="A96" s="60"/>
       <c r="B96" s="29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C96" s="14" t="s">
         <v>24</v>
@@ -10160,16 +10154,16 @@
       </c>
       <c r="Q96" s="32"/>
       <c r="R96" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S96" s="13"/>
       <c r="T96" s="15"/>
       <c r="U96" s="16"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="52"/>
+      <c r="A97" s="60"/>
       <c r="B97" s="48" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C97" s="50" t="s">
         <v>27</v>
@@ -10191,16 +10185,16 @@
       </c>
       <c r="Q97" s="32"/>
       <c r="R97" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S97" s="13"/>
       <c r="T97" s="15"/>
       <c r="U97" s="16"/>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="52"/>
+      <c r="A98" s="60"/>
       <c r="B98" s="48" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C98" s="29" t="s">
         <v>30</v>
@@ -10222,16 +10216,16 @@
       </c>
       <c r="Q98" s="32"/>
       <c r="R98" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S98" s="13"/>
       <c r="T98" s="15"/>
       <c r="U98" s="16"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="52"/>
+      <c r="A99" s="60"/>
       <c r="B99" s="48" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C99" s="29" t="s">
         <v>34</v>
@@ -10253,16 +10247,16 @@
       </c>
       <c r="Q99" s="32"/>
       <c r="R99" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S99" s="13"/>
       <c r="T99" s="15"/>
       <c r="U99" s="16"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="52"/>
+      <c r="A100" s="60"/>
       <c r="B100" s="48" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C100" s="29" t="s">
         <v>37</v>
@@ -10284,16 +10278,16 @@
       </c>
       <c r="Q100" s="32"/>
       <c r="R100" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S100" s="13"/>
       <c r="T100" s="15"/>
       <c r="U100" s="16"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="52"/>
+      <c r="A101" s="60"/>
       <c r="B101" s="48" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C101" s="29" t="s">
         <v>41</v>
@@ -10315,18 +10309,18 @@
       </c>
       <c r="Q101" s="32"/>
       <c r="R101" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S101" s="13"/>
       <c r="T101" s="15"/>
       <c r="U101" s="16"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="56">
+      <c r="A102" s="53">
         <v>15</v>
       </c>
       <c r="B102" s="46" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C102" s="31" t="s">
         <v>15</v>
@@ -10348,16 +10342,16 @@
       </c>
       <c r="Q102" s="35"/>
       <c r="R102" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S102" s="2"/>
       <c r="T102" s="4"/>
       <c r="U102" s="5"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="56"/>
+      <c r="A103" s="53"/>
       <c r="B103" s="46" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C103" s="31" t="s">
         <v>24</v>
@@ -10379,16 +10373,16 @@
       </c>
       <c r="Q103" s="35"/>
       <c r="R103" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S103" s="2"/>
       <c r="T103" s="4"/>
       <c r="U103" s="5"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="56"/>
+      <c r="A104" s="53"/>
       <c r="B104" s="46" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C104" s="31" t="s">
         <v>27</v>
@@ -10410,16 +10404,16 @@
       </c>
       <c r="Q104" s="35"/>
       <c r="R104" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S104" s="2"/>
       <c r="T104" s="4"/>
       <c r="U104" s="5"/>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="56"/>
+      <c r="A105" s="53"/>
       <c r="B105" s="46" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C105" s="31" t="s">
         <v>30</v>
@@ -10441,16 +10435,16 @@
       </c>
       <c r="Q105" s="35"/>
       <c r="R105" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S105" s="2"/>
       <c r="T105" s="4"/>
       <c r="U105" s="5"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="56"/>
+      <c r="A106" s="53"/>
       <c r="B106" s="46" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C106" s="31" t="s">
         <v>34</v>
@@ -10472,16 +10466,16 @@
       </c>
       <c r="Q106" s="35"/>
       <c r="R106" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S106" s="2"/>
       <c r="T106" s="4"/>
       <c r="U106" s="5"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="56"/>
+      <c r="A107" s="53"/>
       <c r="B107" s="46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C107" s="31" t="s">
         <v>37</v>
@@ -10503,16 +10497,16 @@
       </c>
       <c r="Q107" s="35"/>
       <c r="R107" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S107" s="2"/>
       <c r="T107" s="4"/>
       <c r="U107" s="5"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="56"/>
+      <c r="A108" s="53"/>
       <c r="B108" s="46" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C108" s="31" t="s">
         <v>41</v>
@@ -10534,18 +10528,18 @@
       </c>
       <c r="Q108" s="35"/>
       <c r="R108" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S108" s="2"/>
       <c r="T108" s="4"/>
       <c r="U108" s="5"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="52">
+      <c r="A109" s="60">
         <v>16</v>
       </c>
       <c r="B109" s="48" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C109" s="29" t="s">
         <v>15</v>
@@ -10567,16 +10561,16 @@
       </c>
       <c r="Q109" s="32"/>
       <c r="R109" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S109" s="13"/>
       <c r="T109" s="15"/>
       <c r="U109" s="17"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="52"/>
+      <c r="A110" s="60"/>
       <c r="B110" s="48" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C110" s="29" t="s">
         <v>24</v>
@@ -10598,16 +10592,16 @@
       </c>
       <c r="Q110" s="32"/>
       <c r="R110" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S110" s="13"/>
       <c r="T110" s="15"/>
       <c r="U110" s="17"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="52"/>
+      <c r="A111" s="60"/>
       <c r="B111" s="48" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C111" s="29" t="s">
         <v>27</v>
@@ -10629,16 +10623,16 @@
       </c>
       <c r="Q111" s="32"/>
       <c r="R111" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S111" s="13"/>
       <c r="T111" s="15"/>
       <c r="U111" s="17"/>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="52"/>
+      <c r="A112" s="60"/>
       <c r="B112" s="48" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C112" s="29" t="s">
         <v>30</v>
@@ -10660,16 +10654,16 @@
       </c>
       <c r="Q112" s="32"/>
       <c r="R112" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S112" s="13"/>
       <c r="T112" s="15"/>
       <c r="U112" s="17"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="52"/>
+      <c r="A113" s="60"/>
       <c r="B113" s="48" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C113" s="29" t="s">
         <v>34</v>
@@ -10691,16 +10685,16 @@
       </c>
       <c r="Q113" s="32"/>
       <c r="R113" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S113" s="13"/>
       <c r="T113" s="15"/>
       <c r="U113" s="17"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="52"/>
+      <c r="A114" s="60"/>
       <c r="B114" s="48" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C114" s="29" t="s">
         <v>37</v>
@@ -10722,16 +10716,16 @@
       </c>
       <c r="Q114" s="32"/>
       <c r="R114" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S114" s="13"/>
       <c r="T114" s="15"/>
       <c r="U114" s="17"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="52"/>
+      <c r="A115" s="60"/>
       <c r="B115" s="48" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C115" s="29" t="s">
         <v>41</v>
@@ -10753,18 +10747,18 @@
       </c>
       <c r="Q115" s="32"/>
       <c r="R115" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S115" s="13"/>
       <c r="T115" s="15"/>
       <c r="U115" s="17"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="56">
+      <c r="A116" s="53">
         <v>17</v>
       </c>
       <c r="B116" s="46" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C116" s="31" t="s">
         <v>15</v>
@@ -10786,16 +10780,16 @@
       </c>
       <c r="Q116" s="35"/>
       <c r="R116" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S116" s="2"/>
       <c r="T116" s="4"/>
       <c r="U116" s="5"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="56"/>
+      <c r="A117" s="53"/>
       <c r="B117" s="46" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C117" s="31" t="s">
         <v>24</v>
@@ -10817,16 +10811,16 @@
       </c>
       <c r="Q117" s="35"/>
       <c r="R117" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S117" s="2"/>
       <c r="T117" s="4"/>
       <c r="U117" s="5"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="56"/>
+      <c r="A118" s="53"/>
       <c r="B118" s="46" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C118" s="31" t="s">
         <v>27</v>
@@ -10848,16 +10842,16 @@
       </c>
       <c r="Q118" s="35"/>
       <c r="R118" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S118" s="2"/>
       <c r="T118" s="4"/>
       <c r="U118" s="5"/>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="56"/>
+      <c r="A119" s="53"/>
       <c r="B119" s="46" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C119" s="31" t="s">
         <v>30</v>
@@ -10879,16 +10873,16 @@
       </c>
       <c r="Q119" s="35"/>
       <c r="R119" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S119" s="2"/>
       <c r="T119" s="4"/>
       <c r="U119" s="5"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="56"/>
+      <c r="A120" s="53"/>
       <c r="B120" s="46" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C120" s="31" t="s">
         <v>34</v>
@@ -10910,16 +10904,16 @@
       </c>
       <c r="Q120" s="35"/>
       <c r="R120" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S120" s="2"/>
       <c r="T120" s="4"/>
       <c r="U120" s="5"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="56"/>
+      <c r="A121" s="53"/>
       <c r="B121" s="46" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C121" s="31" t="s">
         <v>37</v>
@@ -10941,16 +10935,16 @@
       </c>
       <c r="Q121" s="35"/>
       <c r="R121" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S121" s="2"/>
       <c r="T121" s="4"/>
       <c r="U121" s="5"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="56"/>
+      <c r="A122" s="53"/>
       <c r="B122" s="46" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C122" s="31" t="s">
         <v>41</v>
@@ -10972,18 +10966,18 @@
       </c>
       <c r="Q122" s="35"/>
       <c r="R122" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S122" s="2"/>
       <c r="T122" s="4"/>
       <c r="U122" s="5"/>
     </row>
     <row r="123" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="52">
+      <c r="A123" s="60">
         <v>18</v>
       </c>
       <c r="B123" s="48" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C123" s="29" t="s">
         <v>15</v>
@@ -11005,16 +10999,16 @@
       </c>
       <c r="Q123" s="32"/>
       <c r="R123" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S123" s="13"/>
       <c r="T123" s="15"/>
       <c r="U123" s="17"/>
     </row>
     <row r="124" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="52"/>
+      <c r="A124" s="60"/>
       <c r="B124" s="48" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C124" s="29" t="s">
         <v>24</v>
@@ -11036,16 +11030,16 @@
       </c>
       <c r="Q124" s="32"/>
       <c r="R124" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S124" s="13"/>
       <c r="T124" s="15"/>
       <c r="U124" s="17"/>
     </row>
     <row r="125" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="52"/>
+      <c r="A125" s="60"/>
       <c r="B125" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C125" s="29" t="s">
         <v>27</v>
@@ -11067,16 +11061,16 @@
       </c>
       <c r="Q125" s="32"/>
       <c r="R125" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S125" s="13"/>
       <c r="T125" s="15"/>
       <c r="U125" s="17"/>
     </row>
     <row r="126" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="52"/>
+      <c r="A126" s="60"/>
       <c r="B126" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C126" s="29" t="s">
         <v>30</v>
@@ -11098,45 +11092,45 @@
       </c>
       <c r="Q126" s="32"/>
       <c r="R126" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S126" s="13"/>
       <c r="T126" s="15"/>
       <c r="U126" s="17"/>
     </row>
     <row r="127" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="52"/>
+      <c r="A127" s="60"/>
       <c r="B127" s="51" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C127" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D127" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="E127" s="54"/>
-      <c r="F127" s="54"/>
-      <c r="G127" s="54"/>
-      <c r="H127" s="54"/>
-      <c r="I127" s="54"/>
-      <c r="J127" s="54"/>
-      <c r="K127" s="54"/>
-      <c r="L127" s="54"/>
-      <c r="M127" s="54"/>
-      <c r="N127" s="54"/>
-      <c r="O127" s="54"/>
-      <c r="P127" s="54"/>
-      <c r="Q127" s="54"/>
-      <c r="R127" s="54"/>
-      <c r="S127" s="54"/>
-      <c r="T127" s="54"/>
-      <c r="U127" s="55"/>
+      <c r="D127" s="66" t="s">
+        <v>68</v>
+      </c>
+      <c r="E127" s="67"/>
+      <c r="F127" s="67"/>
+      <c r="G127" s="67"/>
+      <c r="H127" s="67"/>
+      <c r="I127" s="67"/>
+      <c r="J127" s="67"/>
+      <c r="K127" s="67"/>
+      <c r="L127" s="67"/>
+      <c r="M127" s="67"/>
+      <c r="N127" s="67"/>
+      <c r="O127" s="67"/>
+      <c r="P127" s="67"/>
+      <c r="Q127" s="67"/>
+      <c r="R127" s="67"/>
+      <c r="S127" s="67"/>
+      <c r="T127" s="67"/>
+      <c r="U127" s="68"/>
     </row>
     <row r="128" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="52"/>
+      <c r="A128" s="60"/>
       <c r="B128" s="48" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C128" s="29" t="s">
         <v>37</v>
@@ -11158,16 +11152,16 @@
       </c>
       <c r="Q128" s="32"/>
       <c r="R128" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S128" s="13"/>
       <c r="T128" s="15"/>
       <c r="U128" s="17"/>
     </row>
     <row r="129" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="52"/>
+      <c r="A129" s="60"/>
       <c r="B129" s="48" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C129" s="29" t="s">
         <v>41</v>
@@ -11189,18 +11183,18 @@
       </c>
       <c r="Q129" s="32"/>
       <c r="R129" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S129" s="13"/>
       <c r="T129" s="15"/>
       <c r="U129" s="17"/>
     </row>
     <row r="130" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="56">
+      <c r="A130" s="53">
         <v>19</v>
       </c>
       <c r="B130" s="46" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C130" s="31" t="s">
         <v>15</v>
@@ -11222,16 +11216,16 @@
       </c>
       <c r="Q130" s="35"/>
       <c r="R130" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S130" s="2"/>
       <c r="T130" s="4"/>
       <c r="U130" s="5"/>
     </row>
     <row r="131" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="56"/>
+      <c r="A131" s="53"/>
       <c r="B131" s="46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C131" s="31" t="s">
         <v>24</v>
@@ -11253,16 +11247,16 @@
       </c>
       <c r="Q131" s="35"/>
       <c r="R131" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S131" s="2"/>
       <c r="T131" s="4"/>
       <c r="U131" s="5"/>
     </row>
     <row r="132" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="56"/>
+      <c r="A132" s="53"/>
       <c r="B132" s="46" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C132" s="31" t="s">
         <v>27</v>
@@ -11284,16 +11278,16 @@
       </c>
       <c r="Q132" s="35"/>
       <c r="R132" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S132" s="2"/>
       <c r="T132" s="4"/>
       <c r="U132" s="5"/>
     </row>
     <row r="133" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="56"/>
+      <c r="A133" s="53"/>
       <c r="B133" s="46" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C133" s="31" t="s">
         <v>30</v>
@@ -11315,16 +11309,16 @@
       </c>
       <c r="Q133" s="35"/>
       <c r="R133" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S133" s="2"/>
       <c r="T133" s="4"/>
       <c r="U133" s="5"/>
     </row>
     <row r="134" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="56"/>
+      <c r="A134" s="53"/>
       <c r="B134" s="46" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C134" s="31" t="s">
         <v>34</v>
@@ -11346,16 +11340,16 @@
       </c>
       <c r="Q134" s="35"/>
       <c r="R134" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S134" s="2"/>
       <c r="T134" s="4"/>
       <c r="U134" s="5"/>
     </row>
     <row r="135" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="56"/>
+      <c r="A135" s="53"/>
       <c r="B135" s="46" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C135" s="31" t="s">
         <v>37</v>
@@ -11377,16 +11371,16 @@
       </c>
       <c r="Q135" s="35"/>
       <c r="R135" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S135" s="2"/>
       <c r="T135" s="4"/>
       <c r="U135" s="5"/>
     </row>
     <row r="136" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="56"/>
+      <c r="A136" s="53"/>
       <c r="B136" s="46" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C136" s="31" t="s">
         <v>41</v>
@@ -11408,7 +11402,7 @@
       </c>
       <c r="Q136" s="35"/>
       <c r="R136" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S136" s="2"/>
       <c r="T136" s="4"/>
@@ -11430,6 +11424,27 @@
     <row r="150" ht="20.25"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A123:A129"/>
+    <mergeCell ref="D127:U127"/>
+    <mergeCell ref="A130:A136"/>
+    <mergeCell ref="D81:U94"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A101"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="A116:A122"/>
+    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="A74:A80"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="D29:U31"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="A32:A38"/>
     <mergeCell ref="D35:U41"/>
@@ -11446,27 +11461,6 @@
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="D29:U31"/>
-    <mergeCell ref="A46:A52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
-    <mergeCell ref="A123:A129"/>
-    <mergeCell ref="D127:U127"/>
-    <mergeCell ref="A130:A136"/>
-    <mergeCell ref="D81:U94"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="A116:A122"/>
-    <mergeCell ref="A81:A87"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/raw/Timetable_2026Autumn_2025LE.xlsx
+++ b/raw/Timetable_2026Autumn_2025LE.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30431"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14970802-2FB1-4743-8917-A2D6AC0E7B98}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1C74D07-280A-4E1E-844C-2EAD2DC9D9FC}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -156,7 +156,7 @@
     <t>Material Flow Technology</t>
   </si>
   <si>
-    <t>LELecturer</t>
+    <t>LIU Qi</t>
   </si>
   <si>
     <t>6       Sep.</t>
@@ -674,7 +674,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -870,11 +870,88 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1029,19 +1106,10 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1053,22 +1121,13 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1086,9 +1145,6 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1102,6 +1158,69 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1451,81 +1570,81 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="52" t="s">
+      <c r="C2" s="68"/>
+      <c r="D2" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52" t="s">
+      <c r="E2" s="71"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52" t="s">
+      <c r="H2" s="71"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52" t="s">
+      <c r="K2" s="71"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="52"/>
-      <c r="O2" s="52"/>
-      <c r="P2" s="52" t="s">
+      <c r="N2" s="71"/>
+      <c r="O2" s="72"/>
+      <c r="P2" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="52"/>
-      <c r="R2" s="52"/>
-      <c r="S2" s="52" t="s">
+      <c r="Q2" s="71"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="52"/>
-      <c r="U2" s="52"/>
+      <c r="T2" s="71"/>
+      <c r="U2" s="72"/>
     </row>
     <row r="3" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="61" t="s">
+      <c r="A3" s="74"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="52" t="s">
+      <c r="E3" s="71"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52" t="s">
+      <c r="H3" s="71"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52" t="s">
+      <c r="K3" s="71"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="52"/>
-      <c r="O3" s="52"/>
-      <c r="P3" s="52" t="s">
+      <c r="N3" s="71"/>
+      <c r="O3" s="72"/>
+      <c r="P3" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="52"/>
-      <c r="R3" s="52"/>
-      <c r="S3" s="52" t="s">
+      <c r="Q3" s="71"/>
+      <c r="R3" s="72"/>
+      <c r="S3" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="52"/>
-      <c r="U3" s="52"/>
+      <c r="T3" s="71"/>
+      <c r="U3" s="72"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="53">
+      <c r="A4" s="82">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1583,7 +1702,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="53"/>
+      <c r="A5" s="83"/>
       <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
@@ -1641,7 +1760,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="53"/>
+      <c r="A6" s="83"/>
       <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
@@ -1697,7 +1816,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="53"/>
+      <c r="A7" s="83"/>
       <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
@@ -1755,7 +1874,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="53"/>
+      <c r="A8" s="83"/>
       <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
@@ -1817,7 +1936,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="53"/>
+      <c r="A9" s="83"/>
       <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
@@ -1861,7 +1980,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="53"/>
+      <c r="A10" s="84"/>
       <c r="B10" s="2" t="s">
         <v>40</v>
       </c>
@@ -1903,7 +2022,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="60">
+      <c r="A11" s="75">
         <v>2</v>
       </c>
       <c r="B11" s="13" t="s">
@@ -1951,7 +2070,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="60"/>
+      <c r="A12" s="76"/>
       <c r="B12" s="13" t="s">
         <v>46</v>
       </c>
@@ -1995,7 +2114,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="60"/>
+      <c r="A13" s="76"/>
       <c r="B13" s="13" t="s">
         <v>48</v>
       </c>
@@ -2039,7 +2158,7 @@
       </c>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="60"/>
+      <c r="A14" s="76"/>
       <c r="B14" s="13" t="s">
         <v>49</v>
       </c>
@@ -2085,7 +2204,7 @@
       <c r="AA14" s="3"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="60"/>
+      <c r="A15" s="76"/>
       <c r="B15" s="13" t="s">
         <v>53</v>
       </c>
@@ -2119,7 +2238,7 @@
       <c r="AA15" s="3"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="60"/>
+      <c r="A16" s="76"/>
       <c r="B16" s="13" t="s">
         <v>54</v>
       </c>
@@ -2151,7 +2270,7 @@
       <c r="AA16" s="3"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="60"/>
+      <c r="A17" s="77"/>
       <c r="B17" s="13" t="s">
         <v>55</v>
       </c>
@@ -2178,7 +2297,7 @@
       <c r="U17" s="16"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="53">
+      <c r="A18" s="82">
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -2215,7 +2334,7 @@
       <c r="U18" s="5"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="53"/>
+      <c r="A19" s="83"/>
       <c r="B19" s="2" t="s">
         <v>57</v>
       </c>
@@ -2262,7 +2381,7 @@
       <c r="U19" s="5"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="53"/>
+      <c r="A20" s="83"/>
       <c r="B20" s="2" t="s">
         <v>58</v>
       </c>
@@ -2309,7 +2428,7 @@
       <c r="U20" s="5"/>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="53"/>
+      <c r="A21" s="83"/>
       <c r="B21" s="2" t="s">
         <v>59</v>
       </c>
@@ -2368,7 +2487,7 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="53"/>
+      <c r="A22" s="83"/>
       <c r="B22" s="2" t="s">
         <v>60</v>
       </c>
@@ -2409,22 +2528,40 @@
       <c r="U22" s="5"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="53"/>
+      <c r="A23" s="83"/>
       <c r="B23" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="5"/>
+      <c r="D23" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="M23" s="2"/>
       <c r="N23" s="4"/>
       <c r="O23" s="6"/>
@@ -2436,7 +2573,7 @@
       <c r="U23" s="5"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="53"/>
+      <c r="A24" s="84"/>
       <c r="B24" s="21" t="s">
         <v>62</v>
       </c>
@@ -2481,7 +2618,7 @@
       <c r="U24" s="24"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="60">
+      <c r="A25" s="75">
         <v>4</v>
       </c>
       <c r="B25" s="13" t="s">
@@ -2530,7 +2667,7 @@
       <c r="U25" s="16"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="60"/>
+      <c r="A26" s="76"/>
       <c r="B26" s="13" t="s">
         <v>64</v>
       </c>
@@ -2577,7 +2714,7 @@
       <c r="U26" s="16"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="60"/>
+      <c r="A27" s="76"/>
       <c r="B27" s="13" t="s">
         <v>65</v>
       </c>
@@ -2618,7 +2755,7 @@
       <c r="U27" s="16"/>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="60"/>
+      <c r="A28" s="76"/>
       <c r="B28" s="13" t="s">
         <v>66</v>
       </c>
@@ -2665,90 +2802,90 @@
       <c r="U28" s="16"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="60"/>
+      <c r="A29" s="76"/>
       <c r="B29" s="26" t="s">
         <v>67</v>
       </c>
       <c r="C29" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="54" t="s">
+      <c r="D29" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="E29" s="54"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="54"/>
-      <c r="J29" s="54"/>
-      <c r="K29" s="54"/>
-      <c r="L29" s="54"/>
-      <c r="M29" s="54"/>
-      <c r="N29" s="54"/>
-      <c r="O29" s="54"/>
-      <c r="P29" s="54"/>
-      <c r="Q29" s="54"/>
-      <c r="R29" s="54"/>
-      <c r="S29" s="54"/>
-      <c r="T29" s="54"/>
-      <c r="U29" s="55"/>
+      <c r="E29" s="80"/>
+      <c r="F29" s="80"/>
+      <c r="G29" s="80"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="80"/>
+      <c r="J29" s="80"/>
+      <c r="K29" s="80"/>
+      <c r="L29" s="80"/>
+      <c r="M29" s="80"/>
+      <c r="N29" s="80"/>
+      <c r="O29" s="80"/>
+      <c r="P29" s="80"/>
+      <c r="Q29" s="80"/>
+      <c r="R29" s="80"/>
+      <c r="S29" s="80"/>
+      <c r="T29" s="80"/>
+      <c r="U29" s="54"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="60"/>
+      <c r="A30" s="76"/>
       <c r="B30" s="26" t="s">
         <v>69</v>
       </c>
       <c r="C30" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="56"/>
-      <c r="J30" s="56"/>
-      <c r="K30" s="56"/>
-      <c r="L30" s="56"/>
-      <c r="M30" s="56"/>
-      <c r="N30" s="56"/>
-      <c r="O30" s="56"/>
-      <c r="P30" s="56"/>
-      <c r="Q30" s="56"/>
-      <c r="R30" s="56"/>
-      <c r="S30" s="56"/>
-      <c r="T30" s="56"/>
-      <c r="U30" s="57"/>
+      <c r="D30" s="79"/>
+      <c r="E30" s="80"/>
+      <c r="F30" s="80"/>
+      <c r="G30" s="80"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="80"/>
+      <c r="J30" s="80"/>
+      <c r="K30" s="80"/>
+      <c r="L30" s="80"/>
+      <c r="M30" s="80"/>
+      <c r="N30" s="80"/>
+      <c r="O30" s="80"/>
+      <c r="P30" s="80"/>
+      <c r="Q30" s="80"/>
+      <c r="R30" s="80"/>
+      <c r="S30" s="80"/>
+      <c r="T30" s="80"/>
+      <c r="U30" s="54"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="60"/>
+      <c r="A31" s="77"/>
       <c r="B31" s="26" t="s">
         <v>70</v>
       </c>
       <c r="C31" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="58"/>
-      <c r="K31" s="58"/>
-      <c r="L31" s="58"/>
-      <c r="M31" s="58"/>
-      <c r="N31" s="58"/>
-      <c r="O31" s="58"/>
-      <c r="P31" s="58"/>
-      <c r="Q31" s="58"/>
-      <c r="R31" s="58"/>
-      <c r="S31" s="58"/>
-      <c r="T31" s="58"/>
-      <c r="U31" s="59"/>
+      <c r="D31" s="81"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="55"/>
+      <c r="J31" s="55"/>
+      <c r="K31" s="55"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="55"/>
+      <c r="N31" s="55"/>
+      <c r="O31" s="55"/>
+      <c r="P31" s="55"/>
+      <c r="Q31" s="55"/>
+      <c r="R31" s="55"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="55"/>
+      <c r="U31" s="56"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="53">
+      <c r="A32" s="82">
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -2791,7 +2928,7 @@
       <c r="U32" s="5"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="53"/>
+      <c r="A33" s="83"/>
       <c r="B33" s="2" t="s">
         <v>72</v>
       </c>
@@ -2838,7 +2975,7 @@
       <c r="U33" s="5"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="53"/>
+      <c r="A34" s="83"/>
       <c r="B34" s="2" t="s">
         <v>73</v>
       </c>
@@ -2885,117 +3022,117 @@
       <c r="U34" s="5"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="53"/>
+      <c r="A35" s="83"/>
       <c r="B35" s="28" t="s">
         <v>74</v>
       </c>
       <c r="C35" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="54" t="s">
+      <c r="D35" s="78" t="s">
         <v>68</v>
       </c>
-      <c r="E35" s="54"/>
-      <c r="F35" s="54"/>
-      <c r="G35" s="54"/>
-      <c r="H35" s="54"/>
-      <c r="I35" s="54"/>
-      <c r="J35" s="54"/>
-      <c r="K35" s="54"/>
-      <c r="L35" s="54"/>
-      <c r="M35" s="54"/>
-      <c r="N35" s="54"/>
-      <c r="O35" s="54"/>
-      <c r="P35" s="54"/>
-      <c r="Q35" s="54"/>
-      <c r="R35" s="54"/>
-      <c r="S35" s="54"/>
-      <c r="T35" s="54"/>
-      <c r="U35" s="55"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="52"/>
+      <c r="K35" s="52"/>
+      <c r="L35" s="52"/>
+      <c r="M35" s="52"/>
+      <c r="N35" s="52"/>
+      <c r="O35" s="52"/>
+      <c r="P35" s="52"/>
+      <c r="Q35" s="52"/>
+      <c r="R35" s="52"/>
+      <c r="S35" s="52"/>
+      <c r="T35" s="52"/>
+      <c r="U35" s="53"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="53"/>
+      <c r="A36" s="83"/>
       <c r="B36" s="28" t="s">
         <v>75</v>
       </c>
       <c r="C36" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="56"/>
-      <c r="E36" s="56"/>
-      <c r="F36" s="56"/>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="56"/>
-      <c r="J36" s="56"/>
-      <c r="K36" s="56"/>
-      <c r="L36" s="56"/>
-      <c r="M36" s="56"/>
-      <c r="N36" s="56"/>
-      <c r="O36" s="56"/>
-      <c r="P36" s="56"/>
-      <c r="Q36" s="56"/>
-      <c r="R36" s="56"/>
-      <c r="S36" s="56"/>
-      <c r="T36" s="56"/>
-      <c r="U36" s="57"/>
+      <c r="D36" s="79"/>
+      <c r="E36" s="80"/>
+      <c r="F36" s="80"/>
+      <c r="G36" s="80"/>
+      <c r="H36" s="80"/>
+      <c r="I36" s="80"/>
+      <c r="J36" s="80"/>
+      <c r="K36" s="80"/>
+      <c r="L36" s="80"/>
+      <c r="M36" s="80"/>
+      <c r="N36" s="80"/>
+      <c r="O36" s="80"/>
+      <c r="P36" s="80"/>
+      <c r="Q36" s="80"/>
+      <c r="R36" s="80"/>
+      <c r="S36" s="80"/>
+      <c r="T36" s="80"/>
+      <c r="U36" s="54"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="53"/>
+      <c r="A37" s="83"/>
       <c r="B37" s="28" t="s">
         <v>76</v>
       </c>
       <c r="C37" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D37" s="56"/>
-      <c r="E37" s="56"/>
-      <c r="F37" s="56"/>
-      <c r="G37" s="56"/>
-      <c r="H37" s="56"/>
-      <c r="I37" s="56"/>
-      <c r="J37" s="56"/>
-      <c r="K37" s="56"/>
-      <c r="L37" s="56"/>
-      <c r="M37" s="56"/>
-      <c r="N37" s="56"/>
-      <c r="O37" s="56"/>
-      <c r="P37" s="56"/>
-      <c r="Q37" s="56"/>
-      <c r="R37" s="56"/>
-      <c r="S37" s="56"/>
-      <c r="T37" s="56"/>
-      <c r="U37" s="57"/>
+      <c r="D37" s="79"/>
+      <c r="E37" s="80"/>
+      <c r="F37" s="80"/>
+      <c r="G37" s="80"/>
+      <c r="H37" s="80"/>
+      <c r="I37" s="80"/>
+      <c r="J37" s="80"/>
+      <c r="K37" s="80"/>
+      <c r="L37" s="80"/>
+      <c r="M37" s="80"/>
+      <c r="N37" s="80"/>
+      <c r="O37" s="80"/>
+      <c r="P37" s="80"/>
+      <c r="Q37" s="80"/>
+      <c r="R37" s="80"/>
+      <c r="S37" s="80"/>
+      <c r="T37" s="80"/>
+      <c r="U37" s="54"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="53"/>
+      <c r="A38" s="84"/>
       <c r="B38" s="28" t="s">
         <v>77</v>
       </c>
       <c r="C38" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="56"/>
-      <c r="G38" s="56"/>
-      <c r="H38" s="56"/>
-      <c r="I38" s="56"/>
-      <c r="J38" s="56"/>
-      <c r="K38" s="56"/>
-      <c r="L38" s="56"/>
-      <c r="M38" s="56"/>
-      <c r="N38" s="56"/>
-      <c r="O38" s="56"/>
-      <c r="P38" s="56"/>
-      <c r="Q38" s="56"/>
-      <c r="R38" s="56"/>
-      <c r="S38" s="56"/>
-      <c r="T38" s="56"/>
-      <c r="U38" s="57"/>
+      <c r="D38" s="79"/>
+      <c r="E38" s="80"/>
+      <c r="F38" s="80"/>
+      <c r="G38" s="80"/>
+      <c r="H38" s="80"/>
+      <c r="I38" s="80"/>
+      <c r="J38" s="80"/>
+      <c r="K38" s="80"/>
+      <c r="L38" s="80"/>
+      <c r="M38" s="80"/>
+      <c r="N38" s="80"/>
+      <c r="O38" s="80"/>
+      <c r="P38" s="80"/>
+      <c r="Q38" s="80"/>
+      <c r="R38" s="80"/>
+      <c r="S38" s="80"/>
+      <c r="T38" s="80"/>
+      <c r="U38" s="54"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="60">
+      <c r="A39" s="75">
         <v>6</v>
       </c>
       <c r="B39" s="28" t="s">
@@ -3004,81 +3141,81 @@
       <c r="C39" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="56"/>
-      <c r="E39" s="56"/>
-      <c r="F39" s="56"/>
-      <c r="G39" s="56"/>
-      <c r="H39" s="56"/>
-      <c r="I39" s="56"/>
-      <c r="J39" s="56"/>
-      <c r="K39" s="56"/>
-      <c r="L39" s="56"/>
-      <c r="M39" s="56"/>
-      <c r="N39" s="56"/>
-      <c r="O39" s="56"/>
-      <c r="P39" s="56"/>
-      <c r="Q39" s="56"/>
-      <c r="R39" s="56"/>
-      <c r="S39" s="56"/>
-      <c r="T39" s="56"/>
-      <c r="U39" s="57"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="80"/>
+      <c r="F39" s="80"/>
+      <c r="G39" s="80"/>
+      <c r="H39" s="80"/>
+      <c r="I39" s="80"/>
+      <c r="J39" s="80"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="80"/>
+      <c r="M39" s="80"/>
+      <c r="N39" s="80"/>
+      <c r="O39" s="80"/>
+      <c r="P39" s="80"/>
+      <c r="Q39" s="80"/>
+      <c r="R39" s="80"/>
+      <c r="S39" s="80"/>
+      <c r="T39" s="80"/>
+      <c r="U39" s="54"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="60"/>
+      <c r="A40" s="76"/>
       <c r="B40" s="28" t="s">
         <v>79</v>
       </c>
       <c r="C40" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="D40" s="56"/>
-      <c r="E40" s="56"/>
-      <c r="F40" s="56"/>
-      <c r="G40" s="56"/>
-      <c r="H40" s="56"/>
-      <c r="I40" s="56"/>
-      <c r="J40" s="56"/>
-      <c r="K40" s="56"/>
-      <c r="L40" s="56"/>
-      <c r="M40" s="56"/>
-      <c r="N40" s="56"/>
-      <c r="O40" s="56"/>
-      <c r="P40" s="56"/>
-      <c r="Q40" s="56"/>
-      <c r="R40" s="56"/>
-      <c r="S40" s="56"/>
-      <c r="T40" s="56"/>
-      <c r="U40" s="57"/>
+      <c r="D40" s="79"/>
+      <c r="E40" s="80"/>
+      <c r="F40" s="80"/>
+      <c r="G40" s="80"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="80"/>
+      <c r="J40" s="80"/>
+      <c r="K40" s="80"/>
+      <c r="L40" s="80"/>
+      <c r="M40" s="80"/>
+      <c r="N40" s="80"/>
+      <c r="O40" s="80"/>
+      <c r="P40" s="80"/>
+      <c r="Q40" s="80"/>
+      <c r="R40" s="80"/>
+      <c r="S40" s="80"/>
+      <c r="T40" s="80"/>
+      <c r="U40" s="54"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="60"/>
+      <c r="A41" s="76"/>
       <c r="B41" s="28" t="s">
         <v>80</v>
       </c>
       <c r="C41" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D41" s="58"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="58"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="58"/>
-      <c r="K41" s="58"/>
-      <c r="L41" s="58"/>
-      <c r="M41" s="58"/>
-      <c r="N41" s="58"/>
-      <c r="O41" s="58"/>
-      <c r="P41" s="58"/>
-      <c r="Q41" s="58"/>
-      <c r="R41" s="58"/>
-      <c r="S41" s="58"/>
-      <c r="T41" s="58"/>
-      <c r="U41" s="59"/>
+      <c r="D41" s="81"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="55"/>
+      <c r="J41" s="55"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="55"/>
+      <c r="M41" s="55"/>
+      <c r="N41" s="55"/>
+      <c r="O41" s="55"/>
+      <c r="P41" s="55"/>
+      <c r="Q41" s="55"/>
+      <c r="R41" s="55"/>
+      <c r="S41" s="55"/>
+      <c r="T41" s="55"/>
+      <c r="U41" s="56"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="60"/>
+      <c r="A42" s="76"/>
       <c r="B42" s="29" t="s">
         <v>81</v>
       </c>
@@ -3119,7 +3256,7 @@
       </c>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="60"/>
+      <c r="A43" s="76"/>
       <c r="B43" s="29" t="s">
         <v>82</v>
       </c>
@@ -3148,7 +3285,7 @@
       <c r="U43" s="16"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="60"/>
+      <c r="A44" s="76"/>
       <c r="B44" s="30" t="s">
         <v>83</v>
       </c>
@@ -3175,7 +3312,7 @@
       <c r="U44" s="24"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="60"/>
+      <c r="A45" s="77"/>
       <c r="B45" s="29" t="s">
         <v>84</v>
       </c>
@@ -3202,7 +3339,7 @@
       <c r="U45" s="16"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="53">
+      <c r="A46" s="82">
         <v>7</v>
       </c>
       <c r="B46" s="31" t="s">
@@ -3251,7 +3388,7 @@
       <c r="U46" s="5"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="53"/>
+      <c r="A47" s="83"/>
       <c r="B47" s="31" t="s">
         <v>86</v>
       </c>
@@ -3298,7 +3435,7 @@
       <c r="U47" s="5"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="53"/>
+      <c r="A48" s="83"/>
       <c r="B48" s="31" t="s">
         <v>87</v>
       </c>
@@ -3345,7 +3482,7 @@
       <c r="U48" s="5"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="53"/>
+      <c r="A49" s="83"/>
       <c r="B49" s="31" t="s">
         <v>88</v>
       </c>
@@ -3392,7 +3529,7 @@
       <c r="U49" s="5"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="53"/>
+      <c r="A50" s="83"/>
       <c r="B50" s="31" t="s">
         <v>89</v>
       </c>
@@ -3439,7 +3576,7 @@
       <c r="U50" s="5"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="53"/>
+      <c r="A51" s="83"/>
       <c r="B51" s="31" t="s">
         <v>90</v>
       </c>
@@ -3466,7 +3603,7 @@
       <c r="U51" s="5"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="53"/>
+      <c r="A52" s="84"/>
       <c r="B52" s="31" t="s">
         <v>91</v>
       </c>
@@ -3493,7 +3630,7 @@
       <c r="U52" s="5"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="60">
+      <c r="A53" s="75">
         <v>8</v>
       </c>
       <c r="B53" s="29" t="s">
@@ -3542,7 +3679,7 @@
       <c r="U53" s="16"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="60"/>
+      <c r="A54" s="76"/>
       <c r="B54" s="29" t="s">
         <v>93</v>
       </c>
@@ -3583,7 +3720,7 @@
       <c r="U54" s="16"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="60"/>
+      <c r="A55" s="76"/>
       <c r="B55" s="29" t="s">
         <v>94</v>
       </c>
@@ -3630,7 +3767,7 @@
       <c r="U55" s="16"/>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="60"/>
+      <c r="A56" s="76"/>
       <c r="B56" s="29" t="s">
         <v>95</v>
       </c>
@@ -3683,7 +3820,7 @@
       </c>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="60"/>
+      <c r="A57" s="76"/>
       <c r="B57" s="29" t="s">
         <v>96</v>
       </c>
@@ -3730,7 +3867,7 @@
       <c r="U57" s="16"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="60"/>
+      <c r="A58" s="76"/>
       <c r="B58" s="29" t="s">
         <v>97</v>
       </c>
@@ -3757,7 +3894,7 @@
       <c r="U58" s="16"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="60"/>
+      <c r="A59" s="77"/>
       <c r="B59" s="29" t="s">
         <v>98</v>
       </c>
@@ -3784,7 +3921,7 @@
       <c r="U59" s="16"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="53">
+      <c r="A60" s="82">
         <v>9</v>
       </c>
       <c r="B60" s="31" t="s">
@@ -3833,7 +3970,7 @@
       <c r="U60" s="5"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="53"/>
+      <c r="A61" s="83"/>
       <c r="B61" s="31" t="s">
         <v>100</v>
       </c>
@@ -3880,7 +4017,7 @@
       <c r="U61" s="5"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="53"/>
+      <c r="A62" s="83"/>
       <c r="B62" s="31" t="s">
         <v>101</v>
       </c>
@@ -3927,7 +4064,7 @@
       <c r="U62" s="5"/>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="53"/>
+      <c r="A63" s="83"/>
       <c r="B63" s="31" t="s">
         <v>102</v>
       </c>
@@ -3980,7 +4117,7 @@
       </c>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="53"/>
+      <c r="A64" s="83"/>
       <c r="B64" s="31" t="s">
         <v>103</v>
       </c>
@@ -4021,40 +4158,15 @@
       <c r="U64" s="6"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="53"/>
+      <c r="A65" s="83"/>
       <c r="B65" s="31" t="s">
         <v>104</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D65" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H65" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I65" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J65" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K65" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L65" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="F65" s="5"/>
+      <c r="I65" s="5"/>
       <c r="M65" s="2"/>
       <c r="N65" s="4"/>
       <c r="O65" s="6"/>
@@ -4066,7 +4178,7 @@
       <c r="U65" s="6"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="53"/>
+      <c r="A66" s="84"/>
       <c r="B66" s="31" t="s">
         <v>105</v>
       </c>
@@ -4093,7 +4205,7 @@
       <c r="U66" s="6"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="60">
+      <c r="A67" s="75">
         <v>10</v>
       </c>
       <c r="B67" s="29" t="s">
@@ -4142,7 +4254,7 @@
       <c r="U67" s="17"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="60"/>
+      <c r="A68" s="76"/>
       <c r="B68" s="29" t="s">
         <v>107</v>
       </c>
@@ -4183,7 +4295,7 @@
       <c r="U68" s="17"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="60"/>
+      <c r="A69" s="76"/>
       <c r="B69" s="29" t="s">
         <v>108</v>
       </c>
@@ -4230,7 +4342,7 @@
       <c r="U69" s="17"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="60"/>
+      <c r="A70" s="76"/>
       <c r="B70" s="29" t="s">
         <v>109</v>
       </c>
@@ -4283,7 +4395,7 @@
       </c>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="60"/>
+      <c r="A71" s="76"/>
       <c r="B71" s="29" t="s">
         <v>110</v>
       </c>
@@ -4330,7 +4442,7 @@
       <c r="U71" s="17"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="60"/>
+      <c r="A72" s="76"/>
       <c r="B72" s="29" t="s">
         <v>111</v>
       </c>
@@ -4375,7 +4487,7 @@
       <c r="U72" s="17"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="60"/>
+      <c r="A73" s="77"/>
       <c r="B73" s="29" t="s">
         <v>112</v>
       </c>
@@ -4402,7 +4514,7 @@
       <c r="U73" s="17"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="53">
+      <c r="A74" s="82">
         <v>11</v>
       </c>
       <c r="B74" s="31" t="s">
@@ -4445,7 +4557,7 @@
       <c r="U74" s="6"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="53"/>
+      <c r="A75" s="83"/>
       <c r="B75" s="31" t="s">
         <v>114</v>
       </c>
@@ -4486,7 +4598,7 @@
       <c r="U75" s="6"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="53"/>
+      <c r="A76" s="83"/>
       <c r="B76" s="31" t="s">
         <v>115</v>
       </c>
@@ -4527,7 +4639,7 @@
       <c r="U76" s="6"/>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="53"/>
+      <c r="A77" s="83"/>
       <c r="B77" s="31" t="s">
         <v>116</v>
       </c>
@@ -4568,7 +4680,7 @@
       <c r="U77" s="5"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="53"/>
+      <c r="A78" s="83"/>
       <c r="B78" s="31" t="s">
         <v>117</v>
       </c>
@@ -4615,7 +4727,7 @@
       <c r="U78" s="5"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="53"/>
+      <c r="A79" s="83"/>
       <c r="B79" s="31" t="s">
         <v>118</v>
       </c>
@@ -4660,7 +4772,7 @@
       <c r="U79" s="5"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="53"/>
+      <c r="A80" s="84"/>
       <c r="B80" s="31" t="s">
         <v>119</v>
       </c>
@@ -4687,7 +4799,7 @@
       <c r="U80" s="5"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="60">
+      <c r="A81" s="75">
         <v>12</v>
       </c>
       <c r="B81" s="29" t="s">
@@ -4696,191 +4808,191 @@
       <c r="C81" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D81" s="69" t="s">
+      <c r="D81" s="85" t="s">
         <v>121</v>
       </c>
-      <c r="E81" s="69"/>
-      <c r="F81" s="69"/>
-      <c r="G81" s="69"/>
-      <c r="H81" s="69"/>
-      <c r="I81" s="69"/>
-      <c r="J81" s="69"/>
-      <c r="K81" s="69"/>
-      <c r="L81" s="69"/>
-      <c r="M81" s="69"/>
-      <c r="N81" s="69"/>
-      <c r="O81" s="69"/>
-      <c r="P81" s="69"/>
-      <c r="Q81" s="69"/>
-      <c r="R81" s="69"/>
-      <c r="S81" s="69"/>
-      <c r="T81" s="69"/>
-      <c r="U81" s="70"/>
+      <c r="E81" s="63"/>
+      <c r="F81" s="63"/>
+      <c r="G81" s="63"/>
+      <c r="H81" s="63"/>
+      <c r="I81" s="63"/>
+      <c r="J81" s="63"/>
+      <c r="K81" s="63"/>
+      <c r="L81" s="63"/>
+      <c r="M81" s="63"/>
+      <c r="N81" s="63"/>
+      <c r="O81" s="63"/>
+      <c r="P81" s="63"/>
+      <c r="Q81" s="63"/>
+      <c r="R81" s="63"/>
+      <c r="S81" s="63"/>
+      <c r="T81" s="63"/>
+      <c r="U81" s="64"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="60"/>
+      <c r="A82" s="76"/>
       <c r="B82" s="29" t="s">
         <v>122</v>
       </c>
       <c r="C82" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D82" s="71"/>
-      <c r="E82" s="71"/>
-      <c r="F82" s="71"/>
-      <c r="G82" s="71"/>
-      <c r="H82" s="71"/>
-      <c r="I82" s="71"/>
-      <c r="J82" s="71"/>
-      <c r="K82" s="71"/>
-      <c r="L82" s="71"/>
-      <c r="M82" s="71"/>
-      <c r="N82" s="71"/>
-      <c r="O82" s="71"/>
-      <c r="P82" s="71"/>
-      <c r="Q82" s="71"/>
-      <c r="R82" s="71"/>
-      <c r="S82" s="71"/>
-      <c r="T82" s="71"/>
-      <c r="U82" s="72"/>
+      <c r="D82" s="86"/>
+      <c r="E82" s="87"/>
+      <c r="F82" s="87"/>
+      <c r="G82" s="87"/>
+      <c r="H82" s="87"/>
+      <c r="I82" s="87"/>
+      <c r="J82" s="87"/>
+      <c r="K82" s="87"/>
+      <c r="L82" s="87"/>
+      <c r="M82" s="87"/>
+      <c r="N82" s="87"/>
+      <c r="O82" s="87"/>
+      <c r="P82" s="87"/>
+      <c r="Q82" s="87"/>
+      <c r="R82" s="87"/>
+      <c r="S82" s="87"/>
+      <c r="T82" s="87"/>
+      <c r="U82" s="65"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="60"/>
+      <c r="A83" s="76"/>
       <c r="B83" s="29" t="s">
         <v>123</v>
       </c>
       <c r="C83" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D83" s="71"/>
-      <c r="E83" s="71"/>
-      <c r="F83" s="71"/>
-      <c r="G83" s="71"/>
-      <c r="H83" s="71"/>
-      <c r="I83" s="71"/>
-      <c r="J83" s="71"/>
-      <c r="K83" s="71"/>
-      <c r="L83" s="71"/>
-      <c r="M83" s="71"/>
-      <c r="N83" s="71"/>
-      <c r="O83" s="71"/>
-      <c r="P83" s="71"/>
-      <c r="Q83" s="71"/>
-      <c r="R83" s="71"/>
-      <c r="S83" s="71"/>
-      <c r="T83" s="71"/>
-      <c r="U83" s="72"/>
+      <c r="D83" s="86"/>
+      <c r="E83" s="87"/>
+      <c r="F83" s="87"/>
+      <c r="G83" s="87"/>
+      <c r="H83" s="87"/>
+      <c r="I83" s="87"/>
+      <c r="J83" s="87"/>
+      <c r="K83" s="87"/>
+      <c r="L83" s="87"/>
+      <c r="M83" s="87"/>
+      <c r="N83" s="87"/>
+      <c r="O83" s="87"/>
+      <c r="P83" s="87"/>
+      <c r="Q83" s="87"/>
+      <c r="R83" s="87"/>
+      <c r="S83" s="87"/>
+      <c r="T83" s="87"/>
+      <c r="U83" s="65"/>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="60"/>
+      <c r="A84" s="76"/>
       <c r="B84" s="29" t="s">
         <v>124</v>
       </c>
       <c r="C84" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D84" s="71"/>
-      <c r="E84" s="71"/>
-      <c r="F84" s="71"/>
-      <c r="G84" s="71"/>
-      <c r="H84" s="71"/>
-      <c r="I84" s="71"/>
-      <c r="J84" s="71"/>
-      <c r="K84" s="71"/>
-      <c r="L84" s="71"/>
-      <c r="M84" s="71"/>
-      <c r="N84" s="71"/>
-      <c r="O84" s="71"/>
-      <c r="P84" s="71"/>
-      <c r="Q84" s="71"/>
-      <c r="R84" s="71"/>
-      <c r="S84" s="71"/>
-      <c r="T84" s="71"/>
-      <c r="U84" s="72"/>
+      <c r="D84" s="86"/>
+      <c r="E84" s="87"/>
+      <c r="F84" s="87"/>
+      <c r="G84" s="87"/>
+      <c r="H84" s="87"/>
+      <c r="I84" s="87"/>
+      <c r="J84" s="87"/>
+      <c r="K84" s="87"/>
+      <c r="L84" s="87"/>
+      <c r="M84" s="87"/>
+      <c r="N84" s="87"/>
+      <c r="O84" s="87"/>
+      <c r="P84" s="87"/>
+      <c r="Q84" s="87"/>
+      <c r="R84" s="87"/>
+      <c r="S84" s="87"/>
+      <c r="T84" s="87"/>
+      <c r="U84" s="65"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="60"/>
+      <c r="A85" s="76"/>
       <c r="B85" s="29" t="s">
         <v>125</v>
       </c>
       <c r="C85" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D85" s="71"/>
-      <c r="E85" s="71"/>
-      <c r="F85" s="71"/>
-      <c r="G85" s="71"/>
-      <c r="H85" s="71"/>
-      <c r="I85" s="71"/>
-      <c r="J85" s="71"/>
-      <c r="K85" s="71"/>
-      <c r="L85" s="71"/>
-      <c r="M85" s="71"/>
-      <c r="N85" s="71"/>
-      <c r="O85" s="71"/>
-      <c r="P85" s="71"/>
-      <c r="Q85" s="71"/>
-      <c r="R85" s="71"/>
-      <c r="S85" s="71"/>
-      <c r="T85" s="71"/>
-      <c r="U85" s="72"/>
+      <c r="D85" s="86"/>
+      <c r="E85" s="87"/>
+      <c r="F85" s="87"/>
+      <c r="G85" s="87"/>
+      <c r="H85" s="87"/>
+      <c r="I85" s="87"/>
+      <c r="J85" s="87"/>
+      <c r="K85" s="87"/>
+      <c r="L85" s="87"/>
+      <c r="M85" s="87"/>
+      <c r="N85" s="87"/>
+      <c r="O85" s="87"/>
+      <c r="P85" s="87"/>
+      <c r="Q85" s="87"/>
+      <c r="R85" s="87"/>
+      <c r="S85" s="87"/>
+      <c r="T85" s="87"/>
+      <c r="U85" s="65"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="60"/>
+      <c r="A86" s="76"/>
       <c r="B86" s="29" t="s">
         <v>126</v>
       </c>
       <c r="C86" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D86" s="71"/>
-      <c r="E86" s="71"/>
-      <c r="F86" s="71"/>
-      <c r="G86" s="71"/>
-      <c r="H86" s="71"/>
-      <c r="I86" s="71"/>
-      <c r="J86" s="71"/>
-      <c r="K86" s="71"/>
-      <c r="L86" s="71"/>
-      <c r="M86" s="71"/>
-      <c r="N86" s="71"/>
-      <c r="O86" s="71"/>
-      <c r="P86" s="71"/>
-      <c r="Q86" s="71"/>
-      <c r="R86" s="71"/>
-      <c r="S86" s="71"/>
-      <c r="T86" s="71"/>
-      <c r="U86" s="72"/>
+      <c r="D86" s="86"/>
+      <c r="E86" s="87"/>
+      <c r="F86" s="87"/>
+      <c r="G86" s="87"/>
+      <c r="H86" s="87"/>
+      <c r="I86" s="87"/>
+      <c r="J86" s="87"/>
+      <c r="K86" s="87"/>
+      <c r="L86" s="87"/>
+      <c r="M86" s="87"/>
+      <c r="N86" s="87"/>
+      <c r="O86" s="87"/>
+      <c r="P86" s="87"/>
+      <c r="Q86" s="87"/>
+      <c r="R86" s="87"/>
+      <c r="S86" s="87"/>
+      <c r="T86" s="87"/>
+      <c r="U86" s="65"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="60"/>
+      <c r="A87" s="77"/>
       <c r="B87" s="29" t="s">
         <v>127</v>
       </c>
       <c r="C87" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D87" s="71"/>
-      <c r="E87" s="71"/>
-      <c r="F87" s="71"/>
-      <c r="G87" s="71"/>
-      <c r="H87" s="71"/>
-      <c r="I87" s="71"/>
-      <c r="J87" s="71"/>
-      <c r="K87" s="71"/>
-      <c r="L87" s="71"/>
-      <c r="M87" s="71"/>
-      <c r="N87" s="71"/>
-      <c r="O87" s="71"/>
-      <c r="P87" s="71"/>
-      <c r="Q87" s="71"/>
-      <c r="R87" s="71"/>
-      <c r="S87" s="71"/>
-      <c r="T87" s="71"/>
-      <c r="U87" s="72"/>
+      <c r="D87" s="86"/>
+      <c r="E87" s="87"/>
+      <c r="F87" s="87"/>
+      <c r="G87" s="87"/>
+      <c r="H87" s="87"/>
+      <c r="I87" s="87"/>
+      <c r="J87" s="87"/>
+      <c r="K87" s="87"/>
+      <c r="L87" s="87"/>
+      <c r="M87" s="87"/>
+      <c r="N87" s="87"/>
+      <c r="O87" s="87"/>
+      <c r="P87" s="87"/>
+      <c r="Q87" s="87"/>
+      <c r="R87" s="87"/>
+      <c r="S87" s="87"/>
+      <c r="T87" s="87"/>
+      <c r="U87" s="65"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="53">
+      <c r="A88" s="82">
         <v>13</v>
       </c>
       <c r="B88" s="31" t="s">
@@ -4889,189 +5001,189 @@
       <c r="C88" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D88" s="71"/>
-      <c r="E88" s="71"/>
-      <c r="F88" s="71"/>
-      <c r="G88" s="71"/>
-      <c r="H88" s="71"/>
-      <c r="I88" s="71"/>
-      <c r="J88" s="71"/>
-      <c r="K88" s="71"/>
-      <c r="L88" s="71"/>
-      <c r="M88" s="71"/>
-      <c r="N88" s="71"/>
-      <c r="O88" s="71"/>
-      <c r="P88" s="71"/>
-      <c r="Q88" s="71"/>
-      <c r="R88" s="71"/>
-      <c r="S88" s="71"/>
-      <c r="T88" s="71"/>
-      <c r="U88" s="72"/>
+      <c r="D88" s="86"/>
+      <c r="E88" s="87"/>
+      <c r="F88" s="87"/>
+      <c r="G88" s="87"/>
+      <c r="H88" s="87"/>
+      <c r="I88" s="87"/>
+      <c r="J88" s="87"/>
+      <c r="K88" s="87"/>
+      <c r="L88" s="87"/>
+      <c r="M88" s="87"/>
+      <c r="N88" s="87"/>
+      <c r="O88" s="87"/>
+      <c r="P88" s="87"/>
+      <c r="Q88" s="87"/>
+      <c r="R88" s="87"/>
+      <c r="S88" s="87"/>
+      <c r="T88" s="87"/>
+      <c r="U88" s="65"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="53"/>
+      <c r="A89" s="83"/>
       <c r="B89" s="31" t="s">
         <v>129</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D89" s="71"/>
-      <c r="E89" s="71"/>
-      <c r="F89" s="71"/>
-      <c r="G89" s="71"/>
-      <c r="H89" s="71"/>
-      <c r="I89" s="71"/>
-      <c r="J89" s="71"/>
-      <c r="K89" s="71"/>
-      <c r="L89" s="71"/>
-      <c r="M89" s="71"/>
-      <c r="N89" s="71"/>
-      <c r="O89" s="71"/>
-      <c r="P89" s="71"/>
-      <c r="Q89" s="71"/>
-      <c r="R89" s="71"/>
-      <c r="S89" s="71"/>
-      <c r="T89" s="71"/>
-      <c r="U89" s="72"/>
+      <c r="D89" s="86"/>
+      <c r="E89" s="87"/>
+      <c r="F89" s="87"/>
+      <c r="G89" s="87"/>
+      <c r="H89" s="87"/>
+      <c r="I89" s="87"/>
+      <c r="J89" s="87"/>
+      <c r="K89" s="87"/>
+      <c r="L89" s="87"/>
+      <c r="M89" s="87"/>
+      <c r="N89" s="87"/>
+      <c r="O89" s="87"/>
+      <c r="P89" s="87"/>
+      <c r="Q89" s="87"/>
+      <c r="R89" s="87"/>
+      <c r="S89" s="87"/>
+      <c r="T89" s="87"/>
+      <c r="U89" s="65"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="53"/>
+      <c r="A90" s="83"/>
       <c r="B90" s="31" t="s">
         <v>130</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D90" s="71"/>
-      <c r="E90" s="71"/>
-      <c r="F90" s="71"/>
-      <c r="G90" s="71"/>
-      <c r="H90" s="71"/>
-      <c r="I90" s="71"/>
-      <c r="J90" s="71"/>
-      <c r="K90" s="71"/>
-      <c r="L90" s="71"/>
-      <c r="M90" s="71"/>
-      <c r="N90" s="71"/>
-      <c r="O90" s="71"/>
-      <c r="P90" s="71"/>
-      <c r="Q90" s="71"/>
-      <c r="R90" s="71"/>
-      <c r="S90" s="71"/>
-      <c r="T90" s="71"/>
-      <c r="U90" s="72"/>
+      <c r="D90" s="86"/>
+      <c r="E90" s="87"/>
+      <c r="F90" s="87"/>
+      <c r="G90" s="87"/>
+      <c r="H90" s="87"/>
+      <c r="I90" s="87"/>
+      <c r="J90" s="87"/>
+      <c r="K90" s="87"/>
+      <c r="L90" s="87"/>
+      <c r="M90" s="87"/>
+      <c r="N90" s="87"/>
+      <c r="O90" s="87"/>
+      <c r="P90" s="87"/>
+      <c r="Q90" s="87"/>
+      <c r="R90" s="87"/>
+      <c r="S90" s="87"/>
+      <c r="T90" s="87"/>
+      <c r="U90" s="65"/>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="53"/>
+      <c r="A91" s="83"/>
       <c r="B91" s="31" t="s">
         <v>131</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D91" s="71"/>
-      <c r="E91" s="71"/>
-      <c r="F91" s="71"/>
-      <c r="G91" s="71"/>
-      <c r="H91" s="71"/>
-      <c r="I91" s="71"/>
-      <c r="J91" s="71"/>
-      <c r="K91" s="71"/>
-      <c r="L91" s="71"/>
-      <c r="M91" s="71"/>
-      <c r="N91" s="71"/>
-      <c r="O91" s="71"/>
-      <c r="P91" s="71"/>
-      <c r="Q91" s="71"/>
-      <c r="R91" s="71"/>
-      <c r="S91" s="71"/>
-      <c r="T91" s="71"/>
-      <c r="U91" s="72"/>
+      <c r="D91" s="86"/>
+      <c r="E91" s="87"/>
+      <c r="F91" s="87"/>
+      <c r="G91" s="87"/>
+      <c r="H91" s="87"/>
+      <c r="I91" s="87"/>
+      <c r="J91" s="87"/>
+      <c r="K91" s="87"/>
+      <c r="L91" s="87"/>
+      <c r="M91" s="87"/>
+      <c r="N91" s="87"/>
+      <c r="O91" s="87"/>
+      <c r="P91" s="87"/>
+      <c r="Q91" s="87"/>
+      <c r="R91" s="87"/>
+      <c r="S91" s="87"/>
+      <c r="T91" s="87"/>
+      <c r="U91" s="65"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="53"/>
+      <c r="A92" s="83"/>
       <c r="B92" s="31" t="s">
         <v>132</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D92" s="71"/>
-      <c r="E92" s="71"/>
-      <c r="F92" s="71"/>
-      <c r="G92" s="71"/>
-      <c r="H92" s="71"/>
-      <c r="I92" s="71"/>
-      <c r="J92" s="71"/>
-      <c r="K92" s="71"/>
-      <c r="L92" s="71"/>
-      <c r="M92" s="71"/>
-      <c r="N92" s="71"/>
-      <c r="O92" s="71"/>
-      <c r="P92" s="71"/>
-      <c r="Q92" s="71"/>
-      <c r="R92" s="71"/>
-      <c r="S92" s="71"/>
-      <c r="T92" s="71"/>
-      <c r="U92" s="72"/>
+      <c r="D92" s="86"/>
+      <c r="E92" s="87"/>
+      <c r="F92" s="87"/>
+      <c r="G92" s="87"/>
+      <c r="H92" s="87"/>
+      <c r="I92" s="87"/>
+      <c r="J92" s="87"/>
+      <c r="K92" s="87"/>
+      <c r="L92" s="87"/>
+      <c r="M92" s="87"/>
+      <c r="N92" s="87"/>
+      <c r="O92" s="87"/>
+      <c r="P92" s="87"/>
+      <c r="Q92" s="87"/>
+      <c r="R92" s="87"/>
+      <c r="S92" s="87"/>
+      <c r="T92" s="87"/>
+      <c r="U92" s="65"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="53"/>
+      <c r="A93" s="83"/>
       <c r="B93" s="31" t="s">
         <v>133</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D93" s="71"/>
-      <c r="E93" s="71"/>
-      <c r="F93" s="71"/>
-      <c r="G93" s="71"/>
-      <c r="H93" s="71"/>
-      <c r="I93" s="71"/>
-      <c r="J93" s="71"/>
-      <c r="K93" s="71"/>
-      <c r="L93" s="71"/>
-      <c r="M93" s="71"/>
-      <c r="N93" s="71"/>
-      <c r="O93" s="71"/>
-      <c r="P93" s="71"/>
-      <c r="Q93" s="71"/>
-      <c r="R93" s="71"/>
-      <c r="S93" s="71"/>
-      <c r="T93" s="71"/>
-      <c r="U93" s="72"/>
+      <c r="D93" s="86"/>
+      <c r="E93" s="87"/>
+      <c r="F93" s="87"/>
+      <c r="G93" s="87"/>
+      <c r="H93" s="87"/>
+      <c r="I93" s="87"/>
+      <c r="J93" s="87"/>
+      <c r="K93" s="87"/>
+      <c r="L93" s="87"/>
+      <c r="M93" s="87"/>
+      <c r="N93" s="87"/>
+      <c r="O93" s="87"/>
+      <c r="P93" s="87"/>
+      <c r="Q93" s="87"/>
+      <c r="R93" s="87"/>
+      <c r="S93" s="87"/>
+      <c r="T93" s="87"/>
+      <c r="U93" s="65"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="53"/>
+      <c r="A94" s="84"/>
       <c r="B94" s="31" t="s">
         <v>134</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D94" s="73"/>
-      <c r="E94" s="73"/>
-      <c r="F94" s="73"/>
-      <c r="G94" s="73"/>
-      <c r="H94" s="73"/>
-      <c r="I94" s="73"/>
-      <c r="J94" s="73"/>
-      <c r="K94" s="73"/>
-      <c r="L94" s="73"/>
-      <c r="M94" s="73"/>
-      <c r="N94" s="73"/>
-      <c r="O94" s="73"/>
-      <c r="P94" s="73"/>
-      <c r="Q94" s="73"/>
-      <c r="R94" s="73"/>
-      <c r="S94" s="73"/>
-      <c r="T94" s="73"/>
-      <c r="U94" s="74"/>
+      <c r="D94" s="88"/>
+      <c r="E94" s="66"/>
+      <c r="F94" s="66"/>
+      <c r="G94" s="66"/>
+      <c r="H94" s="66"/>
+      <c r="I94" s="66"/>
+      <c r="J94" s="66"/>
+      <c r="K94" s="66"/>
+      <c r="L94" s="66"/>
+      <c r="M94" s="66"/>
+      <c r="N94" s="66"/>
+      <c r="O94" s="66"/>
+      <c r="P94" s="66"/>
+      <c r="Q94" s="66"/>
+      <c r="R94" s="66"/>
+      <c r="S94" s="66"/>
+      <c r="T94" s="66"/>
+      <c r="U94" s="67"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="60">
+      <c r="A95" s="75">
         <v>14</v>
       </c>
       <c r="B95" s="29" t="s">
@@ -5104,7 +5216,7 @@
       <c r="U95" s="16"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="60"/>
+      <c r="A96" s="76"/>
       <c r="B96" s="29" t="s">
         <v>137</v>
       </c>
@@ -5135,7 +5247,7 @@
       <c r="U96" s="16"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="60"/>
+      <c r="A97" s="76"/>
       <c r="B97" s="29" t="s">
         <v>138</v>
       </c>
@@ -5166,7 +5278,7 @@
       <c r="U97" s="16"/>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="60"/>
+      <c r="A98" s="76"/>
       <c r="B98" s="29" t="s">
         <v>139</v>
       </c>
@@ -5197,7 +5309,7 @@
       <c r="U98" s="16"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="60"/>
+      <c r="A99" s="76"/>
       <c r="B99" s="29" t="s">
         <v>140</v>
       </c>
@@ -5228,7 +5340,7 @@
       <c r="U99" s="16"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="60"/>
+      <c r="A100" s="76"/>
       <c r="B100" s="29" t="s">
         <v>141</v>
       </c>
@@ -5259,7 +5371,7 @@
       <c r="U100" s="16"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="60"/>
+      <c r="A101" s="77"/>
       <c r="B101" s="29" t="s">
         <v>142</v>
       </c>
@@ -5290,7 +5402,7 @@
       <c r="U101" s="16"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="53">
+      <c r="A102" s="82">
         <v>15</v>
       </c>
       <c r="B102" s="31" t="s">
@@ -5323,7 +5435,7 @@
       <c r="U102" s="5"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="53"/>
+      <c r="A103" s="83"/>
       <c r="B103" s="31" t="s">
         <v>144</v>
       </c>
@@ -5354,7 +5466,7 @@
       <c r="U103" s="5"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="53"/>
+      <c r="A104" s="83"/>
       <c r="B104" s="31" t="s">
         <v>145</v>
       </c>
@@ -5385,7 +5497,7 @@
       <c r="U104" s="5"/>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="53"/>
+      <c r="A105" s="83"/>
       <c r="B105" s="31" t="s">
         <v>146</v>
       </c>
@@ -5416,7 +5528,7 @@
       <c r="U105" s="5"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="53"/>
+      <c r="A106" s="83"/>
       <c r="B106" s="31" t="s">
         <v>147</v>
       </c>
@@ -5447,7 +5559,7 @@
       <c r="U106" s="5"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="53"/>
+      <c r="A107" s="83"/>
       <c r="B107" s="31" t="s">
         <v>148</v>
       </c>
@@ -5478,7 +5590,7 @@
       <c r="U107" s="5"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="53"/>
+      <c r="A108" s="84"/>
       <c r="B108" s="31" t="s">
         <v>149</v>
       </c>
@@ -5509,7 +5621,7 @@
       <c r="U108" s="5"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="60">
+      <c r="A109" s="75">
         <v>16</v>
       </c>
       <c r="B109" s="29" t="s">
@@ -5542,7 +5654,7 @@
       <c r="U109" s="17"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="60"/>
+      <c r="A110" s="76"/>
       <c r="B110" s="29" t="s">
         <v>151</v>
       </c>
@@ -5573,7 +5685,7 @@
       <c r="U110" s="17"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="60"/>
+      <c r="A111" s="76"/>
       <c r="B111" s="29" t="s">
         <v>152</v>
       </c>
@@ -5604,7 +5716,7 @@
       <c r="U111" s="17"/>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="60"/>
+      <c r="A112" s="76"/>
       <c r="B112" s="29" t="s">
         <v>153</v>
       </c>
@@ -5635,7 +5747,7 @@
       <c r="U112" s="17"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="60"/>
+      <c r="A113" s="76"/>
       <c r="B113" s="29" t="s">
         <v>154</v>
       </c>
@@ -5666,7 +5778,7 @@
       <c r="U113" s="17"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="60"/>
+      <c r="A114" s="76"/>
       <c r="B114" s="29" t="s">
         <v>155</v>
       </c>
@@ -5697,7 +5809,7 @@
       <c r="U114" s="17"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="60"/>
+      <c r="A115" s="77"/>
       <c r="B115" s="29" t="s">
         <v>156</v>
       </c>
@@ -5728,7 +5840,7 @@
       <c r="U115" s="17"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="53">
+      <c r="A116" s="82">
         <v>17</v>
       </c>
       <c r="B116" s="31" t="s">
@@ -5761,7 +5873,7 @@
       <c r="U116" s="5"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="53"/>
+      <c r="A117" s="83"/>
       <c r="B117" s="31" t="s">
         <v>158</v>
       </c>
@@ -5792,7 +5904,7 @@
       <c r="U117" s="5"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="53"/>
+      <c r="A118" s="83"/>
       <c r="B118" s="31" t="s">
         <v>159</v>
       </c>
@@ -5823,7 +5935,7 @@
       <c r="U118" s="5"/>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="53"/>
+      <c r="A119" s="83"/>
       <c r="B119" s="31" t="s">
         <v>160</v>
       </c>
@@ -5854,7 +5966,7 @@
       <c r="U119" s="5"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="53"/>
+      <c r="A120" s="83"/>
       <c r="B120" s="31" t="s">
         <v>161</v>
       </c>
@@ -5885,7 +5997,7 @@
       <c r="U120" s="5"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="53"/>
+      <c r="A121" s="83"/>
       <c r="B121" s="31" t="s">
         <v>162</v>
       </c>
@@ -5916,7 +6028,7 @@
       <c r="U121" s="5"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="53"/>
+      <c r="A122" s="84"/>
       <c r="B122" s="31" t="s">
         <v>163</v>
       </c>
@@ -5947,7 +6059,7 @@
       <c r="U122" s="5"/>
     </row>
     <row r="123" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="60">
+      <c r="A123" s="75">
         <v>18</v>
       </c>
       <c r="B123" s="29" t="s">
@@ -5980,7 +6092,7 @@
       <c r="U123" s="17"/>
     </row>
     <row r="124" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="60"/>
+      <c r="A124" s="76"/>
       <c r="B124" s="29" t="s">
         <v>165</v>
       </c>
@@ -6011,7 +6123,7 @@
       <c r="U124" s="17"/>
     </row>
     <row r="125" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="60"/>
+      <c r="A125" s="76"/>
       <c r="B125" s="29" t="s">
         <v>166</v>
       </c>
@@ -6042,7 +6154,7 @@
       <c r="U125" s="17"/>
     </row>
     <row r="126" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="60"/>
+      <c r="A126" s="76"/>
       <c r="B126" s="29" t="s">
         <v>167</v>
       </c>
@@ -6073,36 +6185,36 @@
       <c r="U126" s="17"/>
     </row>
     <row r="127" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="60"/>
+      <c r="A127" s="76"/>
       <c r="B127" s="28" t="s">
         <v>168</v>
       </c>
       <c r="C127" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D127" s="67" t="s">
+      <c r="D127" s="90" t="s">
         <v>68</v>
       </c>
-      <c r="E127" s="67"/>
-      <c r="F127" s="67"/>
-      <c r="G127" s="67"/>
-      <c r="H127" s="67"/>
-      <c r="I127" s="67"/>
-      <c r="J127" s="67"/>
-      <c r="K127" s="67"/>
-      <c r="L127" s="67"/>
-      <c r="M127" s="67"/>
-      <c r="N127" s="67"/>
-      <c r="O127" s="67"/>
-      <c r="P127" s="67"/>
-      <c r="Q127" s="67"/>
-      <c r="R127" s="67"/>
-      <c r="S127" s="67"/>
-      <c r="T127" s="67"/>
-      <c r="U127" s="68"/>
+      <c r="E127" s="61"/>
+      <c r="F127" s="61"/>
+      <c r="G127" s="61"/>
+      <c r="H127" s="61"/>
+      <c r="I127" s="61"/>
+      <c r="J127" s="61"/>
+      <c r="K127" s="61"/>
+      <c r="L127" s="61"/>
+      <c r="M127" s="61"/>
+      <c r="N127" s="61"/>
+      <c r="O127" s="61"/>
+      <c r="P127" s="61"/>
+      <c r="Q127" s="61"/>
+      <c r="R127" s="61"/>
+      <c r="S127" s="61"/>
+      <c r="T127" s="61"/>
+      <c r="U127" s="62"/>
     </row>
     <row r="128" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="60"/>
+      <c r="A128" s="76"/>
       <c r="B128" s="29" t="s">
         <v>169</v>
       </c>
@@ -6133,7 +6245,7 @@
       <c r="U128" s="17"/>
     </row>
     <row r="129" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="60"/>
+      <c r="A129" s="77"/>
       <c r="B129" s="29" t="s">
         <v>170</v>
       </c>
@@ -6164,7 +6276,7 @@
       <c r="U129" s="17"/>
     </row>
     <row r="130" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="53">
+      <c r="A130" s="82">
         <v>19</v>
       </c>
       <c r="B130" s="31" t="s">
@@ -6197,7 +6309,7 @@
       <c r="U130" s="5"/>
     </row>
     <row r="131" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="53"/>
+      <c r="A131" s="83"/>
       <c r="B131" s="31" t="s">
         <v>172</v>
       </c>
@@ -6228,7 +6340,7 @@
       <c r="U131" s="5"/>
     </row>
     <row r="132" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="53"/>
+      <c r="A132" s="83"/>
       <c r="B132" s="31" t="s">
         <v>173</v>
       </c>
@@ -6259,7 +6371,7 @@
       <c r="U132" s="5"/>
     </row>
     <row r="133" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="53"/>
+      <c r="A133" s="83"/>
       <c r="B133" s="31" t="s">
         <v>174</v>
       </c>
@@ -6290,7 +6402,7 @@
       <c r="U133" s="5"/>
     </row>
     <row r="134" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="53"/>
+      <c r="A134" s="83"/>
       <c r="B134" s="31" t="s">
         <v>175</v>
       </c>
@@ -6321,7 +6433,7 @@
       <c r="U134" s="5"/>
     </row>
     <row r="135" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="53"/>
+      <c r="A135" s="83"/>
       <c r="B135" s="31" t="s">
         <v>176</v>
       </c>
@@ -6352,7 +6464,7 @@
       <c r="U135" s="5"/>
     </row>
     <row r="136" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="53"/>
+      <c r="A136" s="84"/>
       <c r="B136" s="31" t="s">
         <v>177</v>
       </c>
@@ -6398,6 +6510,7 @@
     <row r="150" ht="20.25"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A74:A80"/>
     <mergeCell ref="A123:A129"/>
     <mergeCell ref="D127:U127"/>
     <mergeCell ref="A130:A136"/>
@@ -6408,18 +6521,16 @@
     <mergeCell ref="A109:A115"/>
     <mergeCell ref="A116:A122"/>
     <mergeCell ref="A81:A87"/>
+    <mergeCell ref="M2:O2"/>
     <mergeCell ref="A46:A52"/>
     <mergeCell ref="A53:A59"/>
     <mergeCell ref="A60:A66"/>
     <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
-    <mergeCell ref="J2:L2"/>
     <mergeCell ref="A4:A10"/>
     <mergeCell ref="A11:A17"/>
     <mergeCell ref="A18:A24"/>
     <mergeCell ref="A25:A31"/>
     <mergeCell ref="D29:U31"/>
-    <mergeCell ref="M2:O2"/>
     <mergeCell ref="A32:A38"/>
     <mergeCell ref="D35:U41"/>
     <mergeCell ref="A39:A45"/>
@@ -6435,6 +6546,7 @@
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6477,81 +6589,81 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="63"/>
-      <c r="D2" s="52" t="s">
+      <c r="C2" s="68"/>
+      <c r="D2" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52" t="s">
+      <c r="E2" s="71"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52" t="s">
+      <c r="H2" s="71"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52" t="s">
+      <c r="K2" s="71"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="52"/>
-      <c r="O2" s="52"/>
-      <c r="P2" s="52" t="s">
+      <c r="N2" s="71"/>
+      <c r="O2" s="72"/>
+      <c r="P2" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="52"/>
-      <c r="R2" s="52"/>
-      <c r="S2" s="52" t="s">
+      <c r="Q2" s="71"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="52"/>
-      <c r="U2" s="52"/>
+      <c r="T2" s="71"/>
+      <c r="U2" s="72"/>
     </row>
     <row r="3" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="61" t="s">
+      <c r="A3" s="74"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="52" t="s">
+      <c r="E3" s="71"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52" t="s">
+      <c r="H3" s="71"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52" t="s">
+      <c r="K3" s="71"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="52"/>
-      <c r="O3" s="52"/>
-      <c r="P3" s="52" t="s">
+      <c r="N3" s="71"/>
+      <c r="O3" s="72"/>
+      <c r="P3" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="52"/>
-      <c r="R3" s="52"/>
-      <c r="S3" s="52" t="s">
+      <c r="Q3" s="71"/>
+      <c r="R3" s="72"/>
+      <c r="S3" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="52"/>
-      <c r="U3" s="52"/>
+      <c r="T3" s="71"/>
+      <c r="U3" s="72"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="53">
+      <c r="A4" s="82">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -6609,7 +6721,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="53"/>
+      <c r="A5" s="83"/>
       <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
@@ -6667,7 +6779,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="53"/>
+      <c r="A6" s="83"/>
       <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
@@ -6723,7 +6835,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="53"/>
+      <c r="A7" s="83"/>
       <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
@@ -6781,7 +6893,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="53"/>
+      <c r="A8" s="83"/>
       <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
@@ -6843,7 +6955,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="53"/>
+      <c r="A9" s="83"/>
       <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
@@ -6887,7 +6999,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="53"/>
+      <c r="A10" s="84"/>
       <c r="B10" s="2" t="s">
         <v>40</v>
       </c>
@@ -6929,7 +7041,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="60">
+      <c r="A11" s="75">
         <v>2</v>
       </c>
       <c r="B11" s="13" t="s">
@@ -6977,7 +7089,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="60"/>
+      <c r="A12" s="76"/>
       <c r="B12" s="13" t="s">
         <v>46</v>
       </c>
@@ -7021,7 +7133,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="60"/>
+      <c r="A13" s="76"/>
       <c r="B13" s="13" t="s">
         <v>48</v>
       </c>
@@ -7065,7 +7177,7 @@
       </c>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="60"/>
+      <c r="A14" s="76"/>
       <c r="B14" s="13" t="s">
         <v>49</v>
       </c>
@@ -7111,7 +7223,7 @@
       <c r="AA14" s="3"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="60"/>
+      <c r="A15" s="76"/>
       <c r="B15" s="13" t="s">
         <v>53</v>
       </c>
@@ -7145,7 +7257,7 @@
       <c r="AA15" s="3"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="60"/>
+      <c r="A16" s="76"/>
       <c r="B16" s="13" t="s">
         <v>54</v>
       </c>
@@ -7177,7 +7289,7 @@
       <c r="AA16" s="3"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="60"/>
+      <c r="A17" s="77"/>
       <c r="B17" s="13" t="s">
         <v>55</v>
       </c>
@@ -7204,7 +7316,7 @@
       <c r="U17" s="16"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="53">
+      <c r="A18" s="82">
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -7253,7 +7365,7 @@
       <c r="U18" s="5"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="53"/>
+      <c r="A19" s="83"/>
       <c r="B19" s="2" t="s">
         <v>57</v>
       </c>
@@ -7288,7 +7400,7 @@
       <c r="U19" s="5"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="53"/>
+      <c r="A20" s="83"/>
       <c r="B20" s="2" t="s">
         <v>58</v>
       </c>
@@ -7335,7 +7447,7 @@
       <c r="U20" s="5"/>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="53"/>
+      <c r="A21" s="83"/>
       <c r="B21" s="2" t="s">
         <v>59</v>
       </c>
@@ -7388,7 +7500,7 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="53"/>
+      <c r="A22" s="83"/>
       <c r="B22" s="2" t="s">
         <v>60</v>
       </c>
@@ -7435,22 +7547,40 @@
       <c r="U22" s="5"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="53"/>
+      <c r="A23" s="83"/>
       <c r="B23" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C23" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="5"/>
+      <c r="D23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="M23" s="2"/>
       <c r="N23" s="4"/>
       <c r="O23" s="6"/>
@@ -7462,7 +7592,7 @@
       <c r="U23" s="5"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="53"/>
+      <c r="A24" s="84"/>
       <c r="B24" s="21" t="s">
         <v>62</v>
       </c>
@@ -7472,28 +7602,28 @@
       <c r="D24" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="E24" s="21" t="s">
+      <c r="E24" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="21" t="s">
+      <c r="F24" s="24" t="s">
         <v>18</v>
       </c>
       <c r="G24" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="H24" s="21" t="s">
+      <c r="H24" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="21" t="s">
+      <c r="I24" s="24" t="s">
         <v>18</v>
       </c>
       <c r="J24" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="K24" s="21" t="s">
+      <c r="K24" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="L24" s="21" t="s">
+      <c r="L24" s="24" t="s">
         <v>18</v>
       </c>
       <c r="M24" s="21"/>
@@ -7507,7 +7637,7 @@
       <c r="U24" s="24"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="60">
+      <c r="A25" s="75">
         <v>4</v>
       </c>
       <c r="B25" s="13" t="s">
@@ -7556,7 +7686,7 @@
       <c r="U25" s="16"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="60"/>
+      <c r="A26" s="76"/>
       <c r="B26" s="13" t="s">
         <v>64</v>
       </c>
@@ -7603,7 +7733,7 @@
       <c r="U26" s="16"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="60"/>
+      <c r="A27" s="76"/>
       <c r="B27" s="13" t="s">
         <v>65</v>
       </c>
@@ -7644,7 +7774,7 @@
       <c r="U27" s="16"/>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="60"/>
+      <c r="A28" s="76"/>
       <c r="B28" s="13" t="s">
         <v>66</v>
       </c>
@@ -7691,90 +7821,90 @@
       <c r="U28" s="16"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="60"/>
+      <c r="A29" s="76"/>
       <c r="B29" s="26" t="s">
         <v>67</v>
       </c>
       <c r="C29" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="54" t="s">
+      <c r="D29" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="E29" s="54"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="54"/>
-      <c r="J29" s="54"/>
-      <c r="K29" s="54"/>
-      <c r="L29" s="54"/>
-      <c r="M29" s="54"/>
-      <c r="N29" s="54"/>
-      <c r="O29" s="54"/>
-      <c r="P29" s="54"/>
-      <c r="Q29" s="54"/>
-      <c r="R29" s="54"/>
-      <c r="S29" s="54"/>
-      <c r="T29" s="54"/>
-      <c r="U29" s="55"/>
+      <c r="E29" s="80"/>
+      <c r="F29" s="80"/>
+      <c r="G29" s="80"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="80"/>
+      <c r="J29" s="80"/>
+      <c r="K29" s="80"/>
+      <c r="L29" s="80"/>
+      <c r="M29" s="80"/>
+      <c r="N29" s="80"/>
+      <c r="O29" s="80"/>
+      <c r="P29" s="80"/>
+      <c r="Q29" s="80"/>
+      <c r="R29" s="80"/>
+      <c r="S29" s="80"/>
+      <c r="T29" s="80"/>
+      <c r="U29" s="54"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="60"/>
+      <c r="A30" s="76"/>
       <c r="B30" s="26" t="s">
         <v>69</v>
       </c>
       <c r="C30" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="56"/>
-      <c r="J30" s="56"/>
-      <c r="K30" s="56"/>
-      <c r="L30" s="56"/>
-      <c r="M30" s="56"/>
-      <c r="N30" s="56"/>
-      <c r="O30" s="56"/>
-      <c r="P30" s="56"/>
-      <c r="Q30" s="56"/>
-      <c r="R30" s="56"/>
-      <c r="S30" s="56"/>
-      <c r="T30" s="56"/>
-      <c r="U30" s="57"/>
+      <c r="D30" s="79"/>
+      <c r="E30" s="80"/>
+      <c r="F30" s="80"/>
+      <c r="G30" s="80"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="80"/>
+      <c r="J30" s="80"/>
+      <c r="K30" s="80"/>
+      <c r="L30" s="80"/>
+      <c r="M30" s="80"/>
+      <c r="N30" s="80"/>
+      <c r="O30" s="80"/>
+      <c r="P30" s="80"/>
+      <c r="Q30" s="80"/>
+      <c r="R30" s="80"/>
+      <c r="S30" s="80"/>
+      <c r="T30" s="80"/>
+      <c r="U30" s="54"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="60"/>
+      <c r="A31" s="77"/>
       <c r="B31" s="26" t="s">
         <v>70</v>
       </c>
       <c r="C31" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="58"/>
-      <c r="K31" s="58"/>
-      <c r="L31" s="58"/>
-      <c r="M31" s="58"/>
-      <c r="N31" s="58"/>
-      <c r="O31" s="58"/>
-      <c r="P31" s="58"/>
-      <c r="Q31" s="58"/>
-      <c r="R31" s="58"/>
-      <c r="S31" s="58"/>
-      <c r="T31" s="58"/>
-      <c r="U31" s="59"/>
+      <c r="D31" s="81"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="55"/>
+      <c r="J31" s="55"/>
+      <c r="K31" s="55"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="55"/>
+      <c r="N31" s="55"/>
+      <c r="O31" s="55"/>
+      <c r="P31" s="55"/>
+      <c r="Q31" s="55"/>
+      <c r="R31" s="55"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="55"/>
+      <c r="U31" s="56"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="53">
+      <c r="A32" s="82">
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -7817,7 +7947,7 @@
       <c r="U32" s="5"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="53"/>
+      <c r="A33" s="83"/>
       <c r="B33" s="2" t="s">
         <v>72</v>
       </c>
@@ -7864,7 +7994,7 @@
       <c r="U33" s="5"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="53"/>
+      <c r="A34" s="83"/>
       <c r="B34" s="2" t="s">
         <v>73</v>
       </c>
@@ -7911,117 +8041,117 @@
       <c r="U34" s="5"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="53"/>
+      <c r="A35" s="83"/>
       <c r="B35" s="28" t="s">
         <v>74</v>
       </c>
       <c r="C35" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="54" t="s">
+      <c r="D35" s="78" t="s">
         <v>68</v>
       </c>
-      <c r="E35" s="54"/>
-      <c r="F35" s="54"/>
-      <c r="G35" s="54"/>
-      <c r="H35" s="54"/>
-      <c r="I35" s="54"/>
-      <c r="J35" s="54"/>
-      <c r="K35" s="54"/>
-      <c r="L35" s="54"/>
-      <c r="M35" s="54"/>
-      <c r="N35" s="54"/>
-      <c r="O35" s="54"/>
-      <c r="P35" s="54"/>
-      <c r="Q35" s="54"/>
-      <c r="R35" s="54"/>
-      <c r="S35" s="54"/>
-      <c r="T35" s="54"/>
-      <c r="U35" s="55"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="52"/>
+      <c r="K35" s="52"/>
+      <c r="L35" s="52"/>
+      <c r="M35" s="52"/>
+      <c r="N35" s="52"/>
+      <c r="O35" s="52"/>
+      <c r="P35" s="52"/>
+      <c r="Q35" s="52"/>
+      <c r="R35" s="52"/>
+      <c r="S35" s="52"/>
+      <c r="T35" s="52"/>
+      <c r="U35" s="53"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="53"/>
+      <c r="A36" s="83"/>
       <c r="B36" s="28" t="s">
         <v>75</v>
       </c>
       <c r="C36" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="56"/>
-      <c r="E36" s="56"/>
-      <c r="F36" s="56"/>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="56"/>
-      <c r="J36" s="56"/>
-      <c r="K36" s="56"/>
-      <c r="L36" s="56"/>
-      <c r="M36" s="56"/>
-      <c r="N36" s="56"/>
-      <c r="O36" s="56"/>
-      <c r="P36" s="56"/>
-      <c r="Q36" s="56"/>
-      <c r="R36" s="56"/>
-      <c r="S36" s="56"/>
-      <c r="T36" s="56"/>
-      <c r="U36" s="57"/>
+      <c r="D36" s="79"/>
+      <c r="E36" s="80"/>
+      <c r="F36" s="80"/>
+      <c r="G36" s="80"/>
+      <c r="H36" s="80"/>
+      <c r="I36" s="80"/>
+      <c r="J36" s="80"/>
+      <c r="K36" s="80"/>
+      <c r="L36" s="80"/>
+      <c r="M36" s="80"/>
+      <c r="N36" s="80"/>
+      <c r="O36" s="80"/>
+      <c r="P36" s="80"/>
+      <c r="Q36" s="80"/>
+      <c r="R36" s="80"/>
+      <c r="S36" s="80"/>
+      <c r="T36" s="80"/>
+      <c r="U36" s="54"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="53"/>
+      <c r="A37" s="83"/>
       <c r="B37" s="28" t="s">
         <v>76</v>
       </c>
       <c r="C37" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D37" s="56"/>
-      <c r="E37" s="56"/>
-      <c r="F37" s="56"/>
-      <c r="G37" s="56"/>
-      <c r="H37" s="56"/>
-      <c r="I37" s="56"/>
-      <c r="J37" s="56"/>
-      <c r="K37" s="56"/>
-      <c r="L37" s="56"/>
-      <c r="M37" s="56"/>
-      <c r="N37" s="56"/>
-      <c r="O37" s="56"/>
-      <c r="P37" s="56"/>
-      <c r="Q37" s="56"/>
-      <c r="R37" s="56"/>
-      <c r="S37" s="56"/>
-      <c r="T37" s="56"/>
-      <c r="U37" s="57"/>
+      <c r="D37" s="79"/>
+      <c r="E37" s="80"/>
+      <c r="F37" s="80"/>
+      <c r="G37" s="80"/>
+      <c r="H37" s="80"/>
+      <c r="I37" s="80"/>
+      <c r="J37" s="80"/>
+      <c r="K37" s="80"/>
+      <c r="L37" s="80"/>
+      <c r="M37" s="80"/>
+      <c r="N37" s="80"/>
+      <c r="O37" s="80"/>
+      <c r="P37" s="80"/>
+      <c r="Q37" s="80"/>
+      <c r="R37" s="80"/>
+      <c r="S37" s="80"/>
+      <c r="T37" s="80"/>
+      <c r="U37" s="54"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="53"/>
+      <c r="A38" s="84"/>
       <c r="B38" s="28" t="s">
         <v>77</v>
       </c>
       <c r="C38" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="56"/>
-      <c r="G38" s="56"/>
-      <c r="H38" s="56"/>
-      <c r="I38" s="56"/>
-      <c r="J38" s="56"/>
-      <c r="K38" s="56"/>
-      <c r="L38" s="56"/>
-      <c r="M38" s="56"/>
-      <c r="N38" s="56"/>
-      <c r="O38" s="56"/>
-      <c r="P38" s="56"/>
-      <c r="Q38" s="56"/>
-      <c r="R38" s="56"/>
-      <c r="S38" s="56"/>
-      <c r="T38" s="56"/>
-      <c r="U38" s="57"/>
+      <c r="D38" s="79"/>
+      <c r="E38" s="80"/>
+      <c r="F38" s="80"/>
+      <c r="G38" s="80"/>
+      <c r="H38" s="80"/>
+      <c r="I38" s="80"/>
+      <c r="J38" s="80"/>
+      <c r="K38" s="80"/>
+      <c r="L38" s="80"/>
+      <c r="M38" s="80"/>
+      <c r="N38" s="80"/>
+      <c r="O38" s="80"/>
+      <c r="P38" s="80"/>
+      <c r="Q38" s="80"/>
+      <c r="R38" s="80"/>
+      <c r="S38" s="80"/>
+      <c r="T38" s="80"/>
+      <c r="U38" s="54"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="60">
+      <c r="A39" s="75">
         <v>6</v>
       </c>
       <c r="B39" s="28" t="s">
@@ -8030,81 +8160,81 @@
       <c r="C39" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="56"/>
-      <c r="E39" s="56"/>
-      <c r="F39" s="56"/>
-      <c r="G39" s="56"/>
-      <c r="H39" s="56"/>
-      <c r="I39" s="56"/>
-      <c r="J39" s="56"/>
-      <c r="K39" s="56"/>
-      <c r="L39" s="56"/>
-      <c r="M39" s="56"/>
-      <c r="N39" s="56"/>
-      <c r="O39" s="56"/>
-      <c r="P39" s="56"/>
-      <c r="Q39" s="56"/>
-      <c r="R39" s="56"/>
-      <c r="S39" s="56"/>
-      <c r="T39" s="56"/>
-      <c r="U39" s="57"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="80"/>
+      <c r="F39" s="80"/>
+      <c r="G39" s="80"/>
+      <c r="H39" s="80"/>
+      <c r="I39" s="80"/>
+      <c r="J39" s="80"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="80"/>
+      <c r="M39" s="80"/>
+      <c r="N39" s="80"/>
+      <c r="O39" s="80"/>
+      <c r="P39" s="80"/>
+      <c r="Q39" s="80"/>
+      <c r="R39" s="80"/>
+      <c r="S39" s="80"/>
+      <c r="T39" s="80"/>
+      <c r="U39" s="54"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="60"/>
+      <c r="A40" s="76"/>
       <c r="B40" s="28" t="s">
         <v>79</v>
       </c>
       <c r="C40" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="D40" s="56"/>
-      <c r="E40" s="56"/>
-      <c r="F40" s="56"/>
-      <c r="G40" s="56"/>
-      <c r="H40" s="56"/>
-      <c r="I40" s="56"/>
-      <c r="J40" s="56"/>
-      <c r="K40" s="56"/>
-      <c r="L40" s="56"/>
-      <c r="M40" s="56"/>
-      <c r="N40" s="56"/>
-      <c r="O40" s="56"/>
-      <c r="P40" s="56"/>
-      <c r="Q40" s="56"/>
-      <c r="R40" s="56"/>
-      <c r="S40" s="56"/>
-      <c r="T40" s="56"/>
-      <c r="U40" s="57"/>
+      <c r="D40" s="79"/>
+      <c r="E40" s="80"/>
+      <c r="F40" s="80"/>
+      <c r="G40" s="80"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="80"/>
+      <c r="J40" s="80"/>
+      <c r="K40" s="80"/>
+      <c r="L40" s="80"/>
+      <c r="M40" s="80"/>
+      <c r="N40" s="80"/>
+      <c r="O40" s="80"/>
+      <c r="P40" s="80"/>
+      <c r="Q40" s="80"/>
+      <c r="R40" s="80"/>
+      <c r="S40" s="80"/>
+      <c r="T40" s="80"/>
+      <c r="U40" s="54"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="60"/>
+      <c r="A41" s="76"/>
       <c r="B41" s="28" t="s">
         <v>80</v>
       </c>
       <c r="C41" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D41" s="58"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="58"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="58"/>
-      <c r="K41" s="58"/>
-      <c r="L41" s="58"/>
-      <c r="M41" s="58"/>
-      <c r="N41" s="58"/>
-      <c r="O41" s="58"/>
-      <c r="P41" s="58"/>
-      <c r="Q41" s="58"/>
-      <c r="R41" s="58"/>
-      <c r="S41" s="58"/>
-      <c r="T41" s="58"/>
-      <c r="U41" s="59"/>
+      <c r="D41" s="81"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="55"/>
+      <c r="J41" s="55"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="55"/>
+      <c r="M41" s="55"/>
+      <c r="N41" s="55"/>
+      <c r="O41" s="55"/>
+      <c r="P41" s="55"/>
+      <c r="Q41" s="55"/>
+      <c r="R41" s="55"/>
+      <c r="S41" s="55"/>
+      <c r="T41" s="55"/>
+      <c r="U41" s="56"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="60"/>
+      <c r="A42" s="76"/>
       <c r="B42" s="29" t="s">
         <v>81</v>
       </c>
@@ -8145,7 +8275,7 @@
       </c>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="60"/>
+      <c r="A43" s="76"/>
       <c r="B43" s="29" t="s">
         <v>82</v>
       </c>
@@ -8174,7 +8304,7 @@
       <c r="U43" s="16"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="60"/>
+      <c r="A44" s="76"/>
       <c r="B44" s="30" t="s">
         <v>83</v>
       </c>
@@ -8201,7 +8331,7 @@
       <c r="U44" s="24"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="60"/>
+      <c r="A45" s="77"/>
       <c r="B45" s="29" t="s">
         <v>84</v>
       </c>
@@ -8228,7 +8358,7 @@
       <c r="U45" s="16"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="53">
+      <c r="A46" s="82">
         <v>7</v>
       </c>
       <c r="B46" s="31" t="s">
@@ -8277,7 +8407,7 @@
       <c r="U46" s="5"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="53"/>
+      <c r="A47" s="83"/>
       <c r="B47" s="31" t="s">
         <v>86</v>
       </c>
@@ -8324,7 +8454,7 @@
       <c r="U47" s="5"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="53"/>
+      <c r="A48" s="83"/>
       <c r="B48" s="31" t="s">
         <v>87</v>
       </c>
@@ -8371,7 +8501,7 @@
       <c r="U48" s="5"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="53"/>
+      <c r="A49" s="83"/>
       <c r="B49" s="46" t="s">
         <v>88</v>
       </c>
@@ -8418,7 +8548,7 @@
       <c r="U49" s="5"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="53"/>
+      <c r="A50" s="83"/>
       <c r="B50" s="46" t="s">
         <v>89</v>
       </c>
@@ -8465,7 +8595,7 @@
       <c r="U50" s="5"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="53"/>
+      <c r="A51" s="83"/>
       <c r="B51" s="46" t="s">
         <v>90</v>
       </c>
@@ -8492,7 +8622,7 @@
       <c r="U51" s="5"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="53"/>
+      <c r="A52" s="84"/>
       <c r="B52" s="46" t="s">
         <v>91</v>
       </c>
@@ -8519,7 +8649,7 @@
       <c r="U52" s="5"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="60">
+      <c r="A53" s="75">
         <v>8</v>
       </c>
       <c r="B53" s="48" t="s">
@@ -8562,7 +8692,7 @@
       <c r="U53" s="16"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="60"/>
+      <c r="A54" s="76"/>
       <c r="B54" s="48" t="s">
         <v>93</v>
       </c>
@@ -8609,7 +8739,7 @@
       <c r="U54" s="16"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="60"/>
+      <c r="A55" s="76"/>
       <c r="B55" s="48" t="s">
         <v>94</v>
       </c>
@@ -8650,7 +8780,7 @@
       <c r="U55" s="16"/>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="60"/>
+      <c r="A56" s="76"/>
       <c r="B56" s="48" t="s">
         <v>95</v>
       </c>
@@ -8709,7 +8839,7 @@
       </c>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="60"/>
+      <c r="A57" s="76"/>
       <c r="B57" s="48" t="s">
         <v>96</v>
       </c>
@@ -8756,7 +8886,7 @@
       <c r="U57" s="16"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="60"/>
+      <c r="A58" s="76"/>
       <c r="B58" s="48" t="s">
         <v>97</v>
       </c>
@@ -8783,7 +8913,7 @@
       <c r="U58" s="16"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="60"/>
+      <c r="A59" s="77"/>
       <c r="B59" s="48" t="s">
         <v>98</v>
       </c>
@@ -8810,7 +8940,7 @@
       <c r="U59" s="16"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="53">
+      <c r="A60" s="82">
         <v>9</v>
       </c>
       <c r="B60" s="46" t="s">
@@ -8859,7 +8989,7 @@
       <c r="U60" s="5"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="53"/>
+      <c r="A61" s="83"/>
       <c r="B61" s="46" t="s">
         <v>100</v>
       </c>
@@ -8906,7 +9036,7 @@
       <c r="U61" s="5"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="53"/>
+      <c r="A62" s="83"/>
       <c r="B62" s="46" t="s">
         <v>101</v>
       </c>
@@ -8953,7 +9083,7 @@
       <c r="U62" s="5"/>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="53"/>
+      <c r="A63" s="83"/>
       <c r="B63" s="46" t="s">
         <v>102</v>
       </c>
@@ -9006,7 +9136,7 @@
       </c>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="53"/>
+      <c r="A64" s="83"/>
       <c r="B64" s="46" t="s">
         <v>103</v>
       </c>
@@ -9047,40 +9177,15 @@
       <c r="U64" s="6"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="53"/>
+      <c r="A65" s="83"/>
       <c r="B65" s="46" t="s">
         <v>104</v>
       </c>
       <c r="C65" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H65" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I65" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J65" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K65" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L65" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="F65" s="5"/>
+      <c r="I65" s="5"/>
       <c r="M65" s="2"/>
       <c r="N65" s="4"/>
       <c r="O65" s="6"/>
@@ -9092,7 +9197,7 @@
       <c r="U65" s="6"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="53"/>
+      <c r="A66" s="84"/>
       <c r="B66" s="46" t="s">
         <v>105</v>
       </c>
@@ -9119,7 +9224,7 @@
       <c r="U66" s="6"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="60">
+      <c r="A67" s="75">
         <v>10</v>
       </c>
       <c r="B67" s="48" t="s">
@@ -9162,7 +9267,7 @@
       <c r="U67" s="17"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="60"/>
+      <c r="A68" s="76"/>
       <c r="B68" s="48" t="s">
         <v>107</v>
       </c>
@@ -9209,7 +9314,7 @@
       <c r="U68" s="17"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="60"/>
+      <c r="A69" s="76"/>
       <c r="B69" s="48" t="s">
         <v>108</v>
       </c>
@@ -9250,7 +9355,7 @@
       <c r="U69" s="17"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="60"/>
+      <c r="A70" s="76"/>
       <c r="B70" s="48" t="s">
         <v>109</v>
       </c>
@@ -9309,7 +9414,7 @@
       </c>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="60"/>
+      <c r="A71" s="76"/>
       <c r="B71" s="48" t="s">
         <v>110</v>
       </c>
@@ -9350,7 +9455,7 @@
       <c r="U71" s="17"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="60"/>
+      <c r="A72" s="76"/>
       <c r="B72" s="48" t="s">
         <v>111</v>
       </c>
@@ -9395,7 +9500,7 @@
       <c r="U72" s="17"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="60"/>
+      <c r="A73" s="77"/>
       <c r="B73" s="48" t="s">
         <v>112</v>
       </c>
@@ -9422,7 +9527,7 @@
       <c r="U73" s="17"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="53">
+      <c r="A74" s="82">
         <v>11</v>
       </c>
       <c r="B74" s="46" t="s">
@@ -9471,7 +9576,7 @@
       <c r="U74" s="6"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="53"/>
+      <c r="A75" s="83"/>
       <c r="B75" s="31" t="s">
         <v>114</v>
       </c>
@@ -9512,7 +9617,7 @@
       <c r="U75" s="6"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="53"/>
+      <c r="A76" s="83"/>
       <c r="B76" s="31" t="s">
         <v>115</v>
       </c>
@@ -9553,7 +9658,7 @@
       <c r="U76" s="6"/>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="53"/>
+      <c r="A77" s="83"/>
       <c r="B77" s="31" t="s">
         <v>116</v>
       </c>
@@ -9594,7 +9699,7 @@
       <c r="U77" s="5"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="53"/>
+      <c r="A78" s="83"/>
       <c r="B78" s="31" t="s">
         <v>117</v>
       </c>
@@ -9641,7 +9746,7 @@
       <c r="U78" s="5"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="53"/>
+      <c r="A79" s="83"/>
       <c r="B79" s="31" t="s">
         <v>118</v>
       </c>
@@ -9686,7 +9791,7 @@
       <c r="U79" s="5"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="53"/>
+      <c r="A80" s="84"/>
       <c r="B80" s="31" t="s">
         <v>119</v>
       </c>
@@ -9713,7 +9818,7 @@
       <c r="U80" s="5"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="60">
+      <c r="A81" s="75">
         <v>12</v>
       </c>
       <c r="B81" s="29" t="s">
@@ -9722,191 +9827,191 @@
       <c r="C81" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D81" s="69" t="s">
+      <c r="D81" s="85" t="s">
         <v>121</v>
       </c>
-      <c r="E81" s="69"/>
-      <c r="F81" s="69"/>
-      <c r="G81" s="69"/>
-      <c r="H81" s="69"/>
-      <c r="I81" s="69"/>
-      <c r="J81" s="69"/>
-      <c r="K81" s="69"/>
-      <c r="L81" s="69"/>
-      <c r="M81" s="69"/>
-      <c r="N81" s="69"/>
-      <c r="O81" s="69"/>
-      <c r="P81" s="69"/>
-      <c r="Q81" s="69"/>
-      <c r="R81" s="69"/>
-      <c r="S81" s="69"/>
-      <c r="T81" s="69"/>
-      <c r="U81" s="70"/>
+      <c r="E81" s="63"/>
+      <c r="F81" s="63"/>
+      <c r="G81" s="63"/>
+      <c r="H81" s="63"/>
+      <c r="I81" s="63"/>
+      <c r="J81" s="63"/>
+      <c r="K81" s="63"/>
+      <c r="L81" s="63"/>
+      <c r="M81" s="63"/>
+      <c r="N81" s="63"/>
+      <c r="O81" s="63"/>
+      <c r="P81" s="63"/>
+      <c r="Q81" s="63"/>
+      <c r="R81" s="63"/>
+      <c r="S81" s="63"/>
+      <c r="T81" s="63"/>
+      <c r="U81" s="64"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="60"/>
+      <c r="A82" s="76"/>
       <c r="B82" s="29" t="s">
         <v>122</v>
       </c>
       <c r="C82" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D82" s="71"/>
-      <c r="E82" s="71"/>
-      <c r="F82" s="71"/>
-      <c r="G82" s="71"/>
-      <c r="H82" s="71"/>
-      <c r="I82" s="71"/>
-      <c r="J82" s="71"/>
-      <c r="K82" s="71"/>
-      <c r="L82" s="71"/>
-      <c r="M82" s="71"/>
-      <c r="N82" s="71"/>
-      <c r="O82" s="71"/>
-      <c r="P82" s="71"/>
-      <c r="Q82" s="71"/>
-      <c r="R82" s="71"/>
-      <c r="S82" s="71"/>
-      <c r="T82" s="71"/>
-      <c r="U82" s="72"/>
+      <c r="D82" s="86"/>
+      <c r="E82" s="87"/>
+      <c r="F82" s="87"/>
+      <c r="G82" s="87"/>
+      <c r="H82" s="87"/>
+      <c r="I82" s="87"/>
+      <c r="J82" s="87"/>
+      <c r="K82" s="87"/>
+      <c r="L82" s="87"/>
+      <c r="M82" s="87"/>
+      <c r="N82" s="87"/>
+      <c r="O82" s="87"/>
+      <c r="P82" s="87"/>
+      <c r="Q82" s="87"/>
+      <c r="R82" s="87"/>
+      <c r="S82" s="87"/>
+      <c r="T82" s="87"/>
+      <c r="U82" s="65"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="60"/>
+      <c r="A83" s="76"/>
       <c r="B83" s="29" t="s">
         <v>123</v>
       </c>
       <c r="C83" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D83" s="71"/>
-      <c r="E83" s="71"/>
-      <c r="F83" s="71"/>
-      <c r="G83" s="71"/>
-      <c r="H83" s="71"/>
-      <c r="I83" s="71"/>
-      <c r="J83" s="71"/>
-      <c r="K83" s="71"/>
-      <c r="L83" s="71"/>
-      <c r="M83" s="71"/>
-      <c r="N83" s="71"/>
-      <c r="O83" s="71"/>
-      <c r="P83" s="71"/>
-      <c r="Q83" s="71"/>
-      <c r="R83" s="71"/>
-      <c r="S83" s="71"/>
-      <c r="T83" s="71"/>
-      <c r="U83" s="72"/>
+      <c r="D83" s="86"/>
+      <c r="E83" s="87"/>
+      <c r="F83" s="87"/>
+      <c r="G83" s="87"/>
+      <c r="H83" s="87"/>
+      <c r="I83" s="87"/>
+      <c r="J83" s="87"/>
+      <c r="K83" s="87"/>
+      <c r="L83" s="87"/>
+      <c r="M83" s="87"/>
+      <c r="N83" s="87"/>
+      <c r="O83" s="87"/>
+      <c r="P83" s="87"/>
+      <c r="Q83" s="87"/>
+      <c r="R83" s="87"/>
+      <c r="S83" s="87"/>
+      <c r="T83" s="87"/>
+      <c r="U83" s="65"/>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="60"/>
+      <c r="A84" s="76"/>
       <c r="B84" s="29" t="s">
         <v>124</v>
       </c>
       <c r="C84" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D84" s="71"/>
-      <c r="E84" s="71"/>
-      <c r="F84" s="71"/>
-      <c r="G84" s="71"/>
-      <c r="H84" s="71"/>
-      <c r="I84" s="71"/>
-      <c r="J84" s="71"/>
-      <c r="K84" s="71"/>
-      <c r="L84" s="71"/>
-      <c r="M84" s="71"/>
-      <c r="N84" s="71"/>
-      <c r="O84" s="71"/>
-      <c r="P84" s="71"/>
-      <c r="Q84" s="71"/>
-      <c r="R84" s="71"/>
-      <c r="S84" s="71"/>
-      <c r="T84" s="71"/>
-      <c r="U84" s="72"/>
+      <c r="D84" s="86"/>
+      <c r="E84" s="87"/>
+      <c r="F84" s="87"/>
+      <c r="G84" s="87"/>
+      <c r="H84" s="87"/>
+      <c r="I84" s="87"/>
+      <c r="J84" s="87"/>
+      <c r="K84" s="87"/>
+      <c r="L84" s="87"/>
+      <c r="M84" s="87"/>
+      <c r="N84" s="87"/>
+      <c r="O84" s="87"/>
+      <c r="P84" s="87"/>
+      <c r="Q84" s="87"/>
+      <c r="R84" s="87"/>
+      <c r="S84" s="87"/>
+      <c r="T84" s="87"/>
+      <c r="U84" s="65"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="60"/>
+      <c r="A85" s="76"/>
       <c r="B85" s="29" t="s">
         <v>125</v>
       </c>
       <c r="C85" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D85" s="71"/>
-      <c r="E85" s="71"/>
-      <c r="F85" s="71"/>
-      <c r="G85" s="71"/>
-      <c r="H85" s="71"/>
-      <c r="I85" s="71"/>
-      <c r="J85" s="71"/>
-      <c r="K85" s="71"/>
-      <c r="L85" s="71"/>
-      <c r="M85" s="71"/>
-      <c r="N85" s="71"/>
-      <c r="O85" s="71"/>
-      <c r="P85" s="71"/>
-      <c r="Q85" s="71"/>
-      <c r="R85" s="71"/>
-      <c r="S85" s="71"/>
-      <c r="T85" s="71"/>
-      <c r="U85" s="72"/>
+      <c r="D85" s="86"/>
+      <c r="E85" s="87"/>
+      <c r="F85" s="87"/>
+      <c r="G85" s="87"/>
+      <c r="H85" s="87"/>
+      <c r="I85" s="87"/>
+      <c r="J85" s="87"/>
+      <c r="K85" s="87"/>
+      <c r="L85" s="87"/>
+      <c r="M85" s="87"/>
+      <c r="N85" s="87"/>
+      <c r="O85" s="87"/>
+      <c r="P85" s="87"/>
+      <c r="Q85" s="87"/>
+      <c r="R85" s="87"/>
+      <c r="S85" s="87"/>
+      <c r="T85" s="87"/>
+      <c r="U85" s="65"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="60"/>
+      <c r="A86" s="76"/>
       <c r="B86" s="29" t="s">
         <v>126</v>
       </c>
       <c r="C86" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D86" s="71"/>
-      <c r="E86" s="71"/>
-      <c r="F86" s="71"/>
-      <c r="G86" s="71"/>
-      <c r="H86" s="71"/>
-      <c r="I86" s="71"/>
-      <c r="J86" s="71"/>
-      <c r="K86" s="71"/>
-      <c r="L86" s="71"/>
-      <c r="M86" s="71"/>
-      <c r="N86" s="71"/>
-      <c r="O86" s="71"/>
-      <c r="P86" s="71"/>
-      <c r="Q86" s="71"/>
-      <c r="R86" s="71"/>
-      <c r="S86" s="71"/>
-      <c r="T86" s="71"/>
-      <c r="U86" s="72"/>
+      <c r="D86" s="86"/>
+      <c r="E86" s="87"/>
+      <c r="F86" s="87"/>
+      <c r="G86" s="87"/>
+      <c r="H86" s="87"/>
+      <c r="I86" s="87"/>
+      <c r="J86" s="87"/>
+      <c r="K86" s="87"/>
+      <c r="L86" s="87"/>
+      <c r="M86" s="87"/>
+      <c r="N86" s="87"/>
+      <c r="O86" s="87"/>
+      <c r="P86" s="87"/>
+      <c r="Q86" s="87"/>
+      <c r="R86" s="87"/>
+      <c r="S86" s="87"/>
+      <c r="T86" s="87"/>
+      <c r="U86" s="65"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="60"/>
+      <c r="A87" s="77"/>
       <c r="B87" s="29" t="s">
         <v>127</v>
       </c>
       <c r="C87" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D87" s="71"/>
-      <c r="E87" s="71"/>
-      <c r="F87" s="71"/>
-      <c r="G87" s="71"/>
-      <c r="H87" s="71"/>
-      <c r="I87" s="71"/>
-      <c r="J87" s="71"/>
-      <c r="K87" s="71"/>
-      <c r="L87" s="71"/>
-      <c r="M87" s="71"/>
-      <c r="N87" s="71"/>
-      <c r="O87" s="71"/>
-      <c r="P87" s="71"/>
-      <c r="Q87" s="71"/>
-      <c r="R87" s="71"/>
-      <c r="S87" s="71"/>
-      <c r="T87" s="71"/>
-      <c r="U87" s="72"/>
+      <c r="D87" s="86"/>
+      <c r="E87" s="87"/>
+      <c r="F87" s="87"/>
+      <c r="G87" s="87"/>
+      <c r="H87" s="87"/>
+      <c r="I87" s="87"/>
+      <c r="J87" s="87"/>
+      <c r="K87" s="87"/>
+      <c r="L87" s="87"/>
+      <c r="M87" s="87"/>
+      <c r="N87" s="87"/>
+      <c r="O87" s="87"/>
+      <c r="P87" s="87"/>
+      <c r="Q87" s="87"/>
+      <c r="R87" s="87"/>
+      <c r="S87" s="87"/>
+      <c r="T87" s="87"/>
+      <c r="U87" s="65"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="53">
+      <c r="A88" s="82">
         <v>13</v>
       </c>
       <c r="B88" s="31" t="s">
@@ -9915,189 +10020,189 @@
       <c r="C88" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D88" s="71"/>
-      <c r="E88" s="71"/>
-      <c r="F88" s="71"/>
-      <c r="G88" s="71"/>
-      <c r="H88" s="71"/>
-      <c r="I88" s="71"/>
-      <c r="J88" s="71"/>
-      <c r="K88" s="71"/>
-      <c r="L88" s="71"/>
-      <c r="M88" s="71"/>
-      <c r="N88" s="71"/>
-      <c r="O88" s="71"/>
-      <c r="P88" s="71"/>
-      <c r="Q88" s="71"/>
-      <c r="R88" s="71"/>
-      <c r="S88" s="71"/>
-      <c r="T88" s="71"/>
-      <c r="U88" s="72"/>
+      <c r="D88" s="86"/>
+      <c r="E88" s="87"/>
+      <c r="F88" s="87"/>
+      <c r="G88" s="87"/>
+      <c r="H88" s="87"/>
+      <c r="I88" s="87"/>
+      <c r="J88" s="87"/>
+      <c r="K88" s="87"/>
+      <c r="L88" s="87"/>
+      <c r="M88" s="87"/>
+      <c r="N88" s="87"/>
+      <c r="O88" s="87"/>
+      <c r="P88" s="87"/>
+      <c r="Q88" s="87"/>
+      <c r="R88" s="87"/>
+      <c r="S88" s="87"/>
+      <c r="T88" s="87"/>
+      <c r="U88" s="65"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="53"/>
+      <c r="A89" s="83"/>
       <c r="B89" s="31" t="s">
         <v>129</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D89" s="71"/>
-      <c r="E89" s="71"/>
-      <c r="F89" s="71"/>
-      <c r="G89" s="71"/>
-      <c r="H89" s="71"/>
-      <c r="I89" s="71"/>
-      <c r="J89" s="71"/>
-      <c r="K89" s="71"/>
-      <c r="L89" s="71"/>
-      <c r="M89" s="71"/>
-      <c r="N89" s="71"/>
-      <c r="O89" s="71"/>
-      <c r="P89" s="71"/>
-      <c r="Q89" s="71"/>
-      <c r="R89" s="71"/>
-      <c r="S89" s="71"/>
-      <c r="T89" s="71"/>
-      <c r="U89" s="72"/>
+      <c r="D89" s="86"/>
+      <c r="E89" s="87"/>
+      <c r="F89" s="87"/>
+      <c r="G89" s="87"/>
+      <c r="H89" s="87"/>
+      <c r="I89" s="87"/>
+      <c r="J89" s="87"/>
+      <c r="K89" s="87"/>
+      <c r="L89" s="87"/>
+      <c r="M89" s="87"/>
+      <c r="N89" s="87"/>
+      <c r="O89" s="87"/>
+      <c r="P89" s="87"/>
+      <c r="Q89" s="87"/>
+      <c r="R89" s="87"/>
+      <c r="S89" s="87"/>
+      <c r="T89" s="87"/>
+      <c r="U89" s="65"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="53"/>
+      <c r="A90" s="83"/>
       <c r="B90" s="31" t="s">
         <v>130</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D90" s="71"/>
-      <c r="E90" s="71"/>
-      <c r="F90" s="71"/>
-      <c r="G90" s="71"/>
-      <c r="H90" s="71"/>
-      <c r="I90" s="71"/>
-      <c r="J90" s="71"/>
-      <c r="K90" s="71"/>
-      <c r="L90" s="71"/>
-      <c r="M90" s="71"/>
-      <c r="N90" s="71"/>
-      <c r="O90" s="71"/>
-      <c r="P90" s="71"/>
-      <c r="Q90" s="71"/>
-      <c r="R90" s="71"/>
-      <c r="S90" s="71"/>
-      <c r="T90" s="71"/>
-      <c r="U90" s="72"/>
+      <c r="D90" s="86"/>
+      <c r="E90" s="87"/>
+      <c r="F90" s="87"/>
+      <c r="G90" s="87"/>
+      <c r="H90" s="87"/>
+      <c r="I90" s="87"/>
+      <c r="J90" s="87"/>
+      <c r="K90" s="87"/>
+      <c r="L90" s="87"/>
+      <c r="M90" s="87"/>
+      <c r="N90" s="87"/>
+      <c r="O90" s="87"/>
+      <c r="P90" s="87"/>
+      <c r="Q90" s="87"/>
+      <c r="R90" s="87"/>
+      <c r="S90" s="87"/>
+      <c r="T90" s="87"/>
+      <c r="U90" s="65"/>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="53"/>
+      <c r="A91" s="83"/>
       <c r="B91" s="31" t="s">
         <v>131</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D91" s="71"/>
-      <c r="E91" s="71"/>
-      <c r="F91" s="71"/>
-      <c r="G91" s="71"/>
-      <c r="H91" s="71"/>
-      <c r="I91" s="71"/>
-      <c r="J91" s="71"/>
-      <c r="K91" s="71"/>
-      <c r="L91" s="71"/>
-      <c r="M91" s="71"/>
-      <c r="N91" s="71"/>
-      <c r="O91" s="71"/>
-      <c r="P91" s="71"/>
-      <c r="Q91" s="71"/>
-      <c r="R91" s="71"/>
-      <c r="S91" s="71"/>
-      <c r="T91" s="71"/>
-      <c r="U91" s="72"/>
+      <c r="D91" s="86"/>
+      <c r="E91" s="87"/>
+      <c r="F91" s="87"/>
+      <c r="G91" s="87"/>
+      <c r="H91" s="87"/>
+      <c r="I91" s="87"/>
+      <c r="J91" s="87"/>
+      <c r="K91" s="87"/>
+      <c r="L91" s="87"/>
+      <c r="M91" s="87"/>
+      <c r="N91" s="87"/>
+      <c r="O91" s="87"/>
+      <c r="P91" s="87"/>
+      <c r="Q91" s="87"/>
+      <c r="R91" s="87"/>
+      <c r="S91" s="87"/>
+      <c r="T91" s="87"/>
+      <c r="U91" s="65"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="53"/>
+      <c r="A92" s="83"/>
       <c r="B92" s="31" t="s">
         <v>132</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D92" s="71"/>
-      <c r="E92" s="71"/>
-      <c r="F92" s="71"/>
-      <c r="G92" s="71"/>
-      <c r="H92" s="71"/>
-      <c r="I92" s="71"/>
-      <c r="J92" s="71"/>
-      <c r="K92" s="71"/>
-      <c r="L92" s="71"/>
-      <c r="M92" s="71"/>
-      <c r="N92" s="71"/>
-      <c r="O92" s="71"/>
-      <c r="P92" s="71"/>
-      <c r="Q92" s="71"/>
-      <c r="R92" s="71"/>
-      <c r="S92" s="71"/>
-      <c r="T92" s="71"/>
-      <c r="U92" s="72"/>
+      <c r="D92" s="86"/>
+      <c r="E92" s="87"/>
+      <c r="F92" s="87"/>
+      <c r="G92" s="87"/>
+      <c r="H92" s="87"/>
+      <c r="I92" s="87"/>
+      <c r="J92" s="87"/>
+      <c r="K92" s="87"/>
+      <c r="L92" s="87"/>
+      <c r="M92" s="87"/>
+      <c r="N92" s="87"/>
+      <c r="O92" s="87"/>
+      <c r="P92" s="87"/>
+      <c r="Q92" s="87"/>
+      <c r="R92" s="87"/>
+      <c r="S92" s="87"/>
+      <c r="T92" s="87"/>
+      <c r="U92" s="65"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="53"/>
+      <c r="A93" s="83"/>
       <c r="B93" s="31" t="s">
         <v>133</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D93" s="71"/>
-      <c r="E93" s="71"/>
-      <c r="F93" s="71"/>
-      <c r="G93" s="71"/>
-      <c r="H93" s="71"/>
-      <c r="I93" s="71"/>
-      <c r="J93" s="71"/>
-      <c r="K93" s="71"/>
-      <c r="L93" s="71"/>
-      <c r="M93" s="71"/>
-      <c r="N93" s="71"/>
-      <c r="O93" s="71"/>
-      <c r="P93" s="71"/>
-      <c r="Q93" s="71"/>
-      <c r="R93" s="71"/>
-      <c r="S93" s="71"/>
-      <c r="T93" s="71"/>
-      <c r="U93" s="72"/>
+      <c r="D93" s="86"/>
+      <c r="E93" s="87"/>
+      <c r="F93" s="87"/>
+      <c r="G93" s="87"/>
+      <c r="H93" s="87"/>
+      <c r="I93" s="87"/>
+      <c r="J93" s="87"/>
+      <c r="K93" s="87"/>
+      <c r="L93" s="87"/>
+      <c r="M93" s="87"/>
+      <c r="N93" s="87"/>
+      <c r="O93" s="87"/>
+      <c r="P93" s="87"/>
+      <c r="Q93" s="87"/>
+      <c r="R93" s="87"/>
+      <c r="S93" s="87"/>
+      <c r="T93" s="87"/>
+      <c r="U93" s="65"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="53"/>
+      <c r="A94" s="84"/>
       <c r="B94" s="31" t="s">
         <v>134</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D94" s="73"/>
-      <c r="E94" s="73"/>
-      <c r="F94" s="73"/>
-      <c r="G94" s="73"/>
-      <c r="H94" s="73"/>
-      <c r="I94" s="73"/>
-      <c r="J94" s="73"/>
-      <c r="K94" s="73"/>
-      <c r="L94" s="73"/>
-      <c r="M94" s="73"/>
-      <c r="N94" s="73"/>
-      <c r="O94" s="73"/>
-      <c r="P94" s="73"/>
-      <c r="Q94" s="73"/>
-      <c r="R94" s="73"/>
-      <c r="S94" s="73"/>
-      <c r="T94" s="73"/>
-      <c r="U94" s="74"/>
+      <c r="D94" s="88"/>
+      <c r="E94" s="66"/>
+      <c r="F94" s="66"/>
+      <c r="G94" s="66"/>
+      <c r="H94" s="66"/>
+      <c r="I94" s="66"/>
+      <c r="J94" s="66"/>
+      <c r="K94" s="66"/>
+      <c r="L94" s="66"/>
+      <c r="M94" s="66"/>
+      <c r="N94" s="66"/>
+      <c r="O94" s="66"/>
+      <c r="P94" s="66"/>
+      <c r="Q94" s="66"/>
+      <c r="R94" s="66"/>
+      <c r="S94" s="66"/>
+      <c r="T94" s="66"/>
+      <c r="U94" s="67"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="60">
+      <c r="A95" s="75">
         <v>14</v>
       </c>
       <c r="B95" s="29" t="s">
@@ -10130,7 +10235,7 @@
       <c r="U95" s="16"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="60"/>
+      <c r="A96" s="76"/>
       <c r="B96" s="29" t="s">
         <v>137</v>
       </c>
@@ -10161,7 +10266,7 @@
       <c r="U96" s="16"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="60"/>
+      <c r="A97" s="76"/>
       <c r="B97" s="48" t="s">
         <v>138</v>
       </c>
@@ -10192,7 +10297,7 @@
       <c r="U97" s="16"/>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="60"/>
+      <c r="A98" s="76"/>
       <c r="B98" s="48" t="s">
         <v>139</v>
       </c>
@@ -10223,7 +10328,7 @@
       <c r="U98" s="16"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="60"/>
+      <c r="A99" s="76"/>
       <c r="B99" s="48" t="s">
         <v>140</v>
       </c>
@@ -10254,7 +10359,7 @@
       <c r="U99" s="16"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="60"/>
+      <c r="A100" s="76"/>
       <c r="B100" s="48" t="s">
         <v>141</v>
       </c>
@@ -10285,7 +10390,7 @@
       <c r="U100" s="16"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="60"/>
+      <c r="A101" s="77"/>
       <c r="B101" s="48" t="s">
         <v>142</v>
       </c>
@@ -10316,7 +10421,7 @@
       <c r="U101" s="16"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="53">
+      <c r="A102" s="82">
         <v>15</v>
       </c>
       <c r="B102" s="46" t="s">
@@ -10349,7 +10454,7 @@
       <c r="U102" s="5"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="53"/>
+      <c r="A103" s="83"/>
       <c r="B103" s="46" t="s">
         <v>144</v>
       </c>
@@ -10380,7 +10485,7 @@
       <c r="U103" s="5"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="53"/>
+      <c r="A104" s="83"/>
       <c r="B104" s="46" t="s">
         <v>145</v>
       </c>
@@ -10411,7 +10516,7 @@
       <c r="U104" s="5"/>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="53"/>
+      <c r="A105" s="83"/>
       <c r="B105" s="46" t="s">
         <v>146</v>
       </c>
@@ -10442,7 +10547,7 @@
       <c r="U105" s="5"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="53"/>
+      <c r="A106" s="83"/>
       <c r="B106" s="46" t="s">
         <v>147</v>
       </c>
@@ -10473,7 +10578,7 @@
       <c r="U106" s="5"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="53"/>
+      <c r="A107" s="83"/>
       <c r="B107" s="46" t="s">
         <v>148</v>
       </c>
@@ -10504,7 +10609,7 @@
       <c r="U107" s="5"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="53"/>
+      <c r="A108" s="84"/>
       <c r="B108" s="46" t="s">
         <v>149</v>
       </c>
@@ -10535,7 +10640,7 @@
       <c r="U108" s="5"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="60">
+      <c r="A109" s="75">
         <v>16</v>
       </c>
       <c r="B109" s="48" t="s">
@@ -10568,7 +10673,7 @@
       <c r="U109" s="17"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="60"/>
+      <c r="A110" s="76"/>
       <c r="B110" s="48" t="s">
         <v>151</v>
       </c>
@@ -10599,7 +10704,7 @@
       <c r="U110" s="17"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="60"/>
+      <c r="A111" s="76"/>
       <c r="B111" s="48" t="s">
         <v>152</v>
       </c>
@@ -10630,7 +10735,7 @@
       <c r="U111" s="17"/>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="60"/>
+      <c r="A112" s="76"/>
       <c r="B112" s="48" t="s">
         <v>153</v>
       </c>
@@ -10661,7 +10766,7 @@
       <c r="U112" s="17"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="60"/>
+      <c r="A113" s="76"/>
       <c r="B113" s="48" t="s">
         <v>154</v>
       </c>
@@ -10692,7 +10797,7 @@
       <c r="U113" s="17"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="60"/>
+      <c r="A114" s="76"/>
       <c r="B114" s="48" t="s">
         <v>155</v>
       </c>
@@ -10723,7 +10828,7 @@
       <c r="U114" s="17"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="60"/>
+      <c r="A115" s="77"/>
       <c r="B115" s="48" t="s">
         <v>156</v>
       </c>
@@ -10754,7 +10859,7 @@
       <c r="U115" s="17"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="53">
+      <c r="A116" s="82">
         <v>17</v>
       </c>
       <c r="B116" s="46" t="s">
@@ -10787,7 +10892,7 @@
       <c r="U116" s="5"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="53"/>
+      <c r="A117" s="83"/>
       <c r="B117" s="46" t="s">
         <v>158</v>
       </c>
@@ -10818,7 +10923,7 @@
       <c r="U117" s="5"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="53"/>
+      <c r="A118" s="83"/>
       <c r="B118" s="46" t="s">
         <v>159</v>
       </c>
@@ -10849,7 +10954,7 @@
       <c r="U118" s="5"/>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="53"/>
+      <c r="A119" s="83"/>
       <c r="B119" s="46" t="s">
         <v>160</v>
       </c>
@@ -10880,7 +10985,7 @@
       <c r="U119" s="5"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="53"/>
+      <c r="A120" s="83"/>
       <c r="B120" s="46" t="s">
         <v>161</v>
       </c>
@@ -10911,7 +11016,7 @@
       <c r="U120" s="5"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="53"/>
+      <c r="A121" s="83"/>
       <c r="B121" s="46" t="s">
         <v>162</v>
       </c>
@@ -10942,7 +11047,7 @@
       <c r="U121" s="5"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="53"/>
+      <c r="A122" s="84"/>
       <c r="B122" s="46" t="s">
         <v>163</v>
       </c>
@@ -10973,7 +11078,7 @@
       <c r="U122" s="5"/>
     </row>
     <row r="123" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="60">
+      <c r="A123" s="75">
         <v>18</v>
       </c>
       <c r="B123" s="48" t="s">
@@ -11006,7 +11111,7 @@
       <c r="U123" s="17"/>
     </row>
     <row r="124" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="60"/>
+      <c r="A124" s="76"/>
       <c r="B124" s="48" t="s">
         <v>165</v>
       </c>
@@ -11037,7 +11142,7 @@
       <c r="U124" s="17"/>
     </row>
     <row r="125" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="60"/>
+      <c r="A125" s="76"/>
       <c r="B125" s="48" t="s">
         <v>166</v>
       </c>
@@ -11068,7 +11173,7 @@
       <c r="U125" s="17"/>
     </row>
     <row r="126" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="60"/>
+      <c r="A126" s="76"/>
       <c r="B126" s="48" t="s">
         <v>167</v>
       </c>
@@ -11099,36 +11204,36 @@
       <c r="U126" s="17"/>
     </row>
     <row r="127" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="60"/>
+      <c r="A127" s="76"/>
       <c r="B127" s="51" t="s">
         <v>168</v>
       </c>
       <c r="C127" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D127" s="66" t="s">
+      <c r="D127" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="E127" s="67"/>
-      <c r="F127" s="67"/>
-      <c r="G127" s="67"/>
-      <c r="H127" s="67"/>
-      <c r="I127" s="67"/>
-      <c r="J127" s="67"/>
-      <c r="K127" s="67"/>
-      <c r="L127" s="67"/>
-      <c r="M127" s="67"/>
-      <c r="N127" s="67"/>
-      <c r="O127" s="67"/>
-      <c r="P127" s="67"/>
-      <c r="Q127" s="67"/>
-      <c r="R127" s="67"/>
-      <c r="S127" s="67"/>
-      <c r="T127" s="67"/>
-      <c r="U127" s="68"/>
+      <c r="E127" s="61"/>
+      <c r="F127" s="61"/>
+      <c r="G127" s="61"/>
+      <c r="H127" s="61"/>
+      <c r="I127" s="61"/>
+      <c r="J127" s="61"/>
+      <c r="K127" s="61"/>
+      <c r="L127" s="61"/>
+      <c r="M127" s="61"/>
+      <c r="N127" s="61"/>
+      <c r="O127" s="61"/>
+      <c r="P127" s="61"/>
+      <c r="Q127" s="61"/>
+      <c r="R127" s="61"/>
+      <c r="S127" s="61"/>
+      <c r="T127" s="61"/>
+      <c r="U127" s="62"/>
     </row>
     <row r="128" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="60"/>
+      <c r="A128" s="76"/>
       <c r="B128" s="48" t="s">
         <v>169</v>
       </c>
@@ -11159,7 +11264,7 @@
       <c r="U128" s="17"/>
     </row>
     <row r="129" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="60"/>
+      <c r="A129" s="77"/>
       <c r="B129" s="48" t="s">
         <v>170</v>
       </c>
@@ -11190,7 +11295,7 @@
       <c r="U129" s="17"/>
     </row>
     <row r="130" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="53">
+      <c r="A130" s="82">
         <v>19</v>
       </c>
       <c r="B130" s="46" t="s">
@@ -11223,7 +11328,7 @@
       <c r="U130" s="5"/>
     </row>
     <row r="131" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="53"/>
+      <c r="A131" s="83"/>
       <c r="B131" s="46" t="s">
         <v>172</v>
       </c>
@@ -11254,7 +11359,7 @@
       <c r="U131" s="5"/>
     </row>
     <row r="132" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="53"/>
+      <c r="A132" s="83"/>
       <c r="B132" s="46" t="s">
         <v>173</v>
       </c>
@@ -11285,7 +11390,7 @@
       <c r="U132" s="5"/>
     </row>
     <row r="133" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="53"/>
+      <c r="A133" s="83"/>
       <c r="B133" s="46" t="s">
         <v>174</v>
       </c>
@@ -11316,7 +11421,7 @@
       <c r="U133" s="5"/>
     </row>
     <row r="134" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="53"/>
+      <c r="A134" s="83"/>
       <c r="B134" s="46" t="s">
         <v>175</v>
       </c>
@@ -11347,7 +11452,7 @@
       <c r="U134" s="5"/>
     </row>
     <row r="135" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="53"/>
+      <c r="A135" s="83"/>
       <c r="B135" s="46" t="s">
         <v>176</v>
       </c>
@@ -11378,7 +11483,7 @@
       <c r="U135" s="5"/>
     </row>
     <row r="136" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="53"/>
+      <c r="A136" s="84"/>
       <c r="B136" s="46" t="s">
         <v>177</v>
       </c>
@@ -11424,6 +11529,7 @@
     <row r="150" ht="20.25"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A74:A80"/>
     <mergeCell ref="A123:A129"/>
     <mergeCell ref="D127:U127"/>
     <mergeCell ref="A130:A136"/>
@@ -11434,18 +11540,16 @@
     <mergeCell ref="A109:A115"/>
     <mergeCell ref="A116:A122"/>
     <mergeCell ref="A81:A87"/>
+    <mergeCell ref="M2:O2"/>
     <mergeCell ref="A46:A52"/>
     <mergeCell ref="A53:A59"/>
     <mergeCell ref="A60:A66"/>
     <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
-    <mergeCell ref="J2:L2"/>
     <mergeCell ref="A4:A10"/>
     <mergeCell ref="A11:A17"/>
     <mergeCell ref="A18:A24"/>
     <mergeCell ref="A25:A31"/>
     <mergeCell ref="D29:U31"/>
-    <mergeCell ref="M2:O2"/>
     <mergeCell ref="A32:A38"/>
     <mergeCell ref="D35:U41"/>
     <mergeCell ref="A39:A45"/>
@@ -11461,6 +11565,7 @@
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
